--- a/outils/input/source.xlsx
+++ b/outils/input/source.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\_Boulots\Cine Carbonne\Site\Site_Github_rep\Lab\outils\input\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\_Boulots\Cine Carbonne\Site\Site_Github_rep\outils\input\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B735A55-DDEF-4DA6-B232-AAB68EFF267E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BBF53D85-9B1B-42D3-BD33-F61CC9B9226F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="21840" windowHeight="13740" tabRatio="587" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" tabRatio="587" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="372" uniqueCount="247">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="404" uniqueCount="261">
   <si>
     <t>Semaine</t>
   </si>
@@ -84,9 +84,6 @@
     <t>Catégorie</t>
   </si>
   <si>
-    <t>Séance EPHAD HANDI</t>
-  </si>
-  <si>
     <t>TU 5 €</t>
   </si>
   <si>
@@ -117,664 +114,743 @@
     <t>Empreinte Carbonne 1 film par prog (janvier à mai)</t>
   </si>
   <si>
+    <t>JP</t>
+  </si>
+  <si>
+    <t>Tarif et JP</t>
+  </si>
+  <si>
+    <t>Séances spéciales</t>
+  </si>
+  <si>
+    <t>Prochainement</t>
+  </si>
+  <si>
+    <t>VO/VF</t>
+  </si>
+  <si>
+    <t>Amours chiennes VO</t>
+  </si>
+  <si>
+    <t>VO</t>
+  </si>
+  <si>
+    <t>Ciné goûter JP</t>
+  </si>
+  <si>
+    <t>Réalisateur</t>
+  </si>
+  <si>
+    <t>Prix - Invités</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tout va bien DOC </t>
+  </si>
+  <si>
+    <t>Ciné Patrimoine du samedi 18h</t>
+  </si>
+  <si>
+    <t>ADH 4 € - Autres 5 €</t>
+  </si>
+  <si>
+    <t>La reine Margot - Patrice Chéreau</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Séance EPHAD HANDI </t>
+  </si>
+  <si>
+    <t>Ciné Discussion du samedi 18h</t>
+  </si>
+  <si>
+    <t>La guerre des prix</t>
+  </si>
+  <si>
+    <t>Le chasseur de baleines VO</t>
+  </si>
+  <si>
+    <t>Marsupilami JP Famille</t>
+  </si>
+  <si>
+    <t>It's never over, Jeff Buckley VO DOC</t>
+  </si>
+  <si>
+    <t>Metropolis JP</t>
+  </si>
+  <si>
+    <t>Les légendaires JP</t>
+  </si>
+  <si>
+    <t>La grazia VO</t>
+  </si>
+  <si>
+    <t>La reconquista VO</t>
+  </si>
+  <si>
+    <t>Le retour du projectionniste VO DOC</t>
+  </si>
+  <si>
+    <t>Jusqu'à l'aube VO</t>
+  </si>
+  <si>
+    <t>Super Charlie JP</t>
+  </si>
+  <si>
+    <t>Jeune pousse JP TU 3 €</t>
+  </si>
+  <si>
+    <t>Chers parents</t>
+  </si>
+  <si>
+    <t>Orwell : 2+2=5 VO DOC</t>
+  </si>
+  <si>
+    <t>Un été à la ferme DOC</t>
+  </si>
+  <si>
+    <t>Justa VO</t>
+  </si>
+  <si>
+    <t>Jumpers JP</t>
+  </si>
+  <si>
+    <t>Véronique DOC</t>
+  </si>
+  <si>
+    <t>Deux femmes et quelques hommes</t>
+  </si>
+  <si>
+    <t>Le crime du 3e étage</t>
+  </si>
+  <si>
+    <t>Les K d'or</t>
+  </si>
+  <si>
+    <t>Le testament d'Ann Lee VO</t>
+  </si>
+  <si>
+    <t>Planètes JP Famille</t>
+  </si>
+  <si>
+    <t>Scarlet et l'éternité JP ados à partir de 9/10 ans Sony</t>
+  </si>
+  <si>
+    <t>Orphelin VO</t>
+  </si>
+  <si>
+    <t>Sans toi ni loi</t>
+  </si>
+  <si>
+    <t>Les choses de la vie - Sautet</t>
+  </si>
+  <si>
+    <t>James et la pêche géante JP reprise</t>
+  </si>
+  <si>
+    <t>TU 3 €</t>
+  </si>
+  <si>
+    <t>TU 4,50 €</t>
+  </si>
+  <si>
+    <t>10h</t>
+  </si>
+  <si>
+    <t>14h</t>
+  </si>
+  <si>
+    <t>Les enfants de la Résistance</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JP </t>
+  </si>
+  <si>
+    <t>Ciné Doc du samedi 18h</t>
+  </si>
+  <si>
+    <t>Wong Kar-Wai - The grandmaster VO</t>
+  </si>
+  <si>
+    <t>La traque de Méral</t>
+  </si>
+  <si>
+    <t>La Garonne</t>
+  </si>
+  <si>
+    <t>Nouvelle vague</t>
+  </si>
+  <si>
+    <t>La famille Homolka VO</t>
+  </si>
+  <si>
+    <t>Goat- Rêver plus haut JP</t>
+  </si>
+  <si>
+    <t>Marty Supreme</t>
+  </si>
+  <si>
+    <t>Stand by me VO</t>
+  </si>
+  <si>
+    <t>Derrière les palmiers</t>
+  </si>
+  <si>
+    <t>Yellow letters VO</t>
+  </si>
+  <si>
+    <t>Romeria VO</t>
+  </si>
+  <si>
+    <t>La femme de</t>
+  </si>
+  <si>
+    <t>Silent friend VO 2h25</t>
+  </si>
+  <si>
+    <t>Les contes du pommier JP</t>
+  </si>
+  <si>
+    <t>Morlaix</t>
+  </si>
+  <si>
+    <t>Une fille en or</t>
+  </si>
+  <si>
+    <t>Sauvage</t>
+  </si>
+  <si>
+    <t>La poupée</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+      </rPr>
+      <t>À</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> voix basse VO</t>
+    </r>
+  </si>
+  <si>
+    <t>La corde au cou VO EC</t>
+  </si>
+  <si>
+    <t>Angelo dans la forêt mystérieuse</t>
+  </si>
+  <si>
+    <t>SCOL</t>
+  </si>
+  <si>
+    <t>TU 4 €</t>
+  </si>
+  <si>
+    <t>9h30</t>
+  </si>
+  <si>
+    <t>TU 3,50 €</t>
+  </si>
+  <si>
+    <t>Petites casseroles</t>
+  </si>
+  <si>
+    <t>TU 2,80 €</t>
+  </si>
+  <si>
+    <t>Le peuple loup</t>
+  </si>
+  <si>
+    <t>A walk to freedom</t>
+  </si>
+  <si>
+    <t>Les vacances de Monsieur Hulot</t>
+  </si>
+  <si>
+    <t>Dilili à Paris</t>
+  </si>
+  <si>
+    <t>Arco</t>
+  </si>
+  <si>
+    <t>20h30</t>
+  </si>
+  <si>
+    <t>6 ou 7 nov Bruit du papier</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Les rayons et les ombres </t>
+  </si>
+  <si>
+    <t>Projet dernière chance VF 2h37</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Police flash 80 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reminders of him </t>
+  </si>
+  <si>
+    <t>La danse des renards</t>
+  </si>
+  <si>
+    <t>La gifle VO</t>
+  </si>
+  <si>
+    <t>Las corrientes VO</t>
+  </si>
+  <si>
+    <t>Scènes de nuit VO</t>
+  </si>
+  <si>
+    <t>Précieuses DOC</t>
+  </si>
+  <si>
+    <t>Silentium VO</t>
+  </si>
+  <si>
+    <t>Ceux qui comptent</t>
+  </si>
+  <si>
+    <t>L'ultime héritier VF</t>
+  </si>
+  <si>
+    <t>Anémone Les racines du mensonge VO</t>
+  </si>
+  <si>
+    <t>Walter lapin JP</t>
+  </si>
+  <si>
+    <t>Love on trial VO</t>
+  </si>
+  <si>
+    <t>L'ile de la demoiselle</t>
+  </si>
+  <si>
+    <t>Un jour avec mon père VO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Julian </t>
+  </si>
+  <si>
+    <t>Les filles du ciel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Plus forts que le diable </t>
+  </si>
+  <si>
+    <t>Vol au-dessus d'un nid de coucou VO</t>
+  </si>
+  <si>
+    <t>L'odyssée de Céleste JP</t>
+  </si>
+  <si>
+    <t>Une jeunesse indienne Homebound VO</t>
+  </si>
+  <si>
+    <t>La couleuvre noire VO</t>
+  </si>
+  <si>
+    <t>Edmond et Lucy La forêt c'est l'aventure JP TU 3 €</t>
+  </si>
+  <si>
+    <t>Derrière les drapeaux le soleil VO DOC</t>
+  </si>
+  <si>
+    <t>Les saisons VO DOC</t>
+  </si>
+  <si>
+    <t>La dame deShangaï VO</t>
+  </si>
+  <si>
+    <t>La marque du tueur VO</t>
+  </si>
+  <si>
+    <t>Compostelle</t>
+  </si>
+  <si>
+    <t>Super Mario Galaxy Le film JP</t>
+  </si>
+  <si>
+    <t>The drama VO</t>
+  </si>
+  <si>
+    <t>Plus fort que moi I swear VO</t>
+  </si>
+  <si>
+    <t>Mauvaise pioche</t>
+  </si>
+  <si>
+    <t>Silent friend VO</t>
+  </si>
+  <si>
+    <t>Nuestra tierra VO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le goût des autres </t>
+  </si>
+  <si>
+    <t>Le secret du loup d'Ethiopie JP Famille</t>
+  </si>
+  <si>
+    <t>Peppa au cinéma La famille s'agrandit JP TU 3 €</t>
+  </si>
+  <si>
+    <t>Holding liat VO DOC</t>
+  </si>
+  <si>
+    <t>Cocorico 2</t>
+  </si>
+  <si>
+    <t>L'enfant du désert JP Famillle</t>
+  </si>
+  <si>
+    <t>Le cri des gardes VO</t>
+  </si>
+  <si>
+    <t>Le dernier pour la route VO</t>
+  </si>
+  <si>
+    <t>Pour Klara VO</t>
+  </si>
+  <si>
+    <t>Bisons VO</t>
+  </si>
+  <si>
+    <t>Sur le sentier</t>
+  </si>
+  <si>
+    <t>The world is full of secret VO</t>
+  </si>
+  <si>
+    <t>An evening song VO</t>
+  </si>
+  <si>
+    <t>La ville des chiens VO</t>
+  </si>
+  <si>
+    <t>Little feet VO</t>
+  </si>
+  <si>
+    <t>Juste une illusion, Good luck have fun don't die, Une fille en or, La corde au cou, Morlaix, La fille du konbini, Mickaël, Pour le meilleur, L'arnaqueuse, Les fleurs du manguier, Soum-soum la nuit des astres, Le diable s'habille en Prada 2, Die my love, Sorda, Vivaldi et moi, Sukwann island, L'enfant bélier, Pour le plaisir, C'est quoi l'amour, Sauvaons les meubles, Mon grand-frèrecet moi, Mi amor...</t>
+  </si>
+  <si>
+    <t>Poisson rouge - Fiction - 03'00 (du 3/6 au 7/7)</t>
+  </si>
+  <si>
+    <t>Plan V - Documentaire - 03'00 (du 3/6 au 7/7)</t>
+  </si>
+  <si>
+    <t>J 28/05 soirée</t>
+  </si>
+  <si>
+    <t>La princesse, l'ogre et la fourmi  JPTU 3 €</t>
+  </si>
+  <si>
     <t>17h</t>
   </si>
   <si>
-    <t>Ciné Jeunes du samedi 18h</t>
-  </si>
-  <si>
-    <t>JP</t>
-  </si>
-  <si>
-    <t>Tarif et JP</t>
-  </si>
-  <si>
-    <t>Séances spéciales</t>
-  </si>
-  <si>
-    <t>Prochainement</t>
-  </si>
-  <si>
-    <t>VO/VF</t>
-  </si>
-  <si>
-    <t>Amours chiennes VO</t>
-  </si>
-  <si>
-    <t>VO</t>
-  </si>
-  <si>
-    <t>Ciné goûter JP</t>
-  </si>
-  <si>
-    <t>Réalisateur</t>
-  </si>
-  <si>
-    <t>Prix - Invités</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tout va bien DOC </t>
-  </si>
-  <si>
-    <t>Les lumières de New York VO</t>
-  </si>
-  <si>
-    <t>Mr Nobody against Putin VO DOC</t>
-  </si>
-  <si>
-    <t>Alter ego</t>
-  </si>
-  <si>
-    <t>Victor comme tout le monde</t>
-  </si>
-  <si>
-    <t>Ciné Patrimoine du samedi 18h</t>
-  </si>
-  <si>
-    <t>ADH 4 € - Autres 5 €</t>
-  </si>
-  <si>
-    <t>Ciné Documentaire du samedi 18h</t>
-  </si>
-  <si>
-    <t>La reine Margot - Patrice Chéreau</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Séance EPHAD HANDI </t>
-  </si>
-  <si>
-    <t>Ciné Discussion du samedi 18h</t>
-  </si>
-  <si>
-    <t>Rue Malaga VO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rural DOC invité ? </t>
-  </si>
-  <si>
-    <t>Little trouble girls VO</t>
-  </si>
-  <si>
-    <t>Pédale rurale DOC</t>
-  </si>
-  <si>
-    <t>La guerre des prix</t>
-  </si>
-  <si>
-    <t>Ce qu'il reste de nous</t>
-  </si>
-  <si>
-    <t>La gifle VO</t>
-  </si>
-  <si>
-    <t>Ce qu'il reste de nous VO 2h25</t>
-  </si>
-  <si>
-    <t>Les filles du ciel</t>
-  </si>
-  <si>
-    <t>Love on trial VO</t>
-  </si>
-  <si>
-    <t>Diamanti VO</t>
-  </si>
-  <si>
-    <t>Le chasseur de baleines VO</t>
-  </si>
-  <si>
-    <t>Marsupilami JP Famille</t>
-  </si>
-  <si>
-    <t>Les enfants de la Résistance JP Famille</t>
-  </si>
-  <si>
-    <t>Urchin VO</t>
-  </si>
-  <si>
-    <t>Sainte-Marie aux Mines</t>
-  </si>
-  <si>
-    <t>It's never over, Jeff Buckley VO DOC</t>
-  </si>
-  <si>
-    <t>Metropolis JP</t>
-  </si>
-  <si>
-    <t>Goat - rêver plus haut JP</t>
-  </si>
-  <si>
-    <t>Send help VO</t>
-  </si>
-  <si>
-    <t>Stand by me VO ou VF</t>
-  </si>
-  <si>
-    <t>Le gâteau du président VO</t>
-  </si>
-  <si>
-    <t>Rental family - Dans la vie des autres VO</t>
-  </si>
-  <si>
-    <t>Une balle dans la tête VO John Woo Empreinte Carbonne</t>
-  </si>
-  <si>
-    <t>Les légendaires JP</t>
-  </si>
-  <si>
-    <t>La grazia VO</t>
-  </si>
-  <si>
-    <t>La reconquista VO</t>
-  </si>
-  <si>
-    <t>La grande rêvasion JP</t>
-  </si>
-  <si>
-    <t>Le retour du projectionniste VO DOC</t>
-  </si>
-  <si>
-    <t>Jusqu'à l'aube VO</t>
-  </si>
-  <si>
-    <t>Marty Supreme VO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Le rêve américain </t>
-  </si>
-  <si>
-    <t>Cold storage VF</t>
-  </si>
-  <si>
-    <t>Maigret et le mort amoureux</t>
-  </si>
-  <si>
-    <t>Un monde fragile et merveilleux VO</t>
-  </si>
-  <si>
-    <t>Super Charlie JP</t>
-  </si>
-  <si>
-    <t>Au-delà de Katmandou VO DOC</t>
-  </si>
-  <si>
-    <t>L'ourse et l'oiseau JP TU 3 €</t>
-  </si>
-  <si>
-    <t>La famille Addams JP reprise</t>
-  </si>
-  <si>
-    <t>Esprits rebelles JP TU 3 €</t>
-  </si>
-  <si>
-    <t>Jeune pousse JP TU 3 €</t>
-  </si>
-  <si>
-    <t>Chers parents</t>
-  </si>
-  <si>
-    <t>Scream 7 VF</t>
-  </si>
-  <si>
-    <t>ATHOS - Au cœur de la patrouille de France DOC</t>
-  </si>
-  <si>
-    <t>Le son des souvenirs VO</t>
-  </si>
-  <si>
-    <t>Is this thing on ? VO</t>
-  </si>
-  <si>
-    <t>Orwell : 2+2=5 VO DOC</t>
-  </si>
-  <si>
-    <t>The grandmaster VO</t>
-  </si>
-  <si>
-    <t>Nouvelle vague (ressortie)</t>
-  </si>
-  <si>
-    <t>Women and child VO</t>
-  </si>
-  <si>
-    <t>Un été à la ferme DOC</t>
-  </si>
-  <si>
-    <t>Justa VO</t>
-  </si>
-  <si>
-    <t>5 centimètres par seconde VO</t>
-  </si>
-  <si>
-    <t>Quartier libre</t>
-  </si>
-  <si>
-    <t>Tenir debout</t>
-  </si>
-  <si>
-    <t xml:space="preserve">La maison des femmes </t>
-  </si>
-  <si>
-    <t>The bride ! VO u VF</t>
-  </si>
-  <si>
-    <t>Jumpers JP</t>
-  </si>
-  <si>
-    <t>Pillion VO</t>
-  </si>
-  <si>
-    <t>Rural DOC</t>
-  </si>
-  <si>
-    <t>Christy VO</t>
-  </si>
-  <si>
-    <t>Nino dans la nuit</t>
-  </si>
-  <si>
-    <t>Allah n'est pas obligé JP famille à partir de 9/10 ans</t>
-  </si>
-  <si>
-    <t>Véronique DOC</t>
-  </si>
-  <si>
-    <t>Deux femmes et quelques hommes</t>
-  </si>
-  <si>
-    <t>Une dernière chance</t>
-  </si>
-  <si>
-    <t>Le crime du 3e étage</t>
-  </si>
-  <si>
-    <t>Il maestro VO</t>
-  </si>
-  <si>
-    <t>Les K d'or</t>
-  </si>
-  <si>
-    <t>Le testament d'Ann Lee VO</t>
-  </si>
-  <si>
-    <t>Planètes JP Famille</t>
-  </si>
-  <si>
-    <t>Scarlet et l'éternité JP ados à partir de 9/10 ans Sony</t>
-  </si>
-  <si>
-    <t>Orphelin VO</t>
-  </si>
-  <si>
-    <t>La traque de Meral VO</t>
-  </si>
-  <si>
-    <t>Sans toi ni loi</t>
-  </si>
-  <si>
-    <t>Wong Kar-Wai</t>
-  </si>
-  <si>
-    <t>Encontro</t>
-  </si>
-  <si>
-    <t>Les choses de la vie - Sautet</t>
-  </si>
-  <si>
-    <t xml:space="preserve">La couleuvre noire </t>
-  </si>
-  <si>
-    <t>Aurélien Vernhes-Lermusiaux</t>
-  </si>
-  <si>
-    <t>Cinélatino Avant-première</t>
-  </si>
-  <si>
-    <t>James et la pêche géante JP reprise</t>
-  </si>
-  <si>
-    <t>Coutures VF et VO</t>
-  </si>
-  <si>
-    <t>Le rêve américain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Urchin </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rue Malaga </t>
-  </si>
-  <si>
-    <t>TU 3 €</t>
-  </si>
-  <si>
-    <t xml:space="preserve">L'ourse et l'oiseau </t>
-  </si>
-  <si>
-    <t>invité Jérôme Bayle attente de réponse</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rural </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Marty Supreme </t>
+    <t>avec Empreinte Carbonne</t>
+  </si>
+  <si>
+    <t>20h15</t>
+  </si>
+  <si>
+    <t>11h</t>
+  </si>
+  <si>
+    <t>Rural</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yellow letters </t>
+  </si>
+  <si>
+    <t>Découverte</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Silent friend </t>
+  </si>
+  <si>
+    <t xml:space="preserve">La grazia </t>
+  </si>
+  <si>
+    <t>Coup de cœur</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Goat- Rêver plus haut </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Un jour avec mon père </t>
+  </si>
+  <si>
+    <t>Mention Jury  deJeunes Carbonne fait son Cinéma</t>
+  </si>
+  <si>
+    <t>Ciné Jeunes du samedi 18h - JP  Ados</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Scarlet et l'éternité </t>
+  </si>
+  <si>
+    <t xml:space="preserve">La princesse, l'ogre et la fourmi  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jumpers </t>
+  </si>
+  <si>
+    <t>JP Ados à partir cde 9/10 ans</t>
+  </si>
+  <si>
+    <t>Meilleur scénario Jury de jeunes et meilleur scénario jury d'adultes FCFC Mention Caméra d'or Cannes 2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Projet dernière chance </t>
+  </si>
+  <si>
+    <t>VF</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Orwell : 2+2=5 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Edmond et Lucy La forêt c'est l'aventure </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Les contes du pommier </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Super Mario Galaxy Le film </t>
+  </si>
+  <si>
+    <t>Séance EPHAD HANDI JP Famille</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le secret du loup d'Ethiopie </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Walter lapin </t>
+  </si>
+  <si>
+    <t xml:space="preserve">La soif du mal </t>
+  </si>
+  <si>
+    <t>DOC</t>
+  </si>
+  <si>
+    <t>Grand prix jury de jeunes Festival muret</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Une jeunesse indienne Homebound </t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+      </rPr>
+      <t>À</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> voix basse </t>
+    </r>
   </si>
   <si>
     <t>JP Famille</t>
   </si>
   <si>
-    <t xml:space="preserve">Marsupilami </t>
-  </si>
-  <si>
-    <t>VF/VO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Coutures </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pédale rurale </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Little trouble girls </t>
-  </si>
-  <si>
-    <t>Partenariat Empreinte Carbonne</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Les enfants de la Résistance </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Une balle dans la tête </t>
-  </si>
-  <si>
-    <t xml:space="preserve">La gifle </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ce qu'il reste de nous </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Un monde fragile et merveilleux </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jumpers </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Christy </t>
-  </si>
-  <si>
-    <t>JP Famille  à partir de 9/10 ans</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Allah n'est pas obligé </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pillion </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Love on trial </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Il maestro </t>
-  </si>
-  <si>
-    <t>JP ados à partir de 9/10 ans Sony</t>
-  </si>
-  <si>
-    <t>Sony</t>
-  </si>
-  <si>
-    <t>TU 4,50 €</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Scarlet et l'éternité </t>
-  </si>
-  <si>
-    <t>VF</t>
-  </si>
-  <si>
-    <t xml:space="preserve">La grazia </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Le son des souvenirs </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Planètes </t>
-  </si>
-  <si>
-    <t>Golden Globe meilleur acteur</t>
-  </si>
-  <si>
-    <t>Harris Dickinson</t>
-  </si>
-  <si>
-    <t>Maryam Touzani</t>
-  </si>
-  <si>
-    <t>Grand Prix Jury de jeunes Carbonne fait son cinéma - Meilleure interprétation Un certain regard Cannes</t>
-  </si>
-  <si>
-    <t>Prix du public Venise</t>
-  </si>
-  <si>
-    <t>Prix Fondation Gan</t>
-  </si>
-  <si>
-    <t>Marie Caudry, Aurore Peuffier, Nina Bisyarina</t>
+    <t xml:space="preserve">L'enfant du désert </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le dernier pour la route </t>
+  </si>
+  <si>
+    <t xml:space="preserve">La corde au cou </t>
+  </si>
+  <si>
+    <t>Coup de coeur</t>
+  </si>
+  <si>
+    <t>CM1</t>
+  </si>
+  <si>
+    <t>CM2</t>
+  </si>
+  <si>
+    <t>Ilker Catak</t>
+  </si>
+  <si>
+    <t>Michel Ocelot</t>
+  </si>
+  <si>
+    <t>Vincent Paronnaud</t>
+  </si>
+  <si>
+    <t>Ildiko Enyedi</t>
+  </si>
+  <si>
+    <t>Ugo Bienvenu</t>
+  </si>
+  <si>
+    <t>Emmanuel Patron</t>
+  </si>
+  <si>
+    <t>Paolo Sorrentino</t>
+  </si>
+  <si>
+    <t>Eduard Nazarov</t>
+  </si>
+  <si>
+    <t>Mamoru Hosoda</t>
+  </si>
+  <si>
+    <t>Xavier Giannoli</t>
+  </si>
+  <si>
+    <t>Daniel Chong</t>
+  </si>
+  <si>
+    <t>Meryem Benm'Barek</t>
+  </si>
+  <si>
+    <t>Valéry Carnoy</t>
+  </si>
+  <si>
+    <t>Tyree Dillihay</t>
+  </si>
+  <si>
+    <t>Akinola Davies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kirk Jones </t>
+  </si>
+  <si>
+    <t>David Roux</t>
+  </si>
+  <si>
+    <t>François Narboux</t>
+  </si>
+  <si>
+    <t>Raoul Peck</t>
+  </si>
+  <si>
+    <t>Phil Lord, Christopher Miller</t>
+  </si>
+  <si>
+    <t>Patrick Pass Jr</t>
+  </si>
+  <si>
+    <t>Jean-Baptiste Léonetti</t>
+  </si>
+  <si>
+    <t>Carla Simon</t>
+  </si>
+  <si>
+    <t>Camille Ponsin</t>
+  </si>
+  <si>
+    <t>Aaron Horvath</t>
+  </si>
+  <si>
+    <t>Jean-Luc Gaget</t>
+  </si>
+  <si>
+    <t>Baptiste Deturche</t>
+  </si>
+  <si>
+    <t>Jezan-Baptiste Saurel</t>
+  </si>
+  <si>
+    <t>M</t>
+  </si>
+  <si>
+    <t>H</t>
+  </si>
+  <si>
+    <t>Caroline Origer</t>
+  </si>
+  <si>
+    <t>Orson Welles</t>
+  </si>
+  <si>
+    <t>Jaime Rosales</t>
   </si>
   <si>
     <t>Edouard Bergeon</t>
   </si>
   <si>
-    <t>Josh Safdie</t>
-  </si>
-  <si>
-    <t>Philippe Lacheau</t>
-  </si>
-  <si>
-    <t>Pascal Bonitzer</t>
-  </si>
-  <si>
-    <t>Alice Winocour</t>
-  </si>
-  <si>
-    <t>Antine Vasquez</t>
-  </si>
-  <si>
-    <t>Urška Djukić</t>
-  </si>
-  <si>
-    <t>Natalia Chernysheva</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Esprit(s) rebelle(s) </t>
-  </si>
-  <si>
-    <t>John Woo</t>
-  </si>
-  <si>
-    <t>Anthony Marciano</t>
-  </si>
-  <si>
     <t>Christophe Barratier</t>
   </si>
   <si>
-    <t>Emmanuel Patron</t>
-  </si>
-  <si>
-    <t>Frédéric Hambalek</t>
-  </si>
-  <si>
-    <t>Cherien Dabis</t>
-  </si>
-  <si>
-    <t>Cyril Aris</t>
-  </si>
-  <si>
-    <t>Daniel Chong</t>
-  </si>
-  <si>
-    <t>David Michôd</t>
-  </si>
-  <si>
-    <t>Melisa Godet</t>
-  </si>
-  <si>
-    <t>Zaven Najjar</t>
-  </si>
-  <si>
-    <t>Anthony Dechaux</t>
-  </si>
-  <si>
-    <t>Nicolas Charlet, Bruno Lavaine</t>
-  </si>
-  <si>
-    <t>Saeed Roustaee</t>
-  </si>
-  <si>
-    <t>Harry Lighton</t>
-  </si>
-  <si>
-    <t>Kôji Fukada</t>
-  </si>
-  <si>
-    <t>Andrea di Stefano</t>
-  </si>
-  <si>
-    <t>Mamoru Hosoda</t>
-  </si>
-  <si>
-    <t>Paolo Sorrentino</t>
-  </si>
-  <si>
-    <t>Oliver Hermanus</t>
-  </si>
-  <si>
-    <t>Momoko Seto</t>
-  </si>
-  <si>
-    <t>Rémi Bezançon</t>
-  </si>
-  <si>
-    <t>Bérangère Mc Neese</t>
-  </si>
-  <si>
-    <t>11h</t>
-  </si>
-  <si>
-    <t>Le chant des forêts</t>
-  </si>
-  <si>
-    <t>Vincent Munier</t>
-  </si>
-  <si>
-    <t>Séance sup suite séance annulée</t>
-  </si>
-  <si>
-    <t>14h30</t>
-  </si>
-  <si>
-    <t>Le sommet des dieux</t>
-  </si>
-  <si>
-    <t>SCOL CauC</t>
-  </si>
-  <si>
-    <t>Collège Noé</t>
-  </si>
-  <si>
-    <t>10h</t>
-  </si>
-  <si>
-    <t>Microcosmos</t>
-  </si>
-  <si>
-    <t>SCOL EauC</t>
-  </si>
-  <si>
-    <t>Ec Labsstide Clermont</t>
-  </si>
-  <si>
-    <t>Les Tourouges et les Toubleus</t>
-  </si>
-  <si>
-    <t>SCOL liste</t>
-  </si>
-  <si>
-    <t>Ec mat Hellé</t>
-  </si>
-  <si>
-    <t>14h</t>
-  </si>
-  <si>
-    <t>Les enfants de la Résistance</t>
-  </si>
-  <si>
-    <t>SCOL Actu</t>
-  </si>
-  <si>
-    <t>SCOL Liste</t>
-  </si>
-  <si>
-    <t>13h30</t>
-  </si>
-  <si>
-    <t>Les figures de l'ombre</t>
-  </si>
-  <si>
-    <t>SCOL Pass culture</t>
-  </si>
-  <si>
-    <t>Le chant de la mer</t>
-  </si>
-  <si>
-    <t>Collège Abbal</t>
-  </si>
-  <si>
-    <t>Hellé élem</t>
-  </si>
-  <si>
-    <t>Léo la fabuleuse histoire de Léonard de Vinci</t>
-  </si>
-  <si>
-    <t>Ec Rieux</t>
-  </si>
-  <si>
-    <t>Ec Lautignac</t>
-  </si>
-  <si>
-    <t>Patrick Imbert</t>
-  </si>
-  <si>
-    <t>Claude Nuridsany, Marie Pérennou</t>
-  </si>
-  <si>
-    <t>Samantha Cutler, Daniel Snaddon</t>
-  </si>
-  <si>
-    <t>Theodore Melfi</t>
-  </si>
-  <si>
-    <t>Tomm Moore</t>
-  </si>
-  <si>
-    <t>Jim Capobianco</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Les rayons et les ombres, Police Flash 80, Reminders of him, La danse des renards, Las corrientes,  Ceux qui comptent, Anemone les racines du mensonge, Julian, Un jour avec mon père, Walter lapin, Une jeunesse indienne,  Compostelle, I swear Plus fort que moi,  Mauvaise pioche, Yellow letters, Silent Friend, Derrière les palmiers, Cocorico 2, L'enfant du désert, La femme de, Romeria, Le cri des gardes, Le dernier pour la route, Les contes du pommier... </t>
-  </si>
-  <si>
-    <t>Coup de cœur</t>
-  </si>
-  <si>
-    <t>DOC Découverte</t>
-  </si>
-  <si>
-    <t>Découverte</t>
-  </si>
-  <si>
-    <t>DOC Coup de coeur</t>
-  </si>
-  <si>
-    <t>Woman and child</t>
+    <t>Uzi Geffenblad</t>
+  </si>
+  <si>
+    <t>Neeraj Ghaywan</t>
+  </si>
+  <si>
+    <t>Leyla Bouzid</t>
+  </si>
+  <si>
+    <t>Sophie Beaulieu</t>
+  </si>
+  <si>
+    <t>Gilles de Maistre</t>
+  </si>
+  <si>
+    <t>Yann Samuell</t>
+  </si>
+  <si>
+    <t>Frnacesco Sossai</t>
+  </si>
+  <si>
+    <t>Justin Chadwick</t>
+  </si>
+  <si>
+    <t>Jacques Tati</t>
+  </si>
+  <si>
+    <t>Gus Van Sant</t>
+  </si>
+  <si>
+    <t>CM3 : Super V - Comédie - 02'00 (du 6/5 au 2/6)</t>
+  </si>
+  <si>
+    <t>CM4 : Des filles et des chiens - Comédie - 05'00 (du 6/5 au 2/6)</t>
+  </si>
+  <si>
+    <t>CM3</t>
+  </si>
+  <si>
+    <t>CM4</t>
+  </si>
+  <si>
+    <t>CM1 : Je ne suis pas  - Film militant - 04'00</t>
+  </si>
+  <si>
+    <t>CM2 : Le futur sera chauve - Animation - 05'36</t>
+  </si>
+  <si>
+    <t>Prix montage et interpréation FCFC</t>
+  </si>
+  <si>
+    <t>Plus fort que moi</t>
+  </si>
+  <si>
+    <t>Romeria</t>
   </si>
 </sst>
 </file>
@@ -786,7 +862,7 @@
     <numFmt numFmtId="8" formatCode="#,##0.00\ &quot;€&quot;;[Red]\-#,##0.00\ &quot;€&quot;"/>
     <numFmt numFmtId="164" formatCode="[$-40C]d\-mmm;@"/>
   </numFmts>
-  <fonts count="22" x14ac:knownFonts="1">
+  <fonts count="23" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -932,8 +1008,14 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="17">
+  <fills count="16">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1008,25 +1090,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.39997558519241921"/>
+        <fgColor theme="5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC000"/>
+        <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="1"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1225,7 +1301,7 @@
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="230">
+  <cellXfs count="241">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -1515,17 +1591,11 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="18" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="14" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="6" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1556,9 +1626,6 @@
     <xf numFmtId="0" fontId="19" fillId="7" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="6" fontId="5" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -1613,9 +1680,6 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1628,9 +1692,6 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -1649,23 +1710,14 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1684,19 +1736,12 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1710,9 +1755,6 @@
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -1722,43 +1764,13 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="13" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="14" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="2"/>
-    <xf numFmtId="0" fontId="8" fillId="14" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" xfId="2" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="15" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="15" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="15" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="15" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="16" borderId="4" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="13" borderId="4" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="8" fontId="5" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1770,23 +1782,11 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="16" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="16" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="13" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="6" fontId="6" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="16" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="16" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="16" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="6" fontId="5" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -1825,6 +1825,74 @@
     <xf numFmtId="164" fontId="4" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="13" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="8" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="8" fontId="8" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="14" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="14" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="13" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="13" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="14" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -1849,32 +1917,67 @@
     <xf numFmtId="164" fontId="0" fillId="6" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="16" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="8" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="8" fontId="8" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="16" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="6" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="14" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="15" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="15" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="15" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="15" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="15" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="15" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="2" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="2" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -2212,12 +2315,12 @@
   <dimension ref="A1:O114"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="10.85546875" style="201" customWidth="1"/>
+    <col min="2" max="2" width="10.85546875" style="173" customWidth="1"/>
     <col min="3" max="3" width="8.28515625" customWidth="1"/>
-    <col min="4" max="4" width="5" style="114" customWidth="1"/>
+    <col min="4" max="4" width="5" style="112" customWidth="1"/>
     <col min="5" max="5" width="69.5703125" style="3" customWidth="1"/>
     <col min="6" max="6" width="7.28515625" style="85" customWidth="1"/>
-    <col min="7" max="7" width="6.85546875" style="3" customWidth="1"/>
+    <col min="7" max="7" width="6.85546875" style="85" customWidth="1"/>
     <col min="8" max="8" width="33.5703125" style="3" customWidth="1"/>
     <col min="9" max="9" width="79.140625" style="3" customWidth="1"/>
     <col min="10" max="10" width="35.28515625" style="2" customWidth="1"/>
@@ -2229,929 +2332,972 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="E1" s="102"/>
-      <c r="F1" s="103"/>
-      <c r="G1" s="104"/>
-      <c r="H1" s="104"/>
-      <c r="I1" s="104"/>
-      <c r="J1" s="105"/>
-      <c r="K1" s="192"/>
-      <c r="L1" s="102"/>
+      <c r="E1" s="101" t="s">
+        <v>256</v>
+      </c>
+      <c r="F1" s="103" t="s">
+        <v>252</v>
+      </c>
+      <c r="G1" s="102"/>
+      <c r="H1" s="103"/>
+      <c r="I1" s="101"/>
+      <c r="J1" s="101" t="s">
+        <v>163</v>
+      </c>
+      <c r="K1" s="168"/>
+      <c r="L1" s="101"/>
     </row>
     <row r="2" spans="1:14" s="1" customFormat="1" ht="15.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="202"/>
-      <c r="D2" s="115"/>
-      <c r="E2" s="102"/>
-      <c r="F2" s="106"/>
-      <c r="G2" s="107"/>
-      <c r="H2" s="107"/>
-      <c r="I2" s="107"/>
-      <c r="J2" s="105"/>
-      <c r="K2" s="192"/>
-      <c r="L2" s="102"/>
+      <c r="B2" s="174"/>
+      <c r="D2" s="113"/>
+      <c r="E2" s="101" t="s">
+        <v>257</v>
+      </c>
+      <c r="F2" s="234" t="s">
+        <v>253</v>
+      </c>
+      <c r="G2" s="104"/>
+      <c r="H2" s="105"/>
+      <c r="I2" s="101"/>
+      <c r="J2" s="101" t="s">
+        <v>164</v>
+      </c>
+      <c r="K2" s="168"/>
+      <c r="L2" s="101"/>
       <c r="M2" s="6"/>
     </row>
     <row r="3" spans="1:14" s="71" customFormat="1" ht="21.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="1"/>
-      <c r="B3" s="202"/>
-      <c r="D3" s="116"/>
+      <c r="B3" s="174"/>
+      <c r="D3" s="114"/>
       <c r="E3" s="72" t="s">
         <v>14</v>
       </c>
-      <c r="F3" s="117" t="s">
-        <v>33</v>
+      <c r="F3" s="115" t="s">
+        <v>30</v>
       </c>
       <c r="G3" s="86" t="s">
         <v>13</v>
       </c>
-      <c r="H3" s="125" t="s">
-        <v>37</v>
+      <c r="H3" s="122" t="s">
+        <v>34</v>
       </c>
       <c r="I3" s="75" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="J3" s="73" t="s">
         <v>15</v>
       </c>
       <c r="K3" s="76" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="L3" s="76" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="M3" s="74"/>
     </row>
     <row r="4" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="203" t="s">
+      <c r="A4" s="175" t="s">
         <v>0</v>
       </c>
-      <c r="B4" s="204">
-        <v>46099</v>
+      <c r="B4" s="176">
+        <v>46127</v>
       </c>
       <c r="C4" s="7"/>
       <c r="D4" s="8"/>
       <c r="E4" s="69"/>
       <c r="F4" s="82"/>
-      <c r="G4" s="69"/>
+      <c r="G4" s="82"/>
       <c r="H4" s="69"/>
       <c r="I4" s="69"/>
       <c r="J4" s="70"/>
       <c r="K4" s="70"/>
       <c r="L4" s="70"/>
       <c r="M4" s="62">
-        <v>46071</v>
+        <v>46099</v>
       </c>
       <c r="N4" s="63" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A5" s="205" t="s">
+      <c r="A5" s="177" t="s">
         <v>1</v>
       </c>
-      <c r="B5" s="206">
-        <v>46099</v>
+      <c r="B5" s="178">
+        <v>46127</v>
       </c>
       <c r="C5" s="11"/>
       <c r="D5" s="12"/>
       <c r="E5" s="13"/>
-      <c r="F5" s="127"/>
-      <c r="G5" s="42"/>
+      <c r="F5" s="124"/>
+      <c r="G5" s="124"/>
       <c r="H5" s="42"/>
       <c r="I5" s="42"/>
       <c r="J5" s="42"/>
       <c r="K5" s="13"/>
       <c r="L5" s="13"/>
       <c r="M5" s="55" t="s">
-        <v>42</v>
-      </c>
-      <c r="N5" s="22" t="s">
-        <v>41</v>
+        <v>89</v>
+      </c>
+      <c r="N5" s="120" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A6" s="27"/>
-      <c r="B6" s="207"/>
+      <c r="B6" s="179"/>
       <c r="C6" s="14"/>
-      <c r="D6" s="128"/>
+      <c r="D6" s="125"/>
       <c r="E6" s="15"/>
-      <c r="F6" s="129"/>
-      <c r="G6" s="38"/>
+      <c r="F6" s="126"/>
+      <c r="G6" s="126"/>
       <c r="H6" s="38"/>
       <c r="I6" s="38"/>
       <c r="J6" s="38"/>
       <c r="K6" s="15"/>
       <c r="L6" s="15"/>
       <c r="M6" s="55" t="s">
-        <v>51</v>
-      </c>
-      <c r="N6" s="26" t="s">
-        <v>39</v>
+        <v>85</v>
+      </c>
+      <c r="N6" s="121" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A7" s="27"/>
-      <c r="B7" s="207"/>
+      <c r="B7" s="179"/>
       <c r="C7" s="14"/>
-      <c r="D7" s="128"/>
+      <c r="D7" s="125"/>
       <c r="E7" s="15"/>
-      <c r="F7" s="129"/>
-      <c r="G7" s="38"/>
+      <c r="F7" s="126"/>
+      <c r="G7" s="126"/>
       <c r="H7" s="38"/>
       <c r="I7" s="38"/>
       <c r="J7" s="38"/>
       <c r="K7" s="15"/>
       <c r="L7" s="15"/>
       <c r="M7" s="55" t="s">
-        <v>50</v>
-      </c>
-      <c r="N7" s="22" t="s">
-        <v>40</v>
+        <v>86</v>
+      </c>
+      <c r="N7" s="27" t="s">
+        <v>51</v>
       </c>
     </row>
     <row r="8" spans="1:14" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="41"/>
-      <c r="B8" s="208"/>
+      <c r="B8" s="180"/>
       <c r="C8" s="16" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="17"/>
-      <c r="E8" s="22" t="s">
-        <v>134</v>
-      </c>
-      <c r="F8" s="130" t="s">
-        <v>35</v>
-      </c>
-      <c r="G8" s="37"/>
-      <c r="H8" s="183" t="s">
-        <v>169</v>
-      </c>
-      <c r="I8" s="37" t="s">
-        <v>171</v>
-      </c>
+      <c r="E8" s="226" t="s">
+        <v>172</v>
+      </c>
+      <c r="F8" s="127" t="s">
+        <v>32</v>
+      </c>
+      <c r="G8" s="127"/>
+      <c r="H8" s="231" t="s">
+        <v>207</v>
+      </c>
+      <c r="I8" s="37"/>
       <c r="J8" s="43" t="s">
-        <v>242</v>
+        <v>173</v>
       </c>
       <c r="K8" s="18"/>
       <c r="L8" s="100"/>
       <c r="M8" s="20" t="s">
-        <v>80</v>
-      </c>
-      <c r="N8" s="22" t="s">
-        <v>60</v>
+        <v>112</v>
+      </c>
+      <c r="N8" s="2" t="s">
+        <v>43</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A9" s="209" t="s">
+      <c r="A9" s="181" t="s">
         <v>2</v>
       </c>
-      <c r="B9" s="206">
-        <v>46100</v>
-      </c>
-      <c r="C9" s="11"/>
+      <c r="B9" s="178">
+        <v>46128</v>
+      </c>
+      <c r="C9" s="11" t="s">
+        <v>100</v>
+      </c>
       <c r="D9" s="12"/>
-      <c r="E9" s="131"/>
-      <c r="F9" s="132"/>
-      <c r="G9" s="133"/>
-      <c r="H9" s="133"/>
-      <c r="I9" s="133"/>
-      <c r="J9" s="44"/>
+      <c r="E9" s="199" t="s">
+        <v>107</v>
+      </c>
+      <c r="F9" s="129"/>
+      <c r="G9" s="129"/>
+      <c r="H9" s="130" t="s">
+        <v>208</v>
+      </c>
+      <c r="I9" s="130"/>
+      <c r="J9" s="44" t="s">
+        <v>98</v>
+      </c>
       <c r="K9" s="19"/>
-      <c r="L9" s="101"/>
+      <c r="L9" s="198"/>
       <c r="M9" s="32" t="s">
-        <v>81</v>
-      </c>
-      <c r="N9" s="2" t="s">
-        <v>61</v>
+        <v>111</v>
+      </c>
+      <c r="N9" s="66" t="s">
+        <v>44</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A10" s="56"/>
-      <c r="B10" s="207"/>
+      <c r="B10" s="179"/>
       <c r="C10" s="14" t="s">
-        <v>211</v>
-      </c>
-      <c r="D10" s="128"/>
-      <c r="E10" s="190" t="s">
-        <v>212</v>
+        <v>73</v>
+      </c>
+      <c r="D10" s="125"/>
+      <c r="E10" s="166" t="s">
+        <v>97</v>
       </c>
       <c r="F10" s="83"/>
-      <c r="G10" s="67"/>
-      <c r="H10" s="67"/>
-      <c r="I10" s="67" t="s">
-        <v>235</v>
-      </c>
+      <c r="G10" s="83"/>
+      <c r="H10" s="67" t="s">
+        <v>209</v>
+      </c>
+      <c r="I10" s="67"/>
       <c r="J10" s="45" t="s">
-        <v>213</v>
-      </c>
-      <c r="K10" s="191">
-        <v>2.8</v>
-      </c>
-      <c r="L10" s="2" t="s">
-        <v>214</v>
+        <v>98</v>
+      </c>
+      <c r="K10" s="167" t="s">
+        <v>99</v>
       </c>
       <c r="M10" s="22" t="s">
-        <v>132</v>
+        <v>113</v>
       </c>
       <c r="N10" s="22" t="s">
-        <v>62</v>
+        <v>46</v>
       </c>
     </row>
     <row r="11" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="56"/>
-      <c r="B11" s="210"/>
+      <c r="B11" s="182"/>
       <c r="C11" s="14"/>
-      <c r="D11" s="128"/>
+      <c r="D11" s="125"/>
       <c r="E11" s="26"/>
-      <c r="F11" s="130"/>
-      <c r="G11" s="37"/>
+      <c r="F11" s="127"/>
+      <c r="G11" s="127"/>
       <c r="H11" s="37"/>
       <c r="I11" s="37"/>
       <c r="J11" s="40"/>
       <c r="K11" s="26"/>
       <c r="L11" s="26"/>
       <c r="M11" s="32" t="s">
-        <v>82</v>
+        <v>42</v>
       </c>
       <c r="N11" s="22" t="s">
-        <v>63</v>
+        <v>48</v>
       </c>
     </row>
     <row r="12" spans="1:14" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A12" s="41"/>
-      <c r="B12" s="208"/>
-      <c r="C12" s="16" t="s">
-        <v>3</v>
-      </c>
-      <c r="D12" s="184"/>
+      <c r="B12" s="180"/>
+      <c r="C12" s="17" t="s">
+        <v>109</v>
+      </c>
+      <c r="D12" s="220"/>
       <c r="E12" s="226" t="s">
-        <v>135</v>
-      </c>
-      <c r="F12" s="134" t="s">
-        <v>35</v>
-      </c>
-      <c r="G12" s="40"/>
-      <c r="H12" s="183" t="s">
-        <v>170</v>
-      </c>
-      <c r="I12" s="78" t="s">
-        <v>172</v>
-      </c>
+        <v>174</v>
+      </c>
+      <c r="F12" s="131" t="s">
+        <v>32</v>
+      </c>
+      <c r="G12" s="131"/>
+      <c r="H12" s="231" t="s">
+        <v>210</v>
+      </c>
+      <c r="I12" s="78"/>
       <c r="J12" s="43" t="s">
-        <v>242</v>
+        <v>173</v>
       </c>
       <c r="K12" s="18"/>
-      <c r="L12" s="100"/>
+      <c r="L12" s="18"/>
       <c r="M12" s="22" t="s">
-        <v>83</v>
+        <v>114</v>
       </c>
       <c r="N12" s="22" t="s">
-        <v>64</v>
+        <v>52</v>
       </c>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A13" s="209" t="s">
+      <c r="A13" s="181" t="s">
         <v>4</v>
       </c>
-      <c r="B13" s="206">
-        <v>46101</v>
+      <c r="B13" s="178">
+        <v>46129</v>
       </c>
       <c r="C13" s="11" t="s">
-        <v>215</v>
+        <v>100</v>
       </c>
       <c r="D13" s="12"/>
-      <c r="E13" s="194" t="s">
-        <v>216</v>
-      </c>
-      <c r="F13" s="135"/>
-      <c r="G13" s="24"/>
+      <c r="E13" s="202" t="s">
+        <v>108</v>
+      </c>
+      <c r="F13" s="132"/>
+      <c r="G13" s="235"/>
       <c r="H13" t="s">
-        <v>236</v>
-      </c>
-      <c r="I13"/>
+        <v>211</v>
+      </c>
+      <c r="I13" s="31"/>
       <c r="J13" s="46" t="s">
-        <v>217</v>
-      </c>
-      <c r="K13" s="191">
-        <v>2.8</v>
-      </c>
-      <c r="L13" s="24" t="s">
-        <v>218</v>
-      </c>
+        <v>98</v>
+      </c>
+      <c r="K13" s="167"/>
+      <c r="L13" s="24"/>
       <c r="M13" s="20" t="s">
-        <v>84</v>
-      </c>
-      <c r="N13" s="27" t="s">
-        <v>65</v>
+        <v>115</v>
+      </c>
+      <c r="N13" s="22" t="s">
+        <v>53</v>
       </c>
     </row>
     <row r="14" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="25"/>
-      <c r="B14" s="210"/>
+      <c r="B14" s="182"/>
       <c r="C14" s="14" t="s">
         <v>12</v>
       </c>
-      <c r="D14" s="185"/>
-      <c r="E14" s="226" t="s">
-        <v>42</v>
-      </c>
-      <c r="F14" s="136"/>
-      <c r="G14" s="32"/>
+      <c r="D14" s="125"/>
+      <c r="E14" s="26" t="s">
+        <v>54</v>
+      </c>
+      <c r="F14" s="133"/>
+      <c r="G14" s="236"/>
       <c r="H14" t="s">
-        <v>196</v>
-      </c>
-      <c r="I14" s="54"/>
+        <v>212</v>
+      </c>
+      <c r="I14" s="157"/>
       <c r="J14" s="40" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="K14" s="26" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="L14" s="23"/>
       <c r="M14" s="22" t="s">
-        <v>85</v>
-      </c>
-      <c r="N14" s="22" t="s">
-        <v>66</v>
+        <v>116</v>
+      </c>
+      <c r="N14" s="61" t="s">
+        <v>57</v>
       </c>
     </row>
     <row r="15" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="27"/>
-      <c r="B15" s="210"/>
+      <c r="B15" s="182"/>
       <c r="C15" s="14"/>
-      <c r="D15" s="128"/>
+      <c r="D15" s="125"/>
       <c r="E15" s="26"/>
-      <c r="F15" s="134"/>
-      <c r="G15" s="40"/>
+      <c r="F15" s="131"/>
+      <c r="G15" s="131"/>
       <c r="H15" s="40"/>
       <c r="I15" s="40"/>
       <c r="J15" s="40"/>
       <c r="K15" s="26"/>
       <c r="L15" s="23"/>
       <c r="M15" s="56" t="s">
-        <v>86</v>
-      </c>
-      <c r="N15" s="22" t="s">
-        <v>67</v>
+        <v>117</v>
+      </c>
+      <c r="N15" s="61" t="s">
+        <v>69</v>
       </c>
     </row>
     <row r="16" spans="1:14" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A16" s="41"/>
-      <c r="B16" s="208"/>
+      <c r="B16" s="180"/>
       <c r="C16" s="16" t="s">
         <v>3</v>
       </c>
-      <c r="D16" s="17"/>
-      <c r="E16" s="179" t="s">
-        <v>128</v>
-      </c>
-      <c r="F16" s="134" t="s">
-        <v>35</v>
-      </c>
-      <c r="G16" s="78"/>
-      <c r="H16" s="180" t="s">
-        <v>129</v>
-      </c>
-      <c r="I16" s="40" t="s">
+      <c r="D16" s="220"/>
+      <c r="E16" s="22" t="s">
+        <v>175</v>
+      </c>
+      <c r="F16" s="131" t="s">
+        <v>32</v>
+      </c>
+      <c r="G16" s="163"/>
+      <c r="H16" s="232" t="s">
+        <v>213</v>
+      </c>
+      <c r="I16" s="40"/>
+      <c r="J16" s="97" t="s">
         <v>173</v>
-      </c>
-      <c r="J16" s="181" t="s">
-        <v>130</v>
       </c>
       <c r="K16" s="77"/>
       <c r="L16" s="100"/>
       <c r="M16" s="21" t="s">
-        <v>87</v>
-      </c>
-      <c r="N16" s="22" t="s">
-        <v>68</v>
+        <v>118</v>
+      </c>
+      <c r="N16" s="26" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A17" s="209" t="s">
         <v>5</v>
       </c>
-      <c r="B17" s="206">
-        <v>46102</v>
+      <c r="B17" s="210">
+        <v>46130</v>
       </c>
       <c r="C17" s="11"/>
       <c r="D17" s="12"/>
-      <c r="E17" s="137"/>
-      <c r="F17" s="138"/>
-      <c r="G17" s="139"/>
-      <c r="H17" s="139"/>
-      <c r="I17" s="139"/>
+      <c r="E17" s="188"/>
+      <c r="F17" s="134"/>
+      <c r="G17" s="134"/>
+      <c r="H17" s="135"/>
+      <c r="I17" s="135"/>
       <c r="J17" s="42"/>
-      <c r="K17" s="126"/>
+      <c r="K17" s="123"/>
       <c r="L17" s="13"/>
-      <c r="M17" s="57" t="s">
-        <v>88</v>
+      <c r="M17" s="2" t="s">
+        <v>166</v>
       </c>
       <c r="N17" s="22" t="s">
-        <v>69</v>
+        <v>58</v>
       </c>
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A18" s="56"/>
-      <c r="B18" s="207"/>
+      <c r="A18" s="211"/>
+      <c r="B18" s="218"/>
       <c r="C18" s="14" t="s">
-        <v>27</v>
-      </c>
-      <c r="D18" s="128"/>
-      <c r="E18" s="21" t="s">
-        <v>137</v>
-      </c>
-      <c r="F18" s="130"/>
-      <c r="G18" s="37"/>
+        <v>167</v>
+      </c>
+      <c r="D18" s="125"/>
+      <c r="E18" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="F18" s="127"/>
+      <c r="G18" s="127"/>
       <c r="H18" s="25" t="s">
-        <v>174</v>
+        <v>214</v>
       </c>
       <c r="I18" s="37"/>
       <c r="J18" s="45" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="K18" s="15" t="s">
-        <v>136</v>
+        <v>70</v>
       </c>
       <c r="L18" s="15"/>
-      <c r="M18" s="27" t="s">
-        <v>89</v>
+      <c r="M18" s="57" t="s">
+        <v>119</v>
       </c>
       <c r="N18" s="22" t="s">
-        <v>70</v>
+        <v>59</v>
       </c>
     </row>
     <row r="19" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="56"/>
-      <c r="B19" s="210"/>
+      <c r="A19" s="211"/>
+      <c r="B19" s="212"/>
       <c r="C19" s="14" t="s">
         <v>6</v>
       </c>
-      <c r="D19" s="185"/>
-      <c r="E19" s="226" t="s">
-        <v>139</v>
+      <c r="D19" s="222" t="s">
+        <v>236</v>
+      </c>
+      <c r="E19" s="22" t="s">
+        <v>181</v>
       </c>
       <c r="F19" s="83"/>
-      <c r="G19" s="67"/>
+      <c r="G19" s="83"/>
       <c r="H19" s="67" t="s">
-        <v>175</v>
-      </c>
-      <c r="I19" s="67" t="s">
-        <v>138</v>
-      </c>
-      <c r="J19" s="38" t="s">
-        <v>46</v>
+        <v>215</v>
+      </c>
+      <c r="I19" s="67"/>
+      <c r="J19" s="230" t="s">
+        <v>180</v>
       </c>
       <c r="K19" s="15" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="L19" s="15"/>
       <c r="M19" s="22" t="s">
-        <v>90</v>
-      </c>
-      <c r="N19" s="66" t="s">
-        <v>71</v>
+        <v>120</v>
+      </c>
+      <c r="N19" s="121" t="s">
+        <v>60</v>
       </c>
     </row>
     <row r="20" spans="1:14" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="41"/>
-      <c r="B20" s="208"/>
-      <c r="C20" s="16" t="s">
-        <v>3</v>
-      </c>
-      <c r="D20" s="184"/>
-      <c r="E20" s="182" t="s">
-        <v>140</v>
-      </c>
-      <c r="F20" s="130" t="s">
-        <v>35</v>
-      </c>
-      <c r="G20" s="37"/>
+      <c r="A20" s="213"/>
+      <c r="B20" s="214"/>
+      <c r="C20" s="17" t="s">
+        <v>169</v>
+      </c>
+      <c r="D20" s="220" t="s">
+        <v>235</v>
+      </c>
+      <c r="E20" s="208" t="s">
+        <v>111</v>
+      </c>
+      <c r="F20" s="127"/>
+      <c r="G20" s="127"/>
       <c r="H20" s="37" t="s">
+        <v>216</v>
+      </c>
+      <c r="I20" s="37"/>
+      <c r="J20" s="47" t="s">
         <v>176</v>
       </c>
-      <c r="I20" s="37" t="s">
-        <v>168</v>
-      </c>
-      <c r="J20" s="47" t="s">
-        <v>242</v>
-      </c>
       <c r="K20" s="18"/>
-      <c r="L20" s="110"/>
+      <c r="L20" s="108"/>
       <c r="M20" s="20"/>
       <c r="N20" s="22" t="s">
-        <v>72</v>
+        <v>61</v>
       </c>
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A21" s="209" t="s">
         <v>7</v>
       </c>
-      <c r="B21" s="206">
-        <v>46103</v>
+      <c r="B21" s="210">
+        <v>46131</v>
       </c>
       <c r="C21" s="28"/>
       <c r="D21" s="29"/>
       <c r="E21" s="20"/>
-      <c r="F21" s="127"/>
-      <c r="G21" s="42"/>
+      <c r="F21" s="124"/>
+      <c r="G21" s="124"/>
       <c r="H21" s="42"/>
       <c r="I21" s="42"/>
       <c r="J21" s="48"/>
       <c r="K21" s="13"/>
-      <c r="L21" s="148"/>
+      <c r="L21" s="143"/>
       <c r="M21" s="26"/>
-      <c r="N21" s="123" t="s">
-        <v>74</v>
+      <c r="N21" s="195" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="22" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="56"/>
-      <c r="B22" s="207"/>
+      <c r="A22" s="211"/>
+      <c r="B22" s="218"/>
       <c r="C22" s="14" t="s">
-        <v>12</v>
-      </c>
-      <c r="D22" s="128"/>
+        <v>11</v>
+      </c>
+      <c r="D22" s="125"/>
       <c r="E22" s="22" t="s">
-        <v>142</v>
-      </c>
-      <c r="F22" s="130"/>
-      <c r="G22" s="37"/>
+        <v>183</v>
+      </c>
+      <c r="F22" s="127"/>
+      <c r="G22" s="127"/>
       <c r="H22" s="37" t="s">
-        <v>177</v>
+        <v>217</v>
       </c>
       <c r="I22" s="37"/>
       <c r="J22" s="45" t="s">
-        <v>141</v>
+        <v>75</v>
       </c>
       <c r="K22" s="15"/>
       <c r="L22" s="21"/>
       <c r="M22" s="27"/>
       <c r="N22" s="22" t="s">
-        <v>75</v>
+        <v>64</v>
       </c>
     </row>
     <row r="23" spans="1:14" ht="13.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="56"/>
-      <c r="B23" s="210"/>
+      <c r="A23" s="211"/>
+      <c r="B23" s="212"/>
       <c r="C23" s="14" t="s">
-        <v>27</v>
-      </c>
-      <c r="D23" s="128"/>
-      <c r="E23" s="22" t="s">
-        <v>83</v>
-      </c>
-      <c r="F23" s="130"/>
-      <c r="G23" s="37"/>
+        <v>6</v>
+      </c>
+      <c r="D23" s="125"/>
+      <c r="E23" s="226" t="s">
+        <v>85</v>
+      </c>
+      <c r="F23" s="127"/>
+      <c r="G23" s="127"/>
       <c r="H23" s="37" t="s">
-        <v>178</v>
+        <v>218</v>
       </c>
       <c r="I23" s="37"/>
-      <c r="J23" s="45"/>
+      <c r="J23" s="45" t="s">
+        <v>173</v>
+      </c>
       <c r="K23" s="15"/>
       <c r="L23" s="27"/>
       <c r="M23" s="56"/>
-      <c r="N23" s="124" t="s">
-        <v>76</v>
+      <c r="N23" s="22" t="s">
+        <v>65</v>
       </c>
     </row>
     <row r="24" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="41"/>
-      <c r="B24" s="208"/>
+      <c r="A24" s="213"/>
+      <c r="B24" s="214"/>
       <c r="C24" s="17"/>
       <c r="D24" s="17"/>
       <c r="E24" s="26"/>
-      <c r="F24" s="141"/>
-      <c r="G24" s="142"/>
-      <c r="H24" s="143"/>
-      <c r="I24" s="143"/>
+      <c r="F24" s="137"/>
+      <c r="G24" s="237"/>
+      <c r="H24" s="138"/>
+      <c r="I24" s="138"/>
       <c r="J24" s="39"/>
       <c r="K24" s="78"/>
       <c r="L24" s="78"/>
       <c r="M24" s="22"/>
-      <c r="N24" s="61" t="s">
-        <v>77</v>
+      <c r="N24" s="196" t="s">
+        <v>66</v>
       </c>
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A25" s="209" t="s">
         <v>8</v>
       </c>
-      <c r="B25" s="206">
-        <v>46104</v>
-      </c>
-      <c r="C25" s="11" t="s">
-        <v>215</v>
-      </c>
+      <c r="B25" s="210">
+        <v>46132</v>
+      </c>
+      <c r="C25" s="11"/>
       <c r="D25" s="12"/>
-      <c r="E25" s="195" t="s">
-        <v>219</v>
-      </c>
-      <c r="F25" s="144"/>
-      <c r="G25" s="19"/>
-      <c r="H25" t="s">
-        <v>237</v>
-      </c>
+      <c r="E25" s="19"/>
+      <c r="F25" s="139"/>
+      <c r="G25" s="238"/>
+      <c r="H25"/>
       <c r="I25" s="44"/>
-      <c r="J25" s="44" t="s">
-        <v>225</v>
-      </c>
-      <c r="K25" s="196">
-        <v>4</v>
-      </c>
-      <c r="L25" s="19" t="s">
-        <v>221</v>
-      </c>
+      <c r="J25" s="44"/>
+      <c r="K25" s="171"/>
+      <c r="L25" s="19"/>
       <c r="M25" s="26"/>
-      <c r="N25" s="123" t="s">
-        <v>78</v>
+      <c r="N25" s="61" t="s">
+        <v>62</v>
       </c>
     </row>
     <row r="26" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="110"/>
-      <c r="B26" s="211"/>
+      <c r="A26" s="215"/>
+      <c r="B26" s="216"/>
       <c r="C26" s="16"/>
       <c r="D26" s="17"/>
       <c r="E26" s="18"/>
-      <c r="F26" s="145"/>
-      <c r="G26" s="43"/>
+      <c r="F26" s="140"/>
+      <c r="G26" s="140"/>
       <c r="H26" s="43"/>
       <c r="I26" s="43"/>
       <c r="J26" s="43"/>
-      <c r="K26" s="119"/>
+      <c r="K26" s="116"/>
       <c r="L26" s="18"/>
       <c r="M26" s="26"/>
-      <c r="N26" s="118" t="s">
-        <v>79</v>
+      <c r="N26" s="27" t="s">
+        <v>78</v>
       </c>
     </row>
     <row r="27" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="31" t="s">
+      <c r="A27" s="217" t="s">
         <v>9</v>
       </c>
-      <c r="B27" s="206">
-        <v>46105</v>
+      <c r="B27" s="210">
+        <v>46133</v>
       </c>
       <c r="C27" s="11"/>
       <c r="D27" s="12"/>
-      <c r="E27" s="13"/>
-      <c r="F27" s="127"/>
-      <c r="G27" s="42"/>
+      <c r="E27" s="200"/>
+      <c r="F27" s="124"/>
+      <c r="G27" s="124"/>
       <c r="H27" s="42"/>
       <c r="I27" s="42"/>
       <c r="J27" s="46"/>
       <c r="K27" s="24"/>
       <c r="L27" s="24"/>
       <c r="M27" s="22"/>
-      <c r="N27" s="26"/>
+      <c r="N27" s="26" t="s">
+        <v>54</v>
+      </c>
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A28" s="56"/>
-      <c r="B28" s="207"/>
+      <c r="A28" s="211"/>
+      <c r="B28" s="218"/>
       <c r="C28" s="14"/>
-      <c r="D28" s="128"/>
-      <c r="E28" s="26"/>
-      <c r="F28" s="146"/>
-      <c r="G28" s="147"/>
-      <c r="H28" s="147"/>
-      <c r="I28" s="147"/>
-      <c r="J28" s="45"/>
+      <c r="D28" s="125"/>
+      <c r="E28" s="201"/>
+      <c r="F28" s="141"/>
+      <c r="G28" s="141"/>
+      <c r="H28" s="142"/>
+      <c r="I28" s="142"/>
+      <c r="J28" s="45" t="s">
+        <v>26</v>
+      </c>
       <c r="K28" s="15"/>
       <c r="L28" s="21"/>
       <c r="M28" s="22"/>
-      <c r="N28" s="22"/>
+      <c r="N28" s="66" t="s">
+        <v>80</v>
+      </c>
     </row>
     <row r="29" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="56"/>
-      <c r="B29" s="210"/>
+      <c r="A29" s="211"/>
+      <c r="B29" s="212"/>
       <c r="C29" s="14"/>
-      <c r="D29" s="128"/>
+      <c r="D29" s="125"/>
       <c r="E29" s="15"/>
-      <c r="F29" s="129"/>
-      <c r="G29" s="38"/>
+      <c r="F29" s="126"/>
+      <c r="G29" s="126"/>
       <c r="H29" s="38"/>
       <c r="I29" s="38"/>
       <c r="J29" s="49"/>
-      <c r="K29" s="193"/>
+      <c r="K29" s="169"/>
       <c r="L29" s="79"/>
       <c r="M29" s="27"/>
-      <c r="N29" s="22"/>
+      <c r="N29" s="66" t="s">
+        <v>81</v>
+      </c>
     </row>
     <row r="30" spans="1:14" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="41"/>
-      <c r="B30" s="208"/>
+      <c r="A30" s="213"/>
+      <c r="B30" s="214"/>
       <c r="C30" s="16" t="s">
         <v>3</v>
       </c>
-      <c r="D30" s="184"/>
-      <c r="E30" s="22" t="s">
-        <v>144</v>
-      </c>
-      <c r="F30" s="134" t="s">
-        <v>143</v>
-      </c>
-      <c r="G30" s="40"/>
+      <c r="D30" s="17"/>
+      <c r="E30" s="20" t="s">
+        <v>115</v>
+      </c>
+      <c r="F30" s="131"/>
+      <c r="G30" s="131" t="s">
+        <v>205</v>
+      </c>
       <c r="H30" s="40" t="s">
+        <v>219</v>
+      </c>
+      <c r="I30" s="40" t="s">
         <v>179</v>
       </c>
-      <c r="I30" s="40"/>
-      <c r="J30" s="43"/>
+      <c r="J30" s="43" t="s">
+        <v>173</v>
+      </c>
       <c r="K30" s="18"/>
       <c r="L30" s="100"/>
       <c r="M30" s="58"/>
-      <c r="N30" s="22"/>
+      <c r="N30" s="22" t="s">
+        <v>82</v>
+      </c>
     </row>
     <row r="31" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="203" t="s">
+      <c r="A31" s="175" t="s">
         <v>0</v>
       </c>
-      <c r="B31" s="212">
-        <v>46106</v>
+      <c r="B31" s="184">
+        <v>46134</v>
       </c>
       <c r="C31" s="7"/>
       <c r="D31" s="8"/>
       <c r="E31" s="9"/>
       <c r="F31" s="84"/>
-      <c r="G31" s="68"/>
+      <c r="G31" s="84"/>
       <c r="H31" s="68"/>
       <c r="I31" s="68"/>
       <c r="J31" s="50"/>
       <c r="K31" s="10"/>
       <c r="L31" s="10"/>
       <c r="M31" s="59">
-        <v>46078</v>
-      </c>
-      <c r="N31" s="61"/>
+        <v>46106</v>
+      </c>
+      <c r="N31" s="120" t="s">
+        <v>83</v>
+      </c>
     </row>
     <row r="32" spans="1:14" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="209" t="s">
         <v>1</v>
       </c>
-      <c r="B32" s="206">
-        <v>46106</v>
+      <c r="B32" s="210">
+        <v>46134</v>
       </c>
       <c r="C32" s="12"/>
       <c r="D32" s="12"/>
       <c r="E32" s="13"/>
-      <c r="F32" s="127"/>
-      <c r="G32" s="42"/>
+      <c r="F32" s="124"/>
+      <c r="G32" s="124"/>
       <c r="H32" s="42"/>
       <c r="I32" s="42"/>
       <c r="J32" s="51"/>
       <c r="K32" s="34"/>
       <c r="L32" s="34"/>
       <c r="M32" s="55" t="s">
-        <v>43</v>
+        <v>143</v>
       </c>
       <c r="N32" s="25"/>
     </row>
     <row r="33" spans="1:15" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="56"/>
-      <c r="B33" s="210"/>
-      <c r="C33" s="14"/>
-      <c r="D33" s="128"/>
-      <c r="E33" s="32"/>
-      <c r="F33" s="136"/>
-      <c r="G33" s="54"/>
-      <c r="H33" s="54"/>
+      <c r="A33" s="211"/>
+      <c r="B33" s="212"/>
+      <c r="C33" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="D33" s="125"/>
+      <c r="E33" s="22" t="s">
+        <v>177</v>
+      </c>
+      <c r="F33" s="133"/>
+      <c r="G33" s="133"/>
+      <c r="H33" s="54" t="s">
+        <v>220</v>
+      </c>
       <c r="I33" s="54"/>
-      <c r="J33" s="40"/>
+      <c r="J33" s="40" t="s">
+        <v>26</v>
+      </c>
       <c r="K33" s="26"/>
       <c r="L33" s="26"/>
       <c r="M33" s="55" t="s">
-        <v>52</v>
+        <v>87</v>
       </c>
       <c r="N33" s="64" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="34" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="56"/>
-      <c r="B34" s="210"/>
+      <c r="A34" s="211"/>
+      <c r="B34" s="212"/>
       <c r="C34" s="14"/>
-      <c r="D34" s="128"/>
+      <c r="D34" s="125"/>
       <c r="E34" s="15"/>
-      <c r="F34" s="129"/>
-      <c r="G34" s="38"/>
+      <c r="F34" s="126"/>
+      <c r="G34" s="126"/>
       <c r="H34" s="38"/>
       <c r="I34" s="38"/>
       <c r="J34" s="52"/>
       <c r="K34" s="27"/>
       <c r="L34" s="27"/>
       <c r="M34" s="60" t="s">
-        <v>53</v>
-      </c>
-      <c r="N34" s="177"/>
+        <v>88</v>
+      </c>
+      <c r="N34" s="26" t="s">
+        <v>36</v>
+      </c>
     </row>
     <row r="35" spans="1:15" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="41"/>
-      <c r="B35" s="208"/>
+      <c r="A35" s="213"/>
+      <c r="B35" s="214"/>
       <c r="C35" s="16" t="s">
         <v>3</v>
       </c>
-      <c r="D35" s="149"/>
-      <c r="E35" s="229" t="s">
-        <v>145</v>
-      </c>
-      <c r="F35" s="134"/>
-      <c r="G35" s="40"/>
+      <c r="D35" s="221"/>
+      <c r="E35" s="22" t="s">
+        <v>178</v>
+      </c>
+      <c r="F35" s="131" t="s">
+        <v>32</v>
+      </c>
+      <c r="G35" s="131"/>
       <c r="H35" s="40" t="s">
-        <v>180</v>
-      </c>
-      <c r="I35" s="40"/>
+        <v>221</v>
+      </c>
+      <c r="I35" s="229" t="s">
+        <v>185</v>
+      </c>
       <c r="J35" s="97" t="s">
-        <v>243</v>
+        <v>176</v>
       </c>
       <c r="K35" s="77"/>
       <c r="L35" s="77"/>
-      <c r="M35" s="22" t="s">
-        <v>91</v>
-      </c>
-      <c r="N35" s="61"/>
+      <c r="M35" s="60" t="s">
+        <v>90</v>
+      </c>
+      <c r="N35" s="22" t="s">
+        <v>45</v>
+      </c>
     </row>
     <row r="36" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A36" s="209" t="s">
         <v>2</v>
       </c>
-      <c r="B36" s="206">
-        <v>46107</v>
-      </c>
-      <c r="C36" s="122"/>
+      <c r="B36" s="210">
+        <v>46135</v>
+      </c>
+      <c r="C36" s="119"/>
       <c r="D36" s="12"/>
       <c r="E36" s="13"/>
-      <c r="F36" s="127"/>
-      <c r="G36" s="42"/>
+      <c r="F36" s="124"/>
+      <c r="G36" s="124"/>
       <c r="H36" s="42"/>
       <c r="I36" s="42"/>
       <c r="J36" s="53"/>
       <c r="K36" s="80"/>
       <c r="L36" s="80"/>
-      <c r="M36" s="22" t="s">
-        <v>92</v>
-      </c>
-      <c r="N36" s="25"/>
+      <c r="M36" s="196" t="s">
+        <v>121</v>
+      </c>
+      <c r="N36" s="61" t="s">
+        <v>50</v>
+      </c>
     </row>
     <row r="37" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="56"/>
-      <c r="B37" s="210"/>
-      <c r="C37" s="35"/>
-      <c r="D37" s="128"/>
-      <c r="E37" s="22"/>
-      <c r="F37" s="130"/>
-      <c r="G37" s="37"/>
-      <c r="H37" s="37"/>
+      <c r="A37" s="211"/>
+      <c r="B37" s="212"/>
+      <c r="C37" s="35" t="s">
+        <v>11</v>
+      </c>
+      <c r="D37" s="222"/>
+      <c r="E37" s="22" t="s">
+        <v>181</v>
+      </c>
+      <c r="F37" s="127"/>
+      <c r="G37" s="127"/>
+      <c r="H37" s="67" t="s">
+        <v>215</v>
+      </c>
       <c r="I37" s="37"/>
-      <c r="J37" s="54"/>
+      <c r="J37" s="54" t="s">
+        <v>184</v>
+      </c>
       <c r="K37" s="32"/>
       <c r="L37" s="32"/>
       <c r="M37" s="22" t="s">
-        <v>93</v>
-      </c>
-      <c r="N37" s="61"/>
+        <v>122</v>
+      </c>
+      <c r="N37" s="22" t="s">
+        <v>55</v>
+      </c>
     </row>
     <row r="38" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="56"/>
-      <c r="B38" s="210"/>
+      <c r="A38" s="211"/>
+      <c r="B38" s="212"/>
       <c r="C38" s="35"/>
-      <c r="D38" s="128"/>
+      <c r="D38" s="125"/>
       <c r="E38" s="27"/>
-      <c r="F38" s="150"/>
-      <c r="G38" s="52"/>
+      <c r="F38" s="144"/>
+      <c r="G38" s="144"/>
       <c r="H38" s="52"/>
       <c r="I38" s="52"/>
       <c r="J38" s="54"/>
       <c r="K38" s="32"/>
       <c r="L38" s="32"/>
       <c r="M38" s="26" t="s">
-        <v>94</v>
-      </c>
-      <c r="N38" s="26"/>
+        <v>124</v>
+      </c>
+      <c r="N38" s="196" t="s">
+        <v>56</v>
+      </c>
     </row>
     <row r="39" spans="1:15" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="41"/>
-      <c r="B39" s="208"/>
+      <c r="A39" s="213"/>
+      <c r="B39" s="214"/>
       <c r="C39" s="16" t="s">
         <v>3</v>
       </c>
       <c r="D39" s="17"/>
       <c r="E39" s="226" t="s">
-        <v>146</v>
-      </c>
-      <c r="F39" s="134" t="s">
-        <v>35</v>
-      </c>
-      <c r="G39" s="40"/>
-      <c r="H39" s="183" t="s">
-        <v>181</v>
-      </c>
-      <c r="I39" s="40"/>
+        <v>259</v>
+      </c>
+      <c r="F39" s="131" t="s">
+        <v>32</v>
+      </c>
+      <c r="G39" s="131"/>
+      <c r="H39" s="231" t="s">
+        <v>222</v>
+      </c>
+      <c r="I39" s="40" t="s">
+        <v>258</v>
+      </c>
       <c r="J39" s="97" t="s">
-        <v>244</v>
+        <v>173</v>
       </c>
       <c r="K39" s="77"/>
       <c r="L39" s="77"/>
-      <c r="M39" s="22" t="s">
-        <v>95</v>
+      <c r="M39" s="196" t="s">
+        <v>123</v>
       </c>
       <c r="N39" s="25"/>
     </row>
@@ -3159,88 +3305,86 @@
       <c r="A40" s="209" t="s">
         <v>4</v>
       </c>
-      <c r="B40" s="206">
-        <v>46108</v>
+      <c r="B40" s="210">
+        <v>46136</v>
       </c>
       <c r="C40" s="36"/>
       <c r="D40" s="12"/>
-      <c r="E40" s="131"/>
-      <c r="F40" s="132"/>
-      <c r="G40" s="133"/>
-      <c r="H40" s="133"/>
-      <c r="I40" s="133"/>
+      <c r="E40" s="128"/>
+      <c r="F40" s="129"/>
+      <c r="G40" s="129"/>
+      <c r="H40" s="130"/>
+      <c r="I40" s="130"/>
       <c r="J40" s="53"/>
-      <c r="K40" s="120"/>
+      <c r="K40" s="117"/>
       <c r="L40" s="80"/>
-      <c r="M40" s="178" t="s">
-        <v>96</v>
+      <c r="M40" s="22" t="s">
+        <v>125</v>
       </c>
       <c r="N40" s="65"/>
     </row>
     <row r="41" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="56"/>
-      <c r="B41" s="210"/>
+      <c r="A41" s="211"/>
+      <c r="B41" s="212"/>
       <c r="C41" s="35"/>
-      <c r="D41" s="128"/>
+      <c r="D41" s="125"/>
       <c r="E41" s="26"/>
-      <c r="F41" s="136"/>
-      <c r="G41" s="54"/>
+      <c r="F41" s="133"/>
+      <c r="G41" s="133"/>
       <c r="H41" s="54"/>
       <c r="I41" s="54"/>
       <c r="J41" s="40"/>
       <c r="K41" s="26"/>
       <c r="L41" s="26"/>
-      <c r="M41" s="22" t="s">
-        <v>50</v>
+      <c r="M41" s="66" t="s">
+        <v>126</v>
       </c>
       <c r="N41" s="61"/>
     </row>
     <row r="42" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="56"/>
-      <c r="B42" s="210"/>
+      <c r="A42" s="211"/>
+      <c r="B42" s="212"/>
       <c r="C42" s="14"/>
-      <c r="D42" s="128"/>
+      <c r="D42" s="125"/>
       <c r="E42" s="15"/>
-      <c r="F42" s="129"/>
-      <c r="G42" s="38"/>
+      <c r="F42" s="126"/>
+      <c r="G42" s="126"/>
       <c r="H42" s="38"/>
       <c r="I42" s="15"/>
       <c r="J42" s="52"/>
       <c r="K42" s="27"/>
       <c r="L42" s="27"/>
       <c r="M42" s="22" t="s">
-        <v>98</v>
-      </c>
-      <c r="N42" s="177"/>
+        <v>127</v>
+      </c>
+      <c r="N42" s="164"/>
       <c r="O42" s="5"/>
     </row>
     <row r="43" spans="1:15" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A43" s="41"/>
-      <c r="B43" s="208"/>
+      <c r="A43" s="213"/>
+      <c r="B43" s="214"/>
       <c r="C43" s="33" t="s">
         <v>3</v>
       </c>
-      <c r="D43" s="184"/>
-      <c r="E43" s="20" t="s">
-        <v>140</v>
-      </c>
-      <c r="F43" s="134" t="s">
-        <v>35</v>
-      </c>
-      <c r="G43" s="40"/>
+      <c r="D43" s="220" t="s">
+        <v>236</v>
+      </c>
+      <c r="E43" s="227" t="s">
+        <v>88</v>
+      </c>
+      <c r="F43" s="131"/>
+      <c r="G43" s="131" t="s">
+        <v>206</v>
+      </c>
       <c r="H43" s="37" t="s">
-        <v>176</v>
-      </c>
-      <c r="I43" s="40" t="s">
-        <v>168</v>
-      </c>
-      <c r="J43" s="97" t="s">
-        <v>242</v>
-      </c>
+        <v>223</v>
+      </c>
+      <c r="I43" s="40"/>
+      <c r="J43" s="97"/>
       <c r="K43" s="77"/>
       <c r="L43" s="99"/>
-      <c r="M43" s="22" t="s">
-        <v>99</v>
+      <c r="M43" s="66" t="s">
+        <v>128</v>
       </c>
       <c r="N43" s="22"/>
     </row>
@@ -3248,219 +3392,215 @@
       <c r="A44" s="209" t="s">
         <v>5</v>
       </c>
-      <c r="B44" s="206">
-        <v>46109</v>
+      <c r="B44" s="210">
+        <v>46137</v>
       </c>
       <c r="C44" s="11"/>
       <c r="D44" s="12"/>
-      <c r="E44" s="151"/>
-      <c r="F44" s="152"/>
-      <c r="G44" s="153"/>
-      <c r="H44" s="153"/>
-      <c r="I44" s="153"/>
+      <c r="E44" s="189"/>
+      <c r="F44" s="145"/>
+      <c r="G44" s="145"/>
+      <c r="H44" s="146"/>
+      <c r="I44" s="146"/>
       <c r="J44" s="46"/>
       <c r="K44" s="24"/>
       <c r="L44" s="24"/>
-      <c r="M44" s="178" t="s">
-        <v>100</v>
+      <c r="M44" s="22" t="s">
+        <v>129</v>
       </c>
       <c r="N44" s="26"/>
       <c r="O44" s="4"/>
     </row>
     <row r="45" spans="1:15" ht="13.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="56"/>
-      <c r="B45" s="210"/>
+      <c r="A45" s="211"/>
+      <c r="B45" s="212"/>
       <c r="C45" s="35" t="s">
-        <v>27</v>
-      </c>
-      <c r="D45" s="154"/>
+        <v>167</v>
+      </c>
+      <c r="D45" s="190"/>
       <c r="E45" s="27" t="s">
-        <v>183</v>
-      </c>
-      <c r="F45" s="155"/>
-      <c r="G45" s="156"/>
+        <v>189</v>
+      </c>
+      <c r="F45" s="147"/>
+      <c r="G45" s="147"/>
       <c r="H45" s="25" t="s">
-        <v>182</v>
-      </c>
-      <c r="I45" s="156"/>
+        <v>224</v>
+      </c>
+      <c r="I45" s="148"/>
       <c r="J45" s="45" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="K45" s="22" t="s">
-        <v>136</v>
+        <v>70</v>
       </c>
       <c r="L45" s="22"/>
       <c r="M45" s="26" t="s">
-        <v>102</v>
+        <v>130</v>
       </c>
       <c r="N45" s="61"/>
     </row>
     <row r="46" spans="1:15" ht="13.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="56"/>
-      <c r="B46" s="210"/>
+      <c r="A46" s="211"/>
+      <c r="B46" s="212"/>
       <c r="C46" s="35" t="s">
         <v>6</v>
       </c>
-      <c r="D46" s="154"/>
-      <c r="E46" s="27" t="s">
-        <v>149</v>
+      <c r="D46" s="190"/>
+      <c r="E46" s="22" t="s">
+        <v>188</v>
       </c>
       <c r="F46" s="83" t="s">
-        <v>35</v>
-      </c>
-      <c r="G46" s="67"/>
+        <v>32</v>
+      </c>
+      <c r="G46" s="83"/>
       <c r="H46" s="67" t="s">
-        <v>184</v>
+        <v>225</v>
       </c>
       <c r="I46" s="67"/>
       <c r="J46" s="38" t="s">
-        <v>44</v>
+        <v>76</v>
       </c>
       <c r="K46" s="15" t="s">
-        <v>45</v>
-      </c>
-      <c r="L46" s="15" t="s">
-        <v>147</v>
-      </c>
-      <c r="M46" s="123" t="s">
-        <v>101</v>
+        <v>38</v>
+      </c>
+      <c r="L46" s="15"/>
+      <c r="M46" s="219" t="s">
+        <v>132</v>
       </c>
       <c r="N46" s="61"/>
     </row>
     <row r="47" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A47" s="41"/>
-      <c r="B47" s="208"/>
+      <c r="A47" s="213"/>
+      <c r="B47" s="214"/>
       <c r="C47" s="16" t="s">
         <v>3</v>
       </c>
-      <c r="D47" s="184"/>
-      <c r="E47" s="32" t="s">
-        <v>81</v>
-      </c>
-      <c r="F47" s="157"/>
-      <c r="G47" s="99"/>
-      <c r="H47" s="158" t="s">
-        <v>185</v>
-      </c>
-      <c r="I47" s="159"/>
+      <c r="D47" s="17"/>
+      <c r="E47" s="20" t="s">
+        <v>186</v>
+      </c>
+      <c r="F47" s="149" t="s">
+        <v>187</v>
+      </c>
+      <c r="G47" s="239"/>
+      <c r="H47" s="150" t="s">
+        <v>226</v>
+      </c>
+      <c r="I47" s="151"/>
       <c r="J47" s="39"/>
       <c r="K47" s="78"/>
       <c r="L47" s="78"/>
       <c r="M47" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="N47" s="177"/>
+        <v>133</v>
+      </c>
+      <c r="N47" s="164"/>
     </row>
     <row r="48" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A48" s="209" t="s">
         <v>7</v>
       </c>
-      <c r="B48" s="206">
-        <v>46110</v>
-      </c>
-      <c r="C48" s="12" t="s">
-        <v>207</v>
-      </c>
+      <c r="B48" s="210">
+        <v>46138</v>
+      </c>
+      <c r="C48" s="12"/>
       <c r="D48" s="12"/>
-      <c r="E48" s="188" t="s">
-        <v>208</v>
-      </c>
-      <c r="F48" s="189"/>
-      <c r="G48" s="25"/>
-      <c r="H48" s="25" t="s">
-        <v>209</v>
-      </c>
-      <c r="I48" s="161"/>
-      <c r="J48" s="25" t="s">
-        <v>245</v>
-      </c>
-      <c r="K48" s="177"/>
-      <c r="L48" s="25" t="s">
-        <v>210</v>
-      </c>
+      <c r="E48" s="191"/>
+      <c r="F48" s="165"/>
+      <c r="G48" s="165"/>
+      <c r="H48" s="25"/>
+      <c r="I48" s="153"/>
+      <c r="J48" s="25"/>
+      <c r="K48" s="164"/>
+      <c r="L48" s="25"/>
       <c r="M48" s="61" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="N48" s="25"/>
     </row>
     <row r="49" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A49" s="56"/>
-      <c r="B49" s="210"/>
+      <c r="A49" s="211"/>
+      <c r="B49" s="212"/>
       <c r="C49" s="35" t="s">
         <v>11</v>
       </c>
-      <c r="D49" s="162"/>
-      <c r="E49" s="22" t="s">
-        <v>148</v>
+      <c r="D49" s="223"/>
+      <c r="E49" s="227" t="s">
+        <v>190</v>
       </c>
       <c r="F49" s="83"/>
-      <c r="G49" s="67"/>
+      <c r="G49" s="83"/>
       <c r="H49" s="67" t="s">
-        <v>186</v>
+        <v>227</v>
       </c>
       <c r="I49" s="67"/>
       <c r="J49" s="38" t="s">
-        <v>141</v>
+        <v>26</v>
       </c>
       <c r="K49" s="15"/>
       <c r="L49" s="15"/>
       <c r="M49" s="27" t="s">
-        <v>104</v>
+        <v>135</v>
       </c>
       <c r="N49" s="61"/>
     </row>
     <row r="50" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A50" s="56"/>
-      <c r="B50" s="210"/>
+      <c r="A50" s="211"/>
+      <c r="B50" s="212"/>
       <c r="C50" s="35" t="s">
         <v>6</v>
       </c>
-      <c r="D50" s="186"/>
+      <c r="D50" s="224" t="s">
+        <v>235</v>
+      </c>
       <c r="E50" s="22" t="s">
-        <v>91</v>
-      </c>
-      <c r="F50" s="130"/>
-      <c r="G50" s="37"/>
+        <v>121</v>
+      </c>
+      <c r="F50" s="127"/>
+      <c r="G50" s="127"/>
       <c r="H50" s="37" t="s">
-        <v>187</v>
+        <v>228</v>
       </c>
       <c r="I50" s="22"/>
       <c r="J50" s="98"/>
       <c r="K50" s="81"/>
       <c r="L50" s="81"/>
-      <c r="M50" s="22"/>
+      <c r="M50" s="2" t="s">
+        <v>137</v>
+      </c>
       <c r="N50" s="61"/>
     </row>
     <row r="51" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A51" s="41"/>
-      <c r="B51" s="208"/>
+      <c r="A51" s="213"/>
+      <c r="B51" s="214"/>
       <c r="C51" s="16"/>
       <c r="D51" s="17"/>
-      <c r="E51" s="140"/>
-      <c r="F51" s="163"/>
-      <c r="G51" s="140"/>
-      <c r="H51" s="140"/>
-      <c r="I51" s="140"/>
+      <c r="E51" s="136"/>
+      <c r="F51" s="154"/>
+      <c r="G51" s="154"/>
+      <c r="H51" s="136"/>
+      <c r="I51" s="136"/>
       <c r="J51" s="41"/>
-      <c r="K51" s="110"/>
+      <c r="K51" s="108"/>
       <c r="L51" s="41"/>
-      <c r="M51" s="26"/>
+      <c r="M51" s="22" t="s">
+        <v>136</v>
+      </c>
       <c r="N51" s="89" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="52" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A52" s="209" t="s">
         <v>8</v>
       </c>
-      <c r="B52" s="206">
-        <v>46111</v>
+      <c r="B52" s="210">
+        <v>46139</v>
       </c>
       <c r="C52" s="11"/>
       <c r="D52" s="12"/>
       <c r="E52" s="19"/>
-      <c r="F52" s="144"/>
-      <c r="G52" s="44"/>
+      <c r="F52" s="139"/>
+      <c r="G52" s="139"/>
       <c r="H52" s="44"/>
       <c r="I52" s="44"/>
       <c r="J52" s="44"/>
@@ -3472,13 +3612,13 @@
       </c>
     </row>
     <row r="53" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A53" s="110"/>
-      <c r="B53" s="211"/>
+      <c r="A53" s="215"/>
+      <c r="B53" s="216"/>
       <c r="C53" s="16"/>
       <c r="D53" s="17"/>
       <c r="E53" s="18"/>
-      <c r="F53" s="145"/>
-      <c r="G53" s="43"/>
+      <c r="F53" s="140"/>
+      <c r="G53" s="140"/>
       <c r="H53" s="43"/>
       <c r="I53" s="43"/>
       <c r="J53" s="43"/>
@@ -3486,112 +3626,118 @@
       <c r="L53" s="18"/>
       <c r="M53" s="26"/>
       <c r="N53" s="21" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="54" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A54" s="31" t="s">
+      <c r="A54" s="217" t="s">
         <v>9</v>
       </c>
-      <c r="B54" s="206">
-        <v>46112</v>
+      <c r="B54" s="210">
+        <v>46140</v>
       </c>
       <c r="C54" s="11"/>
       <c r="D54" s="12"/>
-      <c r="E54" s="164"/>
-      <c r="F54" s="127"/>
-      <c r="G54" s="42"/>
+      <c r="E54" s="192"/>
+      <c r="F54" s="124"/>
+      <c r="G54" s="124"/>
       <c r="H54" s="42"/>
       <c r="I54" s="42"/>
       <c r="J54" s="46"/>
       <c r="K54" s="24"/>
       <c r="L54" s="24"/>
       <c r="M54" s="22"/>
-      <c r="N54" s="21"/>
+      <c r="N54" s="21" t="s">
+        <v>110</v>
+      </c>
     </row>
     <row r="55" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A55" s="56"/>
-      <c r="B55" s="207"/>
+      <c r="A55" s="211"/>
+      <c r="B55" s="218"/>
       <c r="C55" s="14" t="s">
-        <v>222</v>
-      </c>
-      <c r="D55" s="128"/>
-      <c r="E55" s="197" t="s">
-        <v>223</v>
-      </c>
-      <c r="F55" s="146"/>
-      <c r="G55" s="147"/>
-      <c r="H55" s="67" t="s">
-        <v>186</v>
-      </c>
-      <c r="I55" s="147"/>
+        <v>11</v>
+      </c>
+      <c r="D55" s="125"/>
+      <c r="E55" s="22" t="s">
+        <v>183</v>
+      </c>
+      <c r="F55" s="141"/>
+      <c r="G55" s="141"/>
+      <c r="H55" s="37" t="s">
+        <v>217</v>
+      </c>
+      <c r="I55" s="142"/>
       <c r="J55" s="45" t="s">
-        <v>224</v>
-      </c>
-      <c r="K55" s="191">
-        <v>3.5</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="K55" s="167"/>
       <c r="L55" s="15"/>
       <c r="M55" s="22"/>
-      <c r="N55" s="108"/>
+      <c r="N55" s="106" t="s">
+        <v>165</v>
+      </c>
     </row>
     <row r="56" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A56" s="56"/>
-      <c r="B56" s="210"/>
+      <c r="A56" s="211"/>
+      <c r="B56" s="212"/>
       <c r="C56" s="14"/>
-      <c r="D56" s="128"/>
+      <c r="D56" s="125"/>
       <c r="E56" s="15"/>
-      <c r="F56" s="129"/>
-      <c r="G56" s="38"/>
+      <c r="F56" s="126"/>
+      <c r="G56" s="126"/>
       <c r="H56" s="38"/>
       <c r="I56" s="38"/>
       <c r="J56" s="49"/>
-      <c r="K56" s="193"/>
+      <c r="K56" s="169"/>
       <c r="L56" s="79"/>
       <c r="M56" s="27"/>
       <c r="N56" s="92"/>
     </row>
     <row r="57" spans="1:14" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A57" s="41"/>
-      <c r="B57" s="208"/>
+      <c r="A57" s="213"/>
+      <c r="B57" s="214"/>
       <c r="C57" s="16" t="s">
         <v>3</v>
       </c>
-      <c r="D57" s="17"/>
+      <c r="D57" s="220"/>
       <c r="E57" s="226" t="s">
-        <v>43</v>
-      </c>
-      <c r="F57" s="134"/>
-      <c r="G57" s="40"/>
-      <c r="H57" s="165" t="s">
-        <v>178</v>
+        <v>260</v>
+      </c>
+      <c r="F57" s="131" t="s">
+        <v>32</v>
+      </c>
+      <c r="G57" s="131"/>
+      <c r="H57" s="155" t="s">
+        <v>229</v>
       </c>
       <c r="I57" s="40"/>
-      <c r="J57" s="43"/>
+      <c r="J57" s="43" t="s">
+        <v>173</v>
+      </c>
       <c r="K57" s="18"/>
       <c r="L57" s="100"/>
       <c r="M57" s="58"/>
       <c r="N57" s="91"/>
     </row>
     <row r="58" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A58" s="203" t="s">
+      <c r="A58" s="175" t="s">
         <v>0</v>
       </c>
-      <c r="B58" s="212">
-        <v>46113</v>
+      <c r="B58" s="184">
+        <v>46141</v>
       </c>
       <c r="C58" s="7"/>
       <c r="D58" s="8"/>
       <c r="E58" s="9"/>
       <c r="F58" s="84"/>
-      <c r="G58" s="68"/>
+      <c r="G58" s="84"/>
       <c r="H58" s="68"/>
       <c r="I58" s="68"/>
       <c r="J58" s="50"/>
       <c r="K58" s="10"/>
       <c r="L58" s="10"/>
       <c r="M58" s="59">
-        <v>46085</v>
+        <v>46113</v>
       </c>
       <c r="N58" s="92"/>
     </row>
@@ -3599,85 +3745,81 @@
       <c r="A59" s="209" t="s">
         <v>1</v>
       </c>
-      <c r="B59" s="206">
-        <v>46113</v>
+      <c r="B59" s="210">
+        <v>46141</v>
       </c>
       <c r="C59" s="11"/>
       <c r="D59" s="12"/>
       <c r="E59" s="13"/>
-      <c r="F59" s="127"/>
-      <c r="G59" s="42"/>
+      <c r="F59" s="124"/>
+      <c r="G59" s="124"/>
       <c r="H59" s="42"/>
       <c r="I59" s="42"/>
       <c r="J59" s="51"/>
-      <c r="K59" s="121"/>
+      <c r="K59" s="118"/>
       <c r="L59" s="24"/>
       <c r="M59" s="55" t="s">
-        <v>54</v>
+        <v>91</v>
       </c>
       <c r="N59" s="21"/>
     </row>
     <row r="60" spans="1:14" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A60" s="56"/>
-      <c r="B60" s="210"/>
+      <c r="A60" s="211"/>
+      <c r="B60" s="212"/>
       <c r="C60" s="14"/>
-      <c r="D60" s="128"/>
+      <c r="D60" s="125"/>
       <c r="E60" s="32"/>
-      <c r="F60" s="136"/>
-      <c r="G60" s="54"/>
+      <c r="F60" s="133"/>
+      <c r="G60" s="133"/>
       <c r="H60" s="54"/>
       <c r="I60" s="54"/>
       <c r="J60" s="40"/>
       <c r="K60" s="26"/>
       <c r="L60" s="26"/>
       <c r="M60" s="55" t="s">
-        <v>56</v>
+        <v>92</v>
       </c>
       <c r="N60" s="90"/>
     </row>
     <row r="61" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A61" s="56"/>
-      <c r="B61" s="210"/>
+      <c r="A61" s="211"/>
+      <c r="B61" s="212"/>
       <c r="C61" s="14"/>
-      <c r="D61" s="128"/>
+      <c r="D61" s="125"/>
       <c r="E61" s="15"/>
-      <c r="F61" s="129"/>
-      <c r="G61" s="38"/>
+      <c r="F61" s="126"/>
+      <c r="G61" s="126"/>
       <c r="H61" s="38"/>
       <c r="I61" s="38"/>
       <c r="J61" s="52"/>
       <c r="K61" s="27"/>
       <c r="L61" s="27"/>
       <c r="M61" s="60" t="s">
-        <v>57</v>
+        <v>93</v>
       </c>
       <c r="N61" s="90"/>
     </row>
     <row r="62" spans="1:14" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A62" s="41"/>
-      <c r="B62" s="208"/>
+      <c r="A62" s="213"/>
+      <c r="B62" s="214"/>
       <c r="C62" s="33" t="s">
         <v>3</v>
       </c>
       <c r="D62" s="17"/>
-      <c r="E62" s="226" t="s">
-        <v>150</v>
-      </c>
-      <c r="F62" s="134" t="s">
-        <v>35</v>
-      </c>
-      <c r="G62" s="40"/>
-      <c r="H62" s="183" t="s">
-        <v>188</v>
+      <c r="E62" s="227" t="s">
+        <v>93</v>
+      </c>
+      <c r="F62" s="131"/>
+      <c r="G62" s="131"/>
+      <c r="H62" s="233" t="s">
+        <v>230</v>
       </c>
       <c r="I62" s="40"/>
-      <c r="J62" s="97" t="s">
-        <v>244</v>
-      </c>
+      <c r="J62" s="97"/>
       <c r="K62" s="77"/>
       <c r="L62" s="99"/>
       <c r="M62" s="22" t="s">
-        <v>106</v>
+        <v>140</v>
       </c>
       <c r="N62" s="27"/>
     </row>
@@ -3685,369 +3827,387 @@
       <c r="A63" s="209" t="s">
         <v>2</v>
       </c>
-      <c r="B63" s="206">
-        <v>46114</v>
+      <c r="B63" s="210">
+        <v>46142</v>
       </c>
       <c r="C63" s="31"/>
       <c r="D63" s="12"/>
       <c r="E63" s="13"/>
-      <c r="F63" s="127"/>
-      <c r="G63" s="42"/>
+      <c r="F63" s="124"/>
+      <c r="G63" s="124"/>
       <c r="H63" s="42"/>
       <c r="I63" s="42"/>
       <c r="J63" s="53"/>
       <c r="K63" s="80"/>
       <c r="L63" s="80"/>
       <c r="M63" s="22" t="s">
-        <v>105</v>
+        <v>141</v>
       </c>
       <c r="N63" s="93" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="64" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A64" s="56"/>
-      <c r="B64" s="210"/>
-      <c r="C64" s="35"/>
-      <c r="D64" s="128"/>
-      <c r="E64" s="22"/>
-      <c r="F64" s="130"/>
-      <c r="G64" s="37"/>
-      <c r="H64" s="37"/>
+      <c r="A64" s="211"/>
+      <c r="B64" s="212"/>
+      <c r="C64" s="35" t="s">
+        <v>11</v>
+      </c>
+      <c r="D64" s="125"/>
+      <c r="E64" s="22" t="s">
+        <v>191</v>
+      </c>
+      <c r="F64" s="127"/>
+      <c r="G64" s="127"/>
+      <c r="H64" s="37" t="s">
+        <v>231</v>
+      </c>
       <c r="I64" s="37"/>
-      <c r="J64" s="54"/>
+      <c r="J64" s="54" t="s">
+        <v>26</v>
+      </c>
       <c r="K64" s="15"/>
       <c r="L64" s="15"/>
       <c r="M64" s="22" t="s">
-        <v>107</v>
+        <v>142</v>
       </c>
       <c r="N64" s="22" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="65" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A65" s="56"/>
-      <c r="B65" s="210"/>
+      <c r="A65" s="211"/>
+      <c r="B65" s="212"/>
       <c r="C65" s="35"/>
-      <c r="D65" s="128"/>
+      <c r="D65" s="125"/>
       <c r="E65" s="27"/>
-      <c r="F65" s="150"/>
-      <c r="G65" s="52"/>
+      <c r="F65" s="144"/>
+      <c r="G65" s="144"/>
       <c r="H65" s="52"/>
       <c r="I65" s="52"/>
       <c r="J65" s="54"/>
       <c r="K65" s="32"/>
       <c r="L65" s="32"/>
       <c r="M65" s="26" t="s">
-        <v>42</v>
+        <v>143</v>
       </c>
       <c r="N65" s="22" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="66" spans="1:15" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A66" s="41"/>
-      <c r="B66" s="208"/>
+      <c r="A66" s="213"/>
+      <c r="B66" s="214"/>
       <c r="C66" s="16" t="s">
         <v>3</v>
       </c>
-      <c r="D66" s="184"/>
-      <c r="E66" s="229" t="s">
-        <v>151</v>
-      </c>
-      <c r="F66" s="134" t="s">
-        <v>35</v>
-      </c>
-      <c r="G66" s="40"/>
+      <c r="D66" s="17"/>
+      <c r="E66" s="226" t="s">
+        <v>92</v>
+      </c>
+      <c r="F66" s="131"/>
+      <c r="G66" s="131" t="s">
+        <v>254</v>
+      </c>
       <c r="H66" s="40" t="s">
-        <v>189</v>
+        <v>232</v>
       </c>
       <c r="I66" s="40"/>
       <c r="J66" s="97" t="s">
-        <v>244</v>
+        <v>173</v>
       </c>
       <c r="K66" s="77"/>
       <c r="L66" s="77"/>
       <c r="M66" s="22" t="s">
-        <v>108</v>
+        <v>144</v>
       </c>
       <c r="N66" s="22" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="67" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A67" s="209" t="s">
         <v>4</v>
       </c>
-      <c r="B67" s="206">
-        <v>46115</v>
+      <c r="B67" s="210">
+        <v>46143</v>
       </c>
       <c r="C67" s="36"/>
       <c r="D67" s="12"/>
-      <c r="E67" s="131"/>
-      <c r="F67" s="132"/>
-      <c r="G67" s="133"/>
-      <c r="H67" s="133"/>
-      <c r="I67" s="133"/>
+      <c r="E67" s="128"/>
+      <c r="F67" s="129"/>
+      <c r="G67" s="129"/>
+      <c r="H67" s="130"/>
+      <c r="I67" s="130"/>
       <c r="J67" s="53"/>
       <c r="K67" s="80"/>
       <c r="L67" s="80"/>
       <c r="M67" s="22" t="s">
-        <v>109</v>
+        <v>145</v>
       </c>
       <c r="N67" s="22" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
     </row>
     <row r="68" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A68" s="56"/>
-      <c r="B68" s="210"/>
+      <c r="A68" s="211"/>
+      <c r="B68" s="212"/>
       <c r="C68" s="14" t="s">
         <v>12</v>
       </c>
-      <c r="D68" s="185"/>
-      <c r="E68" s="32" t="s">
-        <v>81</v>
-      </c>
-      <c r="F68" s="136"/>
-      <c r="G68" s="54"/>
+      <c r="D68" s="222"/>
+      <c r="E68" s="22" t="s">
+        <v>193</v>
+      </c>
+      <c r="F68" s="133"/>
+      <c r="G68" s="133"/>
       <c r="H68" s="54" t="s">
-        <v>185</v>
+        <v>233</v>
       </c>
       <c r="I68" s="54"/>
       <c r="J68" s="40" t="s">
+        <v>192</v>
+      </c>
+      <c r="K68" s="26" t="s">
         <v>16</v>
-      </c>
-      <c r="K68" s="26" t="s">
-        <v>17</v>
       </c>
       <c r="L68" s="26"/>
       <c r="M68" s="22" t="s">
-        <v>110</v>
+        <v>86</v>
       </c>
       <c r="N68" s="65" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
     </row>
     <row r="69" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A69" s="56"/>
-      <c r="B69" s="210"/>
+      <c r="A69" s="211"/>
+      <c r="B69" s="212"/>
       <c r="C69" s="14"/>
-      <c r="D69" s="128"/>
-      <c r="E69" s="166"/>
-      <c r="F69" s="129"/>
-      <c r="G69" s="38"/>
+      <c r="D69" s="125"/>
+      <c r="E69" s="193"/>
+      <c r="F69" s="126"/>
+      <c r="G69" s="126"/>
       <c r="H69" s="38"/>
       <c r="I69" s="38"/>
       <c r="J69" s="52"/>
       <c r="K69" s="27"/>
       <c r="L69" s="27"/>
       <c r="M69" s="22" t="s">
-        <v>111</v>
-      </c>
-      <c r="N69" s="27" t="s">
-        <v>73</v>
+        <v>85</v>
+      </c>
+      <c r="N69" s="25" t="s">
+        <v>77</v>
       </c>
       <c r="O69" s="5"/>
     </row>
     <row r="70" spans="1:15" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A70" s="41"/>
-      <c r="B70" s="208"/>
-      <c r="C70" s="33" t="s">
+      <c r="A70" s="213"/>
+      <c r="B70" s="214"/>
+      <c r="C70" s="16" t="s">
         <v>3</v>
       </c>
       <c r="D70" s="17"/>
       <c r="E70" s="22" t="s">
-        <v>152</v>
-      </c>
-      <c r="F70" s="134" t="s">
-        <v>35</v>
-      </c>
-      <c r="G70" s="40"/>
+        <v>113</v>
+      </c>
+      <c r="F70" s="131"/>
+      <c r="G70" s="131"/>
       <c r="H70" s="40" t="s">
-        <v>190</v>
+        <v>234</v>
       </c>
       <c r="I70" s="40"/>
-      <c r="J70" s="97" t="s">
-        <v>242</v>
-      </c>
+      <c r="J70" s="97"/>
       <c r="K70" s="77"/>
-      <c r="L70" s="99"/>
+      <c r="L70" s="78" t="s">
+        <v>168</v>
+      </c>
       <c r="M70" s="22" t="s">
-        <v>112</v>
-      </c>
-      <c r="N70" s="27" t="s">
-        <v>97</v>
+        <v>146</v>
+      </c>
+      <c r="N70" s="25" t="s">
+        <v>67</v>
       </c>
     </row>
     <row r="71" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A71" s="213" t="s">
+      <c r="A71" s="209" t="s">
         <v>5</v>
       </c>
-      <c r="B71" s="214">
-        <v>46116</v>
+      <c r="B71" s="210">
+        <v>46144</v>
       </c>
       <c r="C71" s="11"/>
       <c r="D71" s="12"/>
-      <c r="E71" s="151"/>
-      <c r="F71" s="152"/>
-      <c r="G71" s="153"/>
-      <c r="H71" s="153"/>
-      <c r="I71" s="153"/>
+      <c r="E71" s="189"/>
+      <c r="F71" s="145"/>
+      <c r="G71" s="145"/>
+      <c r="H71" s="146"/>
+      <c r="I71" s="146"/>
       <c r="J71" s="46"/>
       <c r="K71" s="24"/>
       <c r="L71" s="24"/>
       <c r="M71" s="22" t="s">
-        <v>113</v>
+        <v>148</v>
       </c>
       <c r="N71" s="22" t="s">
-        <v>127</v>
+        <v>68</v>
       </c>
       <c r="O71" s="4"/>
     </row>
     <row r="72" spans="1:15" ht="13.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A72" s="215"/>
-      <c r="B72" s="216"/>
+      <c r="A72" s="211"/>
+      <c r="B72" s="212"/>
       <c r="C72" s="14" t="s">
         <v>11</v>
       </c>
-      <c r="D72" s="154"/>
-      <c r="E72" s="22" t="s">
-        <v>153</v>
-      </c>
-      <c r="F72" s="155"/>
-      <c r="G72" s="156"/>
-      <c r="H72" s="156" t="s">
-        <v>191</v>
-      </c>
-      <c r="I72" s="156"/>
+      <c r="D72" s="190"/>
+      <c r="E72" s="26" t="s">
+        <v>194</v>
+      </c>
+      <c r="F72" s="147"/>
+      <c r="G72" s="147"/>
+      <c r="H72" s="148" t="s">
+        <v>237</v>
+      </c>
+      <c r="I72" s="148"/>
       <c r="J72" s="37" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="K72" s="22" t="s">
-        <v>162</v>
+        <v>71</v>
       </c>
       <c r="L72" s="22"/>
-      <c r="M72" s="124" t="s">
-        <v>114</v>
+      <c r="M72" s="195" t="s">
+        <v>149</v>
       </c>
       <c r="N72" s="25" t="s">
-        <v>124</v>
+        <v>84</v>
       </c>
     </row>
     <row r="73" spans="1:15" ht="13.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A73" s="215"/>
-      <c r="B73" s="216"/>
+      <c r="A73" s="211"/>
+      <c r="B73" s="212"/>
       <c r="C73" s="14" t="s">
         <v>6</v>
       </c>
-      <c r="D73" s="154"/>
-      <c r="E73" s="20" t="s">
-        <v>154</v>
-      </c>
-      <c r="F73" s="111" t="s">
-        <v>35</v>
-      </c>
-      <c r="G73" s="67"/>
+      <c r="D73" s="190"/>
+      <c r="E73" s="22" t="s">
+        <v>195</v>
+      </c>
+      <c r="F73" s="109" t="s">
+        <v>32</v>
+      </c>
+      <c r="G73" s="83"/>
       <c r="H73" s="67" t="s">
-        <v>192</v>
+        <v>238</v>
       </c>
       <c r="I73" s="67"/>
       <c r="J73" s="37" t="s">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="K73" s="15" t="s">
-        <v>45</v>
-      </c>
-      <c r="L73" s="15"/>
+        <v>38</v>
+      </c>
+      <c r="L73" s="26" t="s">
+        <v>168</v>
+      </c>
       <c r="M73" s="61" t="s">
-        <v>115</v>
+        <v>150</v>
       </c>
       <c r="N73" s="25" t="s">
-        <v>125</v>
+        <v>131</v>
       </c>
     </row>
     <row r="74" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A74" s="217"/>
-      <c r="B74" s="218"/>
+      <c r="A74" s="213"/>
+      <c r="B74" s="214"/>
       <c r="C74" s="16" t="s">
         <v>3</v>
       </c>
-      <c r="D74" s="184"/>
-      <c r="E74" s="22" t="s">
-        <v>105</v>
-      </c>
-      <c r="F74" s="167"/>
-      <c r="G74" s="159"/>
-      <c r="H74" s="158" t="s">
-        <v>193</v>
-      </c>
-      <c r="I74" s="158"/>
+      <c r="D74" s="220" t="s">
+        <v>235</v>
+      </c>
+      <c r="E74" s="226" t="s">
+        <v>91</v>
+      </c>
+      <c r="F74" s="156"/>
+      <c r="G74" s="240"/>
+      <c r="H74" s="150" t="s">
+        <v>239</v>
+      </c>
+      <c r="I74" s="150"/>
       <c r="J74" s="39"/>
       <c r="K74" s="78"/>
       <c r="L74" s="78"/>
       <c r="M74" s="61"/>
-      <c r="N74" s="61"/>
+      <c r="N74" s="61" t="s">
+        <v>138</v>
+      </c>
     </row>
     <row r="75" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A75" s="213" t="s">
+      <c r="A75" s="209" t="s">
         <v>7</v>
       </c>
-      <c r="B75" s="214">
-        <v>46117</v>
-      </c>
-      <c r="C75" s="36"/>
+      <c r="B75" s="210">
+        <v>46145</v>
+      </c>
+      <c r="C75" s="36" t="s">
+        <v>170</v>
+      </c>
       <c r="D75" s="12"/>
-      <c r="E75" s="31"/>
-      <c r="F75" s="160"/>
-      <c r="G75" s="161"/>
-      <c r="H75" s="25"/>
-      <c r="I75" s="161"/>
-      <c r="J75" s="25"/>
-      <c r="K75" s="177"/>
+      <c r="E75" s="31" t="s">
+        <v>171</v>
+      </c>
+      <c r="F75" s="152"/>
+      <c r="G75" s="152"/>
+      <c r="H75" s="25" t="s">
+        <v>240</v>
+      </c>
+      <c r="I75" s="153"/>
+      <c r="J75" s="25" t="s">
+        <v>196</v>
+      </c>
+      <c r="K75" s="164"/>
       <c r="L75" s="25"/>
       <c r="M75" s="61"/>
-      <c r="N75" s="22"/>
+      <c r="N75" s="22" t="s">
+        <v>139</v>
+      </c>
     </row>
     <row r="76" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A76" s="215"/>
-      <c r="B76" s="216"/>
+      <c r="A76" s="211"/>
+      <c r="B76" s="212"/>
       <c r="C76" s="35" t="s">
         <v>11</v>
       </c>
-      <c r="D76" s="162"/>
-      <c r="E76" s="22" t="s">
-        <v>156</v>
+      <c r="D76" s="223"/>
+      <c r="E76" s="32" t="s">
+        <v>111</v>
       </c>
       <c r="F76" s="83"/>
-      <c r="G76" s="67"/>
-      <c r="H76" s="67" t="s">
-        <v>194</v>
+      <c r="G76" s="83"/>
+      <c r="H76" s="37" t="s">
+        <v>216</v>
       </c>
       <c r="I76" s="67"/>
       <c r="J76" s="38" t="s">
-        <v>155</v>
+        <v>176</v>
       </c>
       <c r="K76" s="15"/>
       <c r="L76" s="15"/>
       <c r="M76" s="27"/>
-      <c r="N76" s="56"/>
+      <c r="N76" s="56" t="s">
+        <v>147</v>
+      </c>
     </row>
     <row r="77" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A77" s="215"/>
-      <c r="B77" s="216"/>
-      <c r="C77" s="35" t="s">
-        <v>6</v>
-      </c>
-      <c r="D77" s="186"/>
-      <c r="E77" s="226" t="s">
-        <v>54</v>
-      </c>
-      <c r="F77" s="130"/>
-      <c r="G77" s="37"/>
-      <c r="H77" s="37" t="s">
-        <v>195</v>
-      </c>
+      <c r="A77" s="211"/>
+      <c r="B77" s="212"/>
+      <c r="C77" s="35"/>
+      <c r="D77" s="190"/>
+      <c r="E77" s="26"/>
+      <c r="F77" s="127"/>
+      <c r="G77" s="127"/>
+      <c r="H77" s="37"/>
       <c r="I77" s="37"/>
       <c r="J77" s="98"/>
       <c r="K77" s="81"/>
@@ -4056,61 +4216,59 @@
       <c r="N77" s="65"/>
     </row>
     <row r="78" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A78" s="217"/>
-      <c r="B78" s="218"/>
-      <c r="C78" s="16" t="s">
-        <v>3</v>
-      </c>
-      <c r="D78" s="184"/>
-      <c r="E78" s="227" t="s">
-        <v>42</v>
-      </c>
-      <c r="F78" s="163"/>
-      <c r="G78" s="140"/>
-      <c r="H78" t="s">
-        <v>196</v>
-      </c>
-      <c r="I78" s="140"/>
+      <c r="A78" s="213"/>
+      <c r="B78" s="214"/>
+      <c r="C78" s="16"/>
+      <c r="D78" s="17"/>
+      <c r="E78" s="136"/>
+      <c r="F78" s="154"/>
+      <c r="G78" s="154"/>
+      <c r="H78"/>
+      <c r="I78" s="136"/>
       <c r="J78" s="41"/>
-      <c r="K78" s="110"/>
+      <c r="K78" s="108"/>
       <c r="L78" s="41"/>
       <c r="M78" s="26"/>
       <c r="N78" s="27"/>
     </row>
     <row r="79" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A79" s="213" t="s">
+      <c r="A79" s="181" t="s">
         <v>8</v>
       </c>
-      <c r="B79" s="214">
-        <v>46118</v>
+      <c r="B79" s="178">
+        <v>46146</v>
       </c>
       <c r="C79" s="11" t="s">
-        <v>27</v>
-      </c>
-      <c r="D79" s="187"/>
-      <c r="E79" s="228" t="s">
-        <v>133</v>
-      </c>
-      <c r="F79" s="144"/>
-      <c r="G79" s="44"/>
+        <v>100</v>
+      </c>
+      <c r="D79" s="12"/>
+      <c r="E79" s="170" t="s">
+        <v>74</v>
+      </c>
+      <c r="F79" s="139"/>
+      <c r="G79" s="139"/>
       <c r="H79" s="44" t="s">
-        <v>185</v>
+        <v>241</v>
       </c>
       <c r="I79" s="44"/>
-      <c r="J79" s="44"/>
-      <c r="K79" s="19"/>
+      <c r="J79" s="44" t="s">
+        <v>98</v>
+      </c>
+      <c r="K79" s="19" t="s">
+        <v>101</v>
+      </c>
       <c r="L79" s="19"/>
       <c r="M79" s="26"/>
       <c r="N79" s="22"/>
     </row>
     <row r="80" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A80" s="219"/>
-      <c r="B80" s="220"/>
+      <c r="A80" s="108"/>
+      <c r="B80" s="183"/>
       <c r="C80" s="16"/>
       <c r="D80" s="17"/>
       <c r="E80" s="18"/>
-      <c r="F80" s="145"/>
-      <c r="G80" s="43"/>
+      <c r="F80" s="140"/>
+      <c r="G80" s="140"/>
       <c r="H80" s="43"/>
       <c r="I80" s="43"/>
       <c r="J80" s="43"/>
@@ -4123,90 +4281,90 @@
       <c r="A81" s="31" t="s">
         <v>9</v>
       </c>
-      <c r="B81" s="206">
-        <v>46119</v>
-      </c>
-      <c r="C81" s="11"/>
+      <c r="B81" s="178">
+        <v>46147</v>
+      </c>
+      <c r="C81" s="11" t="s">
+        <v>100</v>
+      </c>
       <c r="D81" s="12"/>
-      <c r="E81" s="13"/>
-      <c r="F81" s="127"/>
-      <c r="G81" s="42"/>
-      <c r="H81" s="42"/>
+      <c r="E81" s="185" t="s">
+        <v>102</v>
+      </c>
+      <c r="F81" s="124"/>
+      <c r="G81" s="124"/>
+      <c r="H81" s="42" t="s">
+        <v>242</v>
+      </c>
       <c r="I81" s="42"/>
-      <c r="J81" s="46"/>
-      <c r="K81" s="121"/>
+      <c r="J81" s="46" t="s">
+        <v>98</v>
+      </c>
+      <c r="K81" s="118" t="s">
+        <v>103</v>
+      </c>
       <c r="L81" s="24"/>
       <c r="M81" s="22"/>
       <c r="N81" s="21"/>
     </row>
     <row r="82" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A82" s="56"/>
-      <c r="B82" s="207"/>
-      <c r="C82" s="14" t="s">
-        <v>226</v>
-      </c>
-      <c r="D82" s="128"/>
-      <c r="E82" s="199" t="s">
-        <v>227</v>
-      </c>
-      <c r="F82" s="150" t="s">
-        <v>164</v>
-      </c>
-      <c r="G82" s="147"/>
-      <c r="H82" s="52" t="s">
-        <v>238</v>
-      </c>
-      <c r="I82" s="147"/>
-      <c r="J82" s="45" t="s">
-        <v>228</v>
-      </c>
-      <c r="K82" s="200">
-        <v>4</v>
-      </c>
-      <c r="L82" s="21" t="s">
-        <v>230</v>
-      </c>
+      <c r="B82" s="179"/>
+      <c r="C82" s="14"/>
+      <c r="D82" s="125"/>
+      <c r="E82" s="27"/>
+      <c r="F82" s="144"/>
+      <c r="G82" s="141"/>
+      <c r="H82" s="52"/>
+      <c r="I82" s="142"/>
+      <c r="J82" s="45"/>
+      <c r="K82" s="172"/>
+      <c r="L82" s="21"/>
       <c r="M82" s="22"/>
       <c r="N82" s="96" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="83" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A83" s="56"/>
-      <c r="B83" s="210"/>
+      <c r="B83" s="182"/>
       <c r="C83" s="14"/>
-      <c r="D83" s="128"/>
+      <c r="D83" s="125"/>
       <c r="E83" s="15"/>
-      <c r="F83" s="129"/>
-      <c r="G83" s="38"/>
+      <c r="F83" s="126"/>
+      <c r="G83" s="126"/>
       <c r="H83" s="38"/>
       <c r="I83" s="38"/>
       <c r="J83" s="49"/>
-      <c r="K83" s="193"/>
+      <c r="K83" s="169"/>
       <c r="L83" s="79"/>
       <c r="M83" s="27"/>
       <c r="N83" s="88"/>
     </row>
     <row r="84" spans="1:15" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A84" s="41"/>
-      <c r="B84" s="208"/>
+      <c r="B84" s="180"/>
       <c r="C84" s="16" t="s">
         <v>3</v>
       </c>
-      <c r="D84" s="17"/>
-      <c r="E84" s="22" t="s">
-        <v>246</v>
-      </c>
-      <c r="F84" s="134" t="s">
-        <v>35</v>
-      </c>
-      <c r="G84" s="40"/>
+      <c r="D84" s="220" t="s">
+        <v>236</v>
+      </c>
+      <c r="E84" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="F84" s="131" t="s">
+        <v>32</v>
+      </c>
+      <c r="G84" s="131"/>
       <c r="H84" s="40" t="s">
+        <v>243</v>
+      </c>
+      <c r="I84" s="40" t="s">
         <v>197</v>
       </c>
-      <c r="I84" s="40"/>
       <c r="J84" s="43" t="s">
-        <v>244</v>
+        <v>176</v>
       </c>
       <c r="K84" s="18"/>
       <c r="L84" s="18"/>
@@ -4214,292 +4372,284 @@
       <c r="N84" s="25"/>
     </row>
     <row r="85" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A85" s="203" t="s">
+      <c r="A85" s="175" t="s">
         <v>0</v>
       </c>
-      <c r="B85" s="212">
-        <v>46120</v>
+      <c r="B85" s="184">
+        <v>46148</v>
       </c>
       <c r="C85" s="7"/>
       <c r="D85" s="8"/>
       <c r="E85" s="9"/>
       <c r="F85" s="84"/>
-      <c r="G85" s="68"/>
+      <c r="G85" s="84"/>
       <c r="H85" s="68"/>
       <c r="I85" s="68"/>
       <c r="J85" s="50"/>
       <c r="K85" s="10"/>
       <c r="L85" s="10"/>
       <c r="M85" s="59">
-        <v>46092</v>
+        <v>46120</v>
       </c>
       <c r="N85" s="25"/>
     </row>
     <row r="86" spans="1:15" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A86" s="209" t="s">
+      <c r="A86" s="181" t="s">
         <v>1</v>
       </c>
-      <c r="B86" s="206">
-        <v>46120</v>
+      <c r="B86" s="178">
+        <v>46148</v>
       </c>
       <c r="C86" s="11"/>
       <c r="D86" s="12"/>
       <c r="E86" s="13"/>
-      <c r="F86" s="127"/>
-      <c r="G86" s="42"/>
+      <c r="F86" s="124"/>
+      <c r="G86" s="124"/>
       <c r="H86" s="42"/>
       <c r="I86" s="42"/>
       <c r="J86" s="51"/>
       <c r="K86" s="34"/>
       <c r="L86" s="34"/>
       <c r="M86" s="55" t="s">
-        <v>58</v>
+        <v>96</v>
       </c>
       <c r="N86" s="25"/>
     </row>
     <row r="87" spans="1:15" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A87" s="56"/>
-      <c r="B87" s="210"/>
+      <c r="B87" s="182"/>
       <c r="C87" s="14"/>
-      <c r="D87" s="128"/>
+      <c r="D87" s="125"/>
       <c r="E87" s="32"/>
-      <c r="F87" s="136"/>
-      <c r="G87" s="54"/>
+      <c r="F87" s="133"/>
+      <c r="G87" s="133"/>
       <c r="H87" s="54"/>
       <c r="I87" s="54"/>
       <c r="J87" s="40"/>
       <c r="K87" s="26"/>
       <c r="L87" s="26"/>
       <c r="M87" s="55" t="s">
-        <v>59</v>
+        <v>94</v>
       </c>
       <c r="N87" s="25"/>
     </row>
     <row r="88" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A88" s="56"/>
-      <c r="B88" s="210"/>
+      <c r="B88" s="182"/>
       <c r="C88" s="35"/>
-      <c r="D88" s="128"/>
+      <c r="D88" s="125"/>
       <c r="E88" s="15"/>
-      <c r="F88" s="129"/>
-      <c r="G88" s="38"/>
+      <c r="F88" s="126"/>
+      <c r="G88" s="126"/>
       <c r="H88" s="38"/>
-      <c r="I88" s="169"/>
+      <c r="I88" s="158"/>
       <c r="J88" s="52"/>
       <c r="K88" s="27"/>
       <c r="L88" s="27"/>
-      <c r="M88" s="60"/>
+      <c r="M88" s="60" t="s">
+        <v>95</v>
+      </c>
       <c r="N88" s="25"/>
     </row>
     <row r="89" spans="1:15" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A89" s="41"/>
-      <c r="B89" s="208"/>
+      <c r="B89" s="180"/>
       <c r="C89" s="33" t="s">
         <v>3</v>
       </c>
-      <c r="D89" s="184"/>
-      <c r="E89" s="22" t="s">
-        <v>157</v>
-      </c>
-      <c r="F89" s="134" t="s">
-        <v>35</v>
-      </c>
-      <c r="G89" s="40"/>
+      <c r="D89" s="17"/>
+      <c r="E89" s="227" t="s">
+        <v>199</v>
+      </c>
+      <c r="F89" s="131" t="s">
+        <v>32</v>
+      </c>
+      <c r="G89" s="131"/>
       <c r="H89" s="40" t="s">
-        <v>198</v>
+        <v>244</v>
       </c>
       <c r="I89" s="40"/>
       <c r="J89" s="97" t="s">
-        <v>244</v>
+        <v>173</v>
       </c>
       <c r="K89" s="77"/>
       <c r="L89" s="15"/>
-      <c r="M89" s="22" t="s">
-        <v>116</v>
+      <c r="M89" s="196" t="s">
+        <v>151</v>
       </c>
       <c r="N89" s="25"/>
     </row>
     <row r="90" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A90" s="209" t="s">
+      <c r="A90" s="181" t="s">
         <v>2</v>
       </c>
-      <c r="B90" s="206">
-        <v>46121</v>
-      </c>
-      <c r="C90" s="122"/>
+      <c r="B90" s="178">
+        <v>46149</v>
+      </c>
+      <c r="C90" s="119" t="s">
+        <v>72</v>
+      </c>
       <c r="D90" s="12"/>
-      <c r="E90" s="13"/>
-      <c r="F90" s="127"/>
-      <c r="G90" s="42"/>
+      <c r="E90" s="185" t="s">
+        <v>104</v>
+      </c>
+      <c r="F90" s="124"/>
+      <c r="G90" s="124"/>
       <c r="H90" s="42"/>
       <c r="I90" s="42"/>
-      <c r="J90" s="53"/>
-      <c r="K90" s="80"/>
-      <c r="L90" s="80"/>
-      <c r="M90" s="22" t="s">
-        <v>117</v>
+      <c r="J90" s="46" t="s">
+        <v>98</v>
+      </c>
+      <c r="K90" s="118" t="s">
+        <v>103</v>
+      </c>
+      <c r="L90" s="24"/>
+      <c r="M90" s="196" t="s">
+        <v>152</v>
       </c>
       <c r="N90" s="87"/>
     </row>
     <row r="91" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A91" s="56"/>
-      <c r="B91" s="210"/>
-      <c r="C91" s="35" t="s">
-        <v>222</v>
-      </c>
-      <c r="D91" s="128"/>
-      <c r="E91" s="198" t="s">
-        <v>229</v>
-      </c>
-      <c r="F91" s="130"/>
-      <c r="G91" s="37"/>
-      <c r="H91" s="37" t="s">
-        <v>239</v>
-      </c>
-      <c r="I91" s="37"/>
-      <c r="J91" s="54" t="s">
-        <v>220</v>
-      </c>
-      <c r="K91" s="200">
-        <v>4</v>
-      </c>
-      <c r="L91" s="21" t="s">
-        <v>231</v>
-      </c>
+      <c r="B91" s="182"/>
+      <c r="C91" s="35"/>
+      <c r="D91" s="125"/>
+      <c r="E91" s="194"/>
+      <c r="F91" s="127"/>
+      <c r="G91" s="127"/>
+      <c r="H91" s="37"/>
+      <c r="I91" s="26"/>
+      <c r="J91" s="54"/>
+      <c r="K91" s="172"/>
+      <c r="L91" s="21"/>
       <c r="M91" s="22" t="s">
-        <v>118</v>
-      </c>
-      <c r="N91" s="109" t="s">
-        <v>31</v>
+        <v>88</v>
+      </c>
+      <c r="N91" s="107" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="92" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A92" s="56"/>
-      <c r="B92" s="210"/>
-      <c r="D92" s="128"/>
+      <c r="B92" s="182"/>
+      <c r="D92" s="125"/>
       <c r="E92" s="27"/>
-      <c r="F92" s="150"/>
-      <c r="G92" s="52"/>
+      <c r="F92" s="144"/>
+      <c r="G92" s="144"/>
       <c r="H92" s="52"/>
       <c r="I92" s="52"/>
       <c r="J92" s="54"/>
       <c r="K92" s="32"/>
       <c r="L92" s="32"/>
-      <c r="M92" s="124" t="s">
-        <v>119</v>
-      </c>
-      <c r="N92" s="65"/>
+      <c r="M92" s="26" t="s">
+        <v>93</v>
+      </c>
+      <c r="N92" s="207" t="s">
+        <v>79</v>
+      </c>
     </row>
     <row r="93" spans="1:15" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A93" s="41"/>
-      <c r="B93" s="208"/>
+      <c r="B93" s="180"/>
       <c r="C93" s="16" t="s">
         <v>3</v>
       </c>
       <c r="D93" s="17"/>
       <c r="E93" s="226" t="s">
-        <v>158</v>
-      </c>
-      <c r="F93" s="134" t="s">
-        <v>35</v>
-      </c>
-      <c r="G93" s="40"/>
+        <v>94</v>
+      </c>
+      <c r="F93" s="131"/>
+      <c r="G93" s="131" t="s">
+        <v>255</v>
+      </c>
       <c r="H93" s="40" t="s">
-        <v>199</v>
+        <v>245</v>
       </c>
       <c r="I93" s="40"/>
-      <c r="J93" s="97" t="s">
-        <v>244</v>
-      </c>
+      <c r="J93" s="97"/>
       <c r="K93" s="77"/>
       <c r="L93" s="15"/>
-      <c r="M93" s="22" t="s">
-        <v>120</v>
-      </c>
-      <c r="N93" s="25"/>
+      <c r="M93" s="196" t="s">
+        <v>87</v>
+      </c>
+      <c r="N93" s="65"/>
     </row>
     <row r="94" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A94" s="209" t="s">
         <v>4</v>
       </c>
-      <c r="B94" s="206">
-        <v>46122</v>
+      <c r="B94" s="210">
+        <v>46150</v>
       </c>
       <c r="C94" s="36"/>
       <c r="D94" s="12"/>
-      <c r="E94" s="131"/>
-      <c r="F94" s="132"/>
-      <c r="G94" s="133"/>
-      <c r="H94" s="133"/>
-      <c r="I94" s="133"/>
+      <c r="E94" s="203"/>
+      <c r="F94" s="129"/>
+      <c r="G94" s="129"/>
+      <c r="H94" s="130"/>
+      <c r="I94" s="130"/>
       <c r="J94" s="53"/>
       <c r="K94" s="80"/>
       <c r="L94" s="80"/>
-      <c r="M94" s="22" t="s">
-        <v>55</v>
+      <c r="M94" s="196" t="s">
+        <v>153</v>
       </c>
       <c r="N94" s="65"/>
     </row>
     <row r="95" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A95" s="56"/>
-      <c r="B95" s="210"/>
+      <c r="A95" s="211"/>
+      <c r="B95" s="212"/>
       <c r="C95" s="35"/>
-      <c r="D95" s="128"/>
-      <c r="E95" s="22"/>
-      <c r="F95" s="136"/>
-      <c r="G95" s="54"/>
+      <c r="D95" s="125"/>
+      <c r="E95" s="204"/>
+      <c r="F95" s="133"/>
+      <c r="G95" s="133"/>
       <c r="H95" s="54"/>
       <c r="I95" s="54"/>
       <c r="J95" s="40"/>
       <c r="K95" s="26"/>
       <c r="L95" s="26"/>
       <c r="M95" s="22" t="s">
-        <v>121</v>
+        <v>154</v>
       </c>
       <c r="N95" s="25"/>
     </row>
     <row r="96" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A96" s="56"/>
-      <c r="B96" s="210"/>
+      <c r="A96" s="211"/>
+      <c r="B96" s="212"/>
       <c r="C96" s="14"/>
-      <c r="D96" s="128"/>
-      <c r="E96" s="15"/>
-      <c r="F96" s="129"/>
-      <c r="G96" s="38"/>
-      <c r="H96" s="170"/>
+      <c r="D96" s="125"/>
+      <c r="E96" s="205"/>
+      <c r="F96" s="126"/>
+      <c r="G96" s="126"/>
+      <c r="H96" s="159"/>
       <c r="I96" s="38"/>
       <c r="J96" s="52"/>
       <c r="K96" s="27"/>
       <c r="L96" s="27"/>
-      <c r="M96" s="178" t="s">
-        <v>122</v>
+      <c r="M96" s="196" t="s">
+        <v>90</v>
       </c>
       <c r="N96" s="65"/>
       <c r="O96" s="5"/>
     </row>
     <row r="97" spans="1:15" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A97" s="41"/>
-      <c r="B97" s="208"/>
+      <c r="A97" s="213"/>
+      <c r="B97" s="214"/>
       <c r="C97" s="16" t="s">
         <v>3</v>
       </c>
-      <c r="D97" s="184"/>
-      <c r="E97" s="22" t="s">
-        <v>159</v>
-      </c>
-      <c r="F97" s="134" t="s">
-        <v>35</v>
-      </c>
-      <c r="G97" s="40"/>
-      <c r="H97" s="40" t="s">
-        <v>200</v>
-      </c>
+      <c r="D97" s="17"/>
+      <c r="E97" s="204"/>
+      <c r="F97" s="131"/>
+      <c r="G97" s="131"/>
+      <c r="H97" s="40"/>
       <c r="I97" s="40"/>
       <c r="J97" s="97"/>
       <c r="K97" s="77"/>
       <c r="L97" s="99"/>
       <c r="M97" s="22" t="s">
-        <v>123</v>
+        <v>155</v>
       </c>
       <c r="N97" s="27"/>
     </row>
@@ -4507,203 +4657,199 @@
       <c r="A98" s="209" t="s">
         <v>5</v>
       </c>
-      <c r="B98" s="206">
-        <v>46123</v>
+      <c r="B98" s="210">
+        <v>46151</v>
       </c>
       <c r="C98" s="11"/>
       <c r="D98" s="12"/>
-      <c r="E98" s="151"/>
-      <c r="F98" s="152"/>
-      <c r="G98" s="153"/>
-      <c r="H98" s="153"/>
-      <c r="I98" s="153"/>
+      <c r="E98" s="206"/>
+      <c r="F98" s="145"/>
+      <c r="G98" s="145"/>
+      <c r="H98" s="146"/>
+      <c r="I98" s="146"/>
       <c r="J98" s="46"/>
       <c r="K98" s="24"/>
       <c r="L98" s="34"/>
       <c r="M98" s="22" t="s">
-        <v>126</v>
+        <v>156</v>
       </c>
       <c r="N98" s="25"/>
       <c r="O98" s="4"/>
     </row>
     <row r="99" spans="1:15" ht="13.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A99" s="56"/>
-      <c r="B99" s="210"/>
+      <c r="A99" s="211"/>
+      <c r="B99" s="212"/>
       <c r="C99" s="14" t="s">
         <v>11</v>
       </c>
-      <c r="D99" s="186"/>
-      <c r="E99" s="22" t="s">
-        <v>163</v>
-      </c>
-      <c r="F99" s="155" t="s">
-        <v>164</v>
-      </c>
-      <c r="G99" s="156"/>
-      <c r="H99" s="156" t="s">
-        <v>201</v>
-      </c>
-      <c r="I99" s="156"/>
+      <c r="D99" s="190"/>
+      <c r="E99" s="204"/>
+      <c r="F99" s="147"/>
+      <c r="G99" s="147"/>
+      <c r="H99" s="148"/>
+      <c r="I99" s="148"/>
       <c r="J99" s="37" t="s">
-        <v>160</v>
+        <v>75</v>
       </c>
       <c r="K99" s="22"/>
-      <c r="L99" s="22" t="s">
-        <v>161</v>
-      </c>
-      <c r="M99" s="26"/>
+      <c r="L99" s="22"/>
+      <c r="M99" s="26" t="s">
+        <v>157</v>
+      </c>
       <c r="N99" s="25"/>
     </row>
     <row r="100" spans="1:15" ht="13.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A100" s="56"/>
-      <c r="B100" s="210"/>
+      <c r="A100" s="211"/>
+      <c r="B100" s="212"/>
       <c r="C100" s="14" t="s">
         <v>6</v>
       </c>
-      <c r="D100" s="154"/>
-      <c r="E100" s="26" t="s">
-        <v>165</v>
-      </c>
-      <c r="F100" s="83" t="s">
-        <v>35</v>
-      </c>
-      <c r="G100" s="67"/>
-      <c r="H100" s="67" t="s">
-        <v>202</v>
-      </c>
+      <c r="D100" s="190"/>
+      <c r="E100" s="201"/>
+      <c r="F100" s="83"/>
+      <c r="G100" s="83"/>
+      <c r="H100" s="67"/>
       <c r="I100" s="67"/>
       <c r="J100" s="37" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="K100" s="15" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="L100" s="15"/>
-      <c r="M100" s="61"/>
+      <c r="M100" s="61" t="s">
+        <v>158</v>
+      </c>
       <c r="N100" s="25"/>
     </row>
     <row r="101" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A101" s="41"/>
-      <c r="B101" s="208"/>
+      <c r="A101" s="213"/>
+      <c r="B101" s="214"/>
       <c r="C101" s="16" t="s">
         <v>3</v>
       </c>
-      <c r="D101" s="184"/>
-      <c r="E101" s="26" t="s">
-        <v>166</v>
-      </c>
-      <c r="F101" s="167" t="s">
-        <v>35</v>
-      </c>
-      <c r="G101" s="159"/>
-      <c r="H101" s="158" t="s">
-        <v>203</v>
-      </c>
-      <c r="I101" s="140"/>
-      <c r="J101" s="39" t="s">
-        <v>242</v>
-      </c>
+      <c r="D101" s="17"/>
+      <c r="E101" s="201"/>
+      <c r="F101" s="156"/>
+      <c r="G101" s="240"/>
+      <c r="H101" s="150"/>
+      <c r="I101" s="136"/>
+      <c r="J101" s="39"/>
       <c r="K101" s="78"/>
       <c r="L101" s="30"/>
-      <c r="M101" s="61"/>
+      <c r="M101" s="61" t="s">
+        <v>159</v>
+      </c>
       <c r="N101" s="61"/>
     </row>
     <row r="102" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A102" s="209" t="s">
         <v>7</v>
       </c>
-      <c r="B102" s="206">
-        <v>46124</v>
+      <c r="B102" s="210">
+        <v>46152</v>
       </c>
       <c r="C102" s="11"/>
       <c r="D102" s="12"/>
       <c r="E102" s="31"/>
-      <c r="F102" s="160"/>
-      <c r="G102" s="161"/>
-      <c r="H102" s="171"/>
+      <c r="F102" s="152"/>
+      <c r="G102" s="152"/>
+      <c r="H102" s="160"/>
       <c r="I102" s="25"/>
       <c r="J102" s="25"/>
-      <c r="K102" s="131"/>
+      <c r="K102" s="128"/>
       <c r="L102" s="31"/>
-      <c r="M102" s="61"/>
+      <c r="M102" s="61" t="s">
+        <v>160</v>
+      </c>
       <c r="N102" s="22"/>
     </row>
     <row r="103" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A103" s="56"/>
-      <c r="B103" s="210"/>
+      <c r="A103" s="211"/>
+      <c r="B103" s="212"/>
       <c r="C103" s="14" t="s">
         <v>11</v>
       </c>
-      <c r="D103" s="172"/>
+      <c r="D103" s="225"/>
       <c r="E103" s="22" t="s">
-        <v>167</v>
+        <v>201</v>
       </c>
       <c r="F103" s="83"/>
-      <c r="G103" s="67"/>
+      <c r="G103" s="83"/>
       <c r="H103" s="67" t="s">
-        <v>204</v>
+        <v>246</v>
       </c>
       <c r="I103" s="67"/>
       <c r="J103" s="38" t="s">
-        <v>141</v>
-      </c>
-      <c r="K103" s="15" t="s">
-        <v>162</v>
-      </c>
+        <v>200</v>
+      </c>
+      <c r="K103" s="15"/>
       <c r="L103" s="15"/>
-      <c r="M103" s="27"/>
+      <c r="M103" s="27" t="s">
+        <v>161</v>
+      </c>
       <c r="N103" s="25"/>
     </row>
     <row r="104" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A104" s="56"/>
-      <c r="B104" s="210"/>
+      <c r="A104" s="211"/>
+      <c r="B104" s="212"/>
       <c r="C104" s="14" t="s">
         <v>6</v>
       </c>
-      <c r="D104" s="186"/>
+      <c r="D104" s="224" t="s">
+        <v>235</v>
+      </c>
       <c r="E104" s="22" t="s">
-        <v>116</v>
-      </c>
-      <c r="F104" s="130"/>
-      <c r="G104" s="37"/>
+        <v>140</v>
+      </c>
+      <c r="F104" s="127"/>
+      <c r="G104" s="127"/>
       <c r="H104" s="37" t="s">
-        <v>205</v>
-      </c>
-      <c r="I104" s="173"/>
+        <v>247</v>
+      </c>
+      <c r="I104" s="161"/>
       <c r="J104" s="98"/>
       <c r="K104" s="81"/>
-      <c r="L104" s="168"/>
+      <c r="L104" s="157"/>
       <c r="M104" s="22"/>
       <c r="N104" s="65"/>
     </row>
     <row r="105" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A105" s="41"/>
-      <c r="B105" s="208"/>
-      <c r="C105" s="16"/>
+      <c r="A105" s="213"/>
+      <c r="B105" s="214"/>
+      <c r="C105" s="16" t="s">
+        <v>109</v>
+      </c>
       <c r="D105" s="17"/>
-      <c r="E105" s="140"/>
-      <c r="F105" s="163"/>
-      <c r="G105" s="140"/>
-      <c r="H105" s="140"/>
-      <c r="I105" s="140"/>
-      <c r="J105" s="41"/>
-      <c r="K105" s="110"/>
+      <c r="E105" s="22" t="s">
+        <v>202</v>
+      </c>
+      <c r="F105" s="154"/>
+      <c r="G105" s="154"/>
+      <c r="H105" s="136" t="s">
+        <v>248</v>
+      </c>
+      <c r="I105" s="136"/>
+      <c r="J105" s="41" t="s">
+        <v>173</v>
+      </c>
+      <c r="K105" s="108"/>
       <c r="L105" s="41"/>
       <c r="M105" s="26"/>
       <c r="N105" s="27"/>
     </row>
     <row r="106" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A106" s="209" t="s">
+      <c r="A106" s="181" t="s">
         <v>8</v>
       </c>
-      <c r="B106" s="206">
-        <v>46125</v>
+      <c r="B106" s="178">
+        <v>46153</v>
       </c>
       <c r="C106" s="11"/>
       <c r="D106" s="12"/>
       <c r="E106" s="19"/>
-      <c r="F106" s="144"/>
-      <c r="G106" s="44"/>
+      <c r="F106" s="139"/>
+      <c r="G106" s="139"/>
       <c r="H106" s="44"/>
       <c r="I106" s="44"/>
       <c r="J106" s="44"/>
@@ -4713,17 +4859,29 @@
       <c r="N106" s="22"/>
     </row>
     <row r="107" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A107" s="110"/>
-      <c r="B107" s="211"/>
-      <c r="C107" s="16"/>
+      <c r="A107" s="108"/>
+      <c r="B107" s="183"/>
+      <c r="C107" s="16" t="s">
+        <v>73</v>
+      </c>
       <c r="D107" s="17"/>
-      <c r="E107" s="18"/>
-      <c r="F107" s="145"/>
-      <c r="G107" s="43"/>
-      <c r="H107" s="43"/>
+      <c r="E107" s="197" t="s">
+        <v>105</v>
+      </c>
+      <c r="F107" s="140" t="s">
+        <v>32</v>
+      </c>
+      <c r="G107" s="140"/>
+      <c r="H107" s="43" t="s">
+        <v>249</v>
+      </c>
       <c r="I107" s="43"/>
-      <c r="J107" s="43"/>
-      <c r="K107" s="18"/>
+      <c r="J107" s="43" t="s">
+        <v>98</v>
+      </c>
+      <c r="K107" s="18" t="s">
+        <v>99</v>
+      </c>
       <c r="L107" s="18"/>
       <c r="M107" s="26"/>
       <c r="N107" s="22"/>
@@ -4732,122 +4890,107 @@
       <c r="A108" s="31" t="s">
         <v>9</v>
       </c>
-      <c r="B108" s="206">
-        <v>46126</v>
+      <c r="B108" s="178">
+        <v>46154</v>
       </c>
       <c r="C108" s="11" t="s">
-        <v>215</v>
+        <v>72</v>
       </c>
       <c r="D108" s="12"/>
-      <c r="E108" s="221" t="s">
-        <v>232</v>
-      </c>
-      <c r="F108" s="127"/>
-      <c r="G108" s="42"/>
+      <c r="E108" s="185" t="s">
+        <v>106</v>
+      </c>
+      <c r="F108" s="124"/>
+      <c r="G108" s="124"/>
       <c r="H108" s="42" t="s">
-        <v>240</v>
+        <v>250</v>
       </c>
       <c r="I108" s="42"/>
       <c r="J108" s="46" t="s">
-        <v>217</v>
-      </c>
-      <c r="K108" s="222">
-        <v>3.8</v>
-      </c>
-      <c r="L108" s="24" t="s">
-        <v>234</v>
-      </c>
+        <v>98</v>
+      </c>
+      <c r="K108" s="186" t="s">
+        <v>103</v>
+      </c>
+      <c r="L108" s="24"/>
       <c r="M108" s="22"/>
       <c r="N108" s="21"/>
     </row>
     <row r="109" spans="1:15" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A109" s="56"/>
-      <c r="B109" s="207"/>
-      <c r="C109" s="14" t="s">
-        <v>222</v>
-      </c>
-      <c r="D109" s="128"/>
-      <c r="E109" s="224" t="s">
-        <v>232</v>
-      </c>
-      <c r="F109" s="146"/>
-      <c r="G109" s="147"/>
-      <c r="H109" s="174" t="s">
-        <v>240</v>
-      </c>
-      <c r="I109" s="147"/>
-      <c r="J109" s="40" t="s">
-        <v>217</v>
-      </c>
-      <c r="K109" s="223">
-        <v>3.8</v>
-      </c>
-      <c r="L109" s="21" t="s">
-        <v>233</v>
-      </c>
+      <c r="B109" s="179"/>
+      <c r="C109" s="14"/>
+      <c r="D109" s="125"/>
+      <c r="E109" s="15"/>
+      <c r="F109" s="141"/>
+      <c r="G109" s="141"/>
+      <c r="H109" s="162"/>
+      <c r="I109" s="142"/>
+      <c r="J109" s="40"/>
+      <c r="K109" s="187"/>
+      <c r="L109" s="21"/>
       <c r="M109" s="22"/>
       <c r="N109" s="57"/>
     </row>
     <row r="110" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A110" s="56"/>
-      <c r="B110" s="210"/>
+      <c r="B110" s="182"/>
       <c r="C110" s="14"/>
-      <c r="D110" s="128"/>
+      <c r="D110" s="125"/>
       <c r="E110" s="15"/>
-      <c r="F110" s="129"/>
-      <c r="G110" s="38"/>
+      <c r="F110" s="126"/>
+      <c r="G110" s="126"/>
       <c r="H110" s="38"/>
       <c r="I110" s="38"/>
       <c r="J110" s="49"/>
-      <c r="K110" s="193"/>
+      <c r="K110" s="169"/>
       <c r="L110" s="79"/>
       <c r="M110" s="27"/>
       <c r="N110" s="88"/>
     </row>
     <row r="111" spans="1:15" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A111" s="41"/>
-      <c r="B111" s="208"/>
+      <c r="B111" s="180"/>
       <c r="C111" s="16" t="s">
         <v>3</v>
       </c>
-      <c r="D111" s="17"/>
-      <c r="E111" s="225" t="s">
-        <v>58</v>
-      </c>
-      <c r="F111" s="175"/>
-      <c r="G111" s="78"/>
+      <c r="D111" s="220" t="s">
+        <v>236</v>
+      </c>
+      <c r="E111" s="228" t="s">
+        <v>203</v>
+      </c>
+      <c r="F111" s="163" t="s">
+        <v>32</v>
+      </c>
+      <c r="G111" s="163"/>
       <c r="H111" s="78" t="s">
-        <v>206</v>
+        <v>251</v>
       </c>
       <c r="I111" s="78"/>
       <c r="J111" s="43" t="s">
-        <v>244</v>
+        <v>204</v>
       </c>
       <c r="K111" s="18"/>
-      <c r="L111" s="176"/>
+      <c r="L111" s="43" t="s">
+        <v>168</v>
+      </c>
       <c r="M111" s="94"/>
       <c r="N111" s="95"/>
     </row>
     <row r="113" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E113" s="112" t="s">
-        <v>32</v>
+      <c r="E113" s="110" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="114" spans="5:5" ht="110.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="E114" s="113" t="s">
-        <v>241</v>
+      <c r="E114" s="111" t="s">
+        <v>162</v>
       </c>
     </row>
   </sheetData>
-  <hyperlinks>
-    <hyperlink ref="H16" r:id="rId1" display="https://www.allocine.fr/personne/fichepersonne_gen_cpersonne=244522.html" xr:uid="{882407E6-55DA-4DFF-8C62-DDA3B506B666}"/>
-    <hyperlink ref="H8" r:id="rId2" display="https://www.allocine.fr/personne/fichepersonne_gen_cpersonne=795445.html" xr:uid="{9B728BDA-834A-4D3D-9B8D-58A5534893D5}"/>
-    <hyperlink ref="H12" r:id="rId3" display="https://www.allocine.fr/personne/fichepersonne_gen_cpersonne=616464.html" xr:uid="{D48C2977-A417-4209-B99D-E5976C8F1727}"/>
-    <hyperlink ref="H39" r:id="rId4" display="https://www.allocine.fr/personne/fichepersonne_gen_cpersonne=906041.html" xr:uid="{6A4B0B41-0CFC-4C89-B6E2-81AF9D557084}"/>
-    <hyperlink ref="H62" r:id="rId5" display="https://www.allocine.fr/personne/fichepersonne_gen_cpersonne=814383.html" xr:uid="{659854BB-4E75-46DF-9333-316B1CE6F3A3}"/>
-  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" scale="37" orientation="portrait" horizontalDpi="4294967293" verticalDpi="4294967293" r:id="rId6"/>
+  <pageSetup paperSize="9" scale="37" orientation="portrait" horizontalDpi="4294967293" verticalDpi="4294967293" r:id="rId1"/>
 </worksheet>
 </file>
 

--- a/outils/input/source.xlsx
+++ b/outils/input/source.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="26924"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/a386a22b2d8d1dbd/000 CINE CARBONNE 2026/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\_Boulots\Cine Carbonne\Site\Site_Github_rep\outils\input\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="642" documentId="8_{AF6E83F5-6B86-4BFF-B52F-88C43D9380DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{74BD99DB-20C4-441A-946B-3FD268B6E485}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A1B0632B-A064-4C93-9166-939838591789}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="587" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" tabRatio="587" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="389" uniqueCount="261">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="325" uniqueCount="222">
   <si>
     <t>Semaine</t>
   </si>
@@ -129,694 +129,577 @@
     <t>Amours chiennes VO</t>
   </si>
   <si>
+    <t>Réalisateur</t>
+  </si>
+  <si>
+    <t>Prix - Invités</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tout va bien DOC </t>
+  </si>
+  <si>
+    <t>ADH 4 € - Autres 5 €</t>
+  </si>
+  <si>
+    <t>La reine Margot - Patrice Chéreau</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Séance EPHAD HANDI </t>
+  </si>
+  <si>
+    <t>Marsupilami JP Famille</t>
+  </si>
+  <si>
+    <t>It's never over, Jeff Buckley VO DOC</t>
+  </si>
+  <si>
+    <t>Le retour du projectionniste VO DOC</t>
+  </si>
+  <si>
+    <t>Un été à la ferme DOC</t>
+  </si>
+  <si>
+    <t>Orphelin VO</t>
+  </si>
+  <si>
+    <t>Sans toi ni loi</t>
+  </si>
+  <si>
+    <t>Les choses de la vie - Sautet</t>
+  </si>
+  <si>
+    <t>James et la pêche géante JP reprise</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JP </t>
+  </si>
+  <si>
+    <t>Wong Kar-Wai - The grandmaster VO</t>
+  </si>
+  <si>
+    <t>La Garonne</t>
+  </si>
+  <si>
+    <t>Stand by me VO</t>
+  </si>
+  <si>
+    <t>Les contes du pommier JP</t>
+  </si>
+  <si>
+    <t>6 ou 7 nov Bruit du papier</t>
+  </si>
+  <si>
+    <t>Vol au-dessus d'un nid de coucou VO</t>
+  </si>
+  <si>
+    <t>L'odyssée de Céleste JP</t>
+  </si>
+  <si>
+    <t>La dame deShangaï VO</t>
+  </si>
+  <si>
+    <t>La marque du tueur VO</t>
+  </si>
+  <si>
+    <t>Compostelle</t>
+  </si>
+  <si>
+    <t>The drama VO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le goût des autres </t>
+  </si>
+  <si>
+    <t>J 28/05 soirée</t>
+  </si>
+  <si>
+    <t>Ciné Club du samedi 18h</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Scarlet et l'éternité JP ados à partir de 9/10 ans </t>
+  </si>
+  <si>
+    <t>Sorda VO</t>
+  </si>
+  <si>
+    <t>Nous l'orchestre DOC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C'est quoi l'amour ? </t>
+  </si>
+  <si>
+    <t>L'affaire Abdallah DOC</t>
+  </si>
+  <si>
+    <t>Ginza Cosmetics VO</t>
+  </si>
+  <si>
+    <t>Les fleurs du manguier VO</t>
+  </si>
+  <si>
+    <t>Drunken noodles VO</t>
+  </si>
+  <si>
+    <t>Dao 3h05</t>
+  </si>
+  <si>
+    <t>Elfie et les supers Elfkins JP</t>
+  </si>
+  <si>
+    <t>L'enfant bélier</t>
+  </si>
+  <si>
+    <t>Un balcon à Limoges</t>
+  </si>
+  <si>
+    <t>Le Maure de Karatas VO</t>
+  </si>
+  <si>
+    <t>Pluie noire VO</t>
+  </si>
+  <si>
+    <t>Depardon et l'Afrique DOC</t>
+  </si>
+  <si>
+    <t>Pour le plaisir</t>
+  </si>
+  <si>
+    <t>Sauvons les meubles</t>
+  </si>
+  <si>
+    <t>The new west VO</t>
+  </si>
+  <si>
+    <t>Cinque secondi VO</t>
+  </si>
+  <si>
+    <t>Cosmos VO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ciné goûter JP </t>
+  </si>
+  <si>
+    <t>CM5 : Poisson rouge - Fiction - 03'00 (du 3/6 au 7/7)</t>
+  </si>
+  <si>
+    <t>CM6 : Plan V - Documentaire - 03'00 (du 3/6 au 7/7)</t>
+  </si>
+  <si>
+    <t>TU 3 €</t>
+  </si>
+  <si>
+    <t>JP Famille TU 4,50 €</t>
+  </si>
+  <si>
+    <t>TU 4,50 €</t>
+  </si>
+  <si>
+    <t>Ouverture Cannes 2026</t>
+  </si>
+  <si>
+    <t>TU 5 €</t>
+  </si>
+  <si>
+    <t>Ciné Club ou Ciné DOC du samedi 18h</t>
+  </si>
+  <si>
+    <t>Ciné Jeunes du samedi 18h</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ciné Jeunes du samedi 18h </t>
+  </si>
+  <si>
+    <t>Le diable s'habille en Prada 2 VO</t>
+  </si>
+  <si>
+    <t>La vénus électrique Ouverture Cannes 2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The criminals VO? </t>
+  </si>
+  <si>
+    <t>Monte là-dessus Harold Lloyd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Juste une illusion </t>
+  </si>
+  <si>
+    <t>Le dernier pour la route VO</t>
+  </si>
+  <si>
+    <t>Super Mario Galaxy Le film jP</t>
+  </si>
+  <si>
+    <t>Tout va super</t>
+  </si>
+  <si>
+    <t>Father VO Prix Sang neuf Reims Polar 2026</t>
+  </si>
+  <si>
+    <t>L'affaire Zanetti</t>
+  </si>
+  <si>
+    <t>Le garçon qui faisait danser les collines VO Prix Carbonne</t>
+  </si>
+  <si>
+    <t>Nouveaux copains à Puffin Rock JP 1h19 3ans</t>
+  </si>
+  <si>
+    <t>The Christophers VO</t>
+  </si>
+  <si>
+    <t>D'un monde à l'autre DOC</t>
+  </si>
+  <si>
+    <t>L'illusion de Yakushima VO</t>
+  </si>
+  <si>
+    <t>Sur la route d'Omaha VO Deauville 2025 Prix du jury</t>
+  </si>
+  <si>
+    <t>Ulysse Clôture Un certain regard Cannes 2026</t>
+  </si>
+  <si>
+    <t>L'abandon Cannes 2026 Hors compétition</t>
+  </si>
+  <si>
+    <t>Histoires parralèles Cannes 2026 Compétition</t>
+  </si>
+  <si>
+    <t>L'être aimé VO Cannes 2026 Compétition</t>
+  </si>
+  <si>
+    <t>Elise sous emprise</t>
+  </si>
+  <si>
+    <t>CHaO JP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Star wars The Mandalorian and Grogu VFVO </t>
+  </si>
+  <si>
+    <t>Autofiction VO Cannes 2026 Compétition</t>
+  </si>
+  <si>
+    <t>Les goûteuses d'Hitler VO</t>
+  </si>
+  <si>
+    <t>Vanilla VO</t>
+  </si>
+  <si>
+    <t>All you need is kill Animé ados</t>
+  </si>
+  <si>
+    <t>Morte e vida Madalena VO</t>
+  </si>
+  <si>
+    <t>Colony VO Cannes 2026 Hors compétition</t>
+  </si>
+  <si>
+    <t>Mata</t>
+  </si>
+  <si>
+    <t>L'objet du délit Cannes 2026 Hors Compétition</t>
+  </si>
+  <si>
+    <t>Le virtuose VO</t>
+  </si>
+  <si>
+    <t>Cocotte VO</t>
+  </si>
+  <si>
+    <t>Father VO</t>
+  </si>
+  <si>
+    <t>A bras le corps (Silent rebellion)</t>
+  </si>
+  <si>
+    <t>Le dernier souffle d'un yakusa VO Animé adulte Annecy 2025</t>
+  </si>
+  <si>
+    <t>Le pont VO</t>
+  </si>
+  <si>
+    <t>Le coyote VO</t>
+  </si>
+  <si>
+    <t>La bataille de Gaulle L'âge de fer 2h40</t>
+  </si>
+  <si>
+    <t>Scarie movie VF</t>
+  </si>
+  <si>
+    <t>Anna et les enfants</t>
+  </si>
+  <si>
+    <t>The plague VO Prix de la critique Deauville 2025</t>
+  </si>
+  <si>
+    <t>En nous DOC</t>
+  </si>
+  <si>
+    <t>Bait VO</t>
+  </si>
+  <si>
+    <t>Francesca &amp; Giovanni VO</t>
+  </si>
+  <si>
+    <t>La tsigane Sur les routes avec Tameratong VO DOC</t>
+  </si>
+  <si>
+    <t>Toutes mes sœurs VO DOC</t>
+  </si>
+  <si>
+    <t>16h30</t>
+  </si>
+  <si>
+    <t>Le vertige Cannes Quinzaine des cinéastes</t>
+  </si>
+  <si>
+    <t>L'abandon</t>
+  </si>
+  <si>
+    <t>10h</t>
+  </si>
+  <si>
+    <t>SCOL</t>
+  </si>
+  <si>
+    <t>14h</t>
+  </si>
+  <si>
+    <t>Filmo 3,50 €</t>
+  </si>
+  <si>
+    <t>9h30</t>
+  </si>
+  <si>
+    <t>Gratuit</t>
+  </si>
+  <si>
+    <t>14h?</t>
+  </si>
+  <si>
+    <t>Gratuit - Voir avexc l'école pour précisions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">L'être aimé VO Cannes 2026 Compétition </t>
+  </si>
+  <si>
     <t>VO</t>
   </si>
   <si>
-    <t>Réalisateur</t>
-  </si>
-  <si>
-    <t>Prix - Invités</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tout va bien DOC </t>
-  </si>
-  <si>
-    <t>ADH 4 € - Autres 5 €</t>
-  </si>
-  <si>
-    <t>La reine Margot - Patrice Chéreau</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Séance EPHAD HANDI </t>
-  </si>
-  <si>
-    <t>Marsupilami JP Famille</t>
-  </si>
-  <si>
-    <t>It's never over, Jeff Buckley VO DOC</t>
-  </si>
-  <si>
-    <t>Le retour du projectionniste VO DOC</t>
-  </si>
-  <si>
-    <t>Jeune pousse JP TU 3 €</t>
-  </si>
-  <si>
-    <t>Un été à la ferme DOC</t>
-  </si>
-  <si>
-    <t>Véronique DOC</t>
-  </si>
-  <si>
-    <t>Deux femmes et quelques hommes</t>
-  </si>
-  <si>
-    <t>Le testament d'Ann Lee VO</t>
-  </si>
-  <si>
-    <t>Orphelin VO</t>
-  </si>
-  <si>
-    <t>Sans toi ni loi</t>
-  </si>
-  <si>
-    <t>Les choses de la vie - Sautet</t>
-  </si>
-  <si>
-    <t>James et la pêche géante JP reprise</t>
-  </si>
-  <si>
-    <t xml:space="preserve">JP </t>
-  </si>
-  <si>
-    <t>Ciné Doc du samedi 18h</t>
-  </si>
-  <si>
-    <t>Wong Kar-Wai - The grandmaster VO</t>
-  </si>
-  <si>
-    <t>La Garonne</t>
-  </si>
-  <si>
-    <t>Stand by me VO</t>
-  </si>
-  <si>
-    <t>Romeria VO</t>
-  </si>
-  <si>
-    <t>Les contes du pommier JP</t>
-  </si>
-  <si>
-    <t>Morlaix</t>
-  </si>
-  <si>
-    <t>Une fille en or</t>
-  </si>
-  <si>
-    <t>La poupée</t>
-  </si>
-  <si>
-    <t>SCOL</t>
-  </si>
-  <si>
-    <t>9h30</t>
-  </si>
-  <si>
-    <t>6 ou 7 nov Bruit du papier</t>
-  </si>
-  <si>
-    <t>Anémone Les racines du mensonge VO</t>
-  </si>
-  <si>
-    <t>L'ile de la demoiselle</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Julian </t>
-  </si>
-  <si>
-    <t>Vol au-dessus d'un nid de coucou VO</t>
-  </si>
-  <si>
-    <t>L'odyssée de Céleste JP</t>
-  </si>
-  <si>
-    <t>La dame deShangaï VO</t>
-  </si>
-  <si>
-    <t>La marque du tueur VO</t>
-  </si>
-  <si>
-    <t>Compostelle</t>
-  </si>
-  <si>
-    <t>Super Mario Galaxy Le film JP</t>
-  </si>
-  <si>
-    <t>The drama VO</t>
-  </si>
-  <si>
-    <t>Mauvaise pioche</t>
-  </si>
-  <si>
-    <t>Nuestra tierra VO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Le goût des autres </t>
-  </si>
-  <si>
-    <t>Le secret du loup d'Ethiopie JP Famille</t>
-  </si>
-  <si>
-    <t>Peppa au cinéma La famille s'agrandit JP TU 3 €</t>
-  </si>
-  <si>
-    <t>Cocorico 2</t>
-  </si>
-  <si>
-    <t>L'enfant du désert JP Famillle</t>
-  </si>
-  <si>
-    <t>Le cri des gardes VO</t>
-  </si>
-  <si>
-    <t>J 28/05 soirée</t>
-  </si>
-  <si>
-    <t>Ciné Jeunes du samedi 18h - JP  Ados</t>
+    <t>Prix Sang neuf Reims Polar 2026</t>
+  </si>
+  <si>
+    <t>Father</t>
+  </si>
+  <si>
+    <t>Tereza Nvotova</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Cannes 2026 Hors compétition</t>
+  </si>
+  <si>
+    <t>Cannes 2026 Hors compétition</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cannes 2026 Compétition </t>
+  </si>
+  <si>
+    <t xml:space="preserve">L'être aimé </t>
+  </si>
+  <si>
+    <t>L'odyssée de Céleste</t>
+  </si>
+  <si>
+    <t>Histoires parralèles</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Cannes 2026 Compétition</t>
+  </si>
+  <si>
+    <t>The new west</t>
+  </si>
+  <si>
+    <t>Cannes 2026 Compétition</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Prix Carbonne</t>
+  </si>
+  <si>
+    <t>Le garçon qui faisait danser les collines</t>
+  </si>
+  <si>
+    <t>Nouveaux copains à Puffin Rock</t>
+  </si>
+  <si>
+    <t>Star wars The Mandalorian and Grogu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VO </t>
+  </si>
+  <si>
+    <t>CHaO</t>
+  </si>
+  <si>
+    <t>Autofiction</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> (à partir de 14h)</t>
+  </si>
+  <si>
+    <t>La vénus électrique</t>
+  </si>
+  <si>
+    <t>L'être aimé</t>
+  </si>
+  <si>
+    <t>D'un monde à l'autre</t>
+  </si>
+  <si>
+    <t>Colony</t>
+  </si>
+  <si>
+    <t>Super Mario Galaxy Le film</t>
+  </si>
+  <si>
+    <t>L'objet du délit</t>
+  </si>
+  <si>
+    <t>Cannes 2026 Hors Compétition</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le vertige </t>
+  </si>
+  <si>
+    <t>Cannes 2026 Cannes Quinzaine des cinéastes</t>
+  </si>
+  <si>
+    <t>The Christophers</t>
+  </si>
+  <si>
+    <t>Deauville 2025 Prix du jury</t>
+  </si>
+  <si>
+    <t>Sur la route d'Omaha</t>
   </si>
   <si>
     <t>VF</t>
   </si>
   <si>
-    <t>CM3 : Super V - Comédie - 02'00 (du 6/5 au 2/6)</t>
-  </si>
-  <si>
-    <t>CM4 : Des filles et des chiens - Comédie - 05'00 (du 6/5 au 2/6)</t>
-  </si>
-  <si>
-    <t>CM1 : Je ne suis pas  - Film militant - 04'00</t>
-  </si>
-  <si>
-    <t>CM2 : Le futur sera chauve - Animation - 05'36</t>
-  </si>
-  <si>
-    <t>Ciné Club du samedi 18h</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Scarlet et l'éternité JP ados à partir de 9/10 ans </t>
-  </si>
-  <si>
-    <t>18h30</t>
-  </si>
-  <si>
-    <t>gratuit</t>
-  </si>
-  <si>
-    <t>suivi d'un échange avec G Biarc psychologue et FCPE</t>
-  </si>
-  <si>
-    <t>Good luck have fun don't die</t>
-  </si>
-  <si>
-    <t>Filmo 3,50 €</t>
-  </si>
-  <si>
-    <t>Bily Elliot</t>
-  </si>
-  <si>
-    <t>Ec élem Chanfreau</t>
-  </si>
-  <si>
-    <t>Spectacle FCPE</t>
-  </si>
-  <si>
-    <t>Servcice culturel</t>
-  </si>
-  <si>
-    <t>TER</t>
-  </si>
-  <si>
-    <t>Théâtre 107</t>
-  </si>
-  <si>
-    <t>Sorda VO</t>
-  </si>
-  <si>
-    <t>Nous l'orchestre DOC</t>
-  </si>
-  <si>
-    <t>Sukkwan island VO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C'est quoi l'amour ? </t>
-  </si>
-  <si>
-    <t>Mi amor</t>
-  </si>
-  <si>
-    <t>Mon grand frère et moi VO</t>
-  </si>
-  <si>
-    <t>Mi amor avec EC</t>
-  </si>
-  <si>
-    <t>Elise sous emprise</t>
-  </si>
-  <si>
-    <t>The world of love VO</t>
-  </si>
-  <si>
-    <t>La vénus électrique Ouverture Cannes 2026 2 séances</t>
-  </si>
-  <si>
-    <t>ChaO JP</t>
-  </si>
-  <si>
-    <t>L'affaire Abdallah DOC</t>
-  </si>
-  <si>
-    <t>Projet dernière chance VO</t>
-  </si>
-  <si>
-    <t>Juste une ilusion</t>
-  </si>
-  <si>
-    <t>Bagarre</t>
-  </si>
-  <si>
-    <t>La fille du Kombini VO</t>
-  </si>
-  <si>
-    <t>Truly naked VO</t>
-  </si>
-  <si>
-    <t>La petite graine</t>
-  </si>
-  <si>
-    <t>Hayat VO</t>
-  </si>
-  <si>
-    <t>Affection affection</t>
-  </si>
-  <si>
-    <t>L'eden</t>
-  </si>
-  <si>
-    <t>Ginza Cosmetics VO</t>
-  </si>
-  <si>
-    <t>Mickaël VO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pour le meilleur </t>
-  </si>
-  <si>
-    <t>L'arnaqueuse</t>
-  </si>
-  <si>
-    <t>A voix basse VO</t>
-  </si>
-  <si>
-    <t>Les fleurs du manguier VO</t>
-  </si>
-  <si>
-    <t>Première ligne</t>
-  </si>
-  <si>
-    <t>Caravane VO</t>
-  </si>
-  <si>
-    <t>Soumsoum la nuit des astres VO</t>
-  </si>
-  <si>
-    <t>Drunken noodles VO</t>
-  </si>
-  <si>
-    <t>Le diable s'habille en Prada 2 VF ou VO</t>
-  </si>
-  <si>
-    <t>Die my love VO</t>
-  </si>
-  <si>
-    <t>Vivaldi et moi VO</t>
-  </si>
-  <si>
-    <t>Le 13e round VO</t>
-  </si>
-  <si>
-    <t>Dao 3h05</t>
-  </si>
-  <si>
-    <t>Elfie et les supers Elfkins JP</t>
-  </si>
-  <si>
-    <t>L'enfant bélier</t>
-  </si>
-  <si>
-    <t>Un balcon à Limoges</t>
-  </si>
-  <si>
-    <t>Le Maure de Karatas VO</t>
-  </si>
-  <si>
-    <t>Pluie noire VO</t>
-  </si>
-  <si>
-    <t>Depardon et l'Afrique DOC</t>
-  </si>
-  <si>
-    <t>Pour le plaisir</t>
-  </si>
-  <si>
-    <t>The criminals VO? avec EC</t>
-  </si>
-  <si>
-    <t>Mortal Kombat 2 VF</t>
-  </si>
-  <si>
-    <t>Sauvons les meubles</t>
-  </si>
-  <si>
-    <t>The new west VO</t>
-  </si>
-  <si>
-    <t>Cinque secondi VO</t>
-  </si>
-  <si>
-    <t>Cosmos VO</t>
-  </si>
-  <si>
-    <t>La corde au cou VO avec EC</t>
-  </si>
-  <si>
-    <t>Juste une illusion</t>
-  </si>
-  <si>
-    <t>17h</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ciné goûter JP </t>
-  </si>
-  <si>
-    <t>Cocotte VO</t>
-  </si>
-  <si>
-    <t>20h30</t>
-  </si>
-  <si>
-    <t>Good luck have fun don't die VO</t>
-  </si>
-  <si>
-    <t>10h</t>
-  </si>
-  <si>
-    <t>Au fil de l'eau</t>
-  </si>
-  <si>
-    <t>SCOL EauC</t>
-  </si>
-  <si>
-    <t>Ec mat Chanfreau</t>
-  </si>
-  <si>
-    <t>MacPat le chat chanteur</t>
-  </si>
-  <si>
-    <t>Ec Saint julien</t>
-  </si>
-  <si>
-    <t>SCOL Liste</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ec Hellé </t>
-  </si>
-  <si>
-    <t>Le roi des masques</t>
-  </si>
-  <si>
-    <t>SCOL EetC</t>
-  </si>
-  <si>
-    <t>Lautignac</t>
-  </si>
-  <si>
-    <t>CM5 : Poisson rouge - Fiction - 03'00 (du 3/6 au 7/7)</t>
-  </si>
-  <si>
-    <t>CM6 : Plan V - Documentaire - 03'00 (du 3/6 au 7/7)</t>
-  </si>
-  <si>
-    <t>CM3</t>
-  </si>
-  <si>
-    <t>CM4</t>
-  </si>
-  <si>
-    <t>CM5</t>
-  </si>
-  <si>
-    <t>14h</t>
-  </si>
-  <si>
-    <t>Dans la roue du petit Prince</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Contes sur moi </t>
-  </si>
-  <si>
-    <t xml:space="preserve">MJC </t>
-  </si>
-  <si>
-    <t>Binet Danse</t>
-  </si>
-  <si>
-    <t>à préciser</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SCOL avec Vélo 107 </t>
-  </si>
-  <si>
-    <t>film récupéré par Ciné Carbonne EEPU Chanfreau</t>
-  </si>
-  <si>
-    <t>film récupéré  par Ciné Carbonne EEPU Hellé</t>
-  </si>
-  <si>
-    <t>Yannick Billard</t>
-  </si>
-  <si>
-    <t>Coup de cœur</t>
-  </si>
-  <si>
-    <t>Découverte</t>
-  </si>
-  <si>
-    <t>Coup de cœur DOC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sukkwan island </t>
-  </si>
-  <si>
-    <t xml:space="preserve">La fille du Kombini </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nous l'orchestre </t>
-  </si>
-  <si>
-    <t>TU 3 €</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jeune pousse </t>
-  </si>
-  <si>
-    <t xml:space="preserve">L'odyssée de Céleste </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sorda </t>
-  </si>
-  <si>
-    <t>Partenariat Empreinte Carbonne</t>
-  </si>
-  <si>
-    <t xml:space="preserve">La corde au cou </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mi amor </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mon grand frère et moi </t>
-  </si>
-  <si>
-    <t>JP Famille</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Le cri des gardes </t>
-  </si>
-  <si>
-    <t xml:space="preserve">L'enfant du désert </t>
-  </si>
-  <si>
-    <t>JP Famille TU 4,50 €</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Super Mario Galaxy Le film </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nuestra tierra </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Le secret du loup d'Ethiopie </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Projet dernière chance </t>
-  </si>
-  <si>
-    <t xml:space="preserve">The world of love </t>
-  </si>
-  <si>
-    <t>Prtenariat FCPE Semaine moins d'écrans</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Conférence filmée Serge Tisseron </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Soumsoum la nuit des astres </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Elfie et les supers Elfkins </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hayat </t>
-  </si>
-  <si>
-    <t>TU 4,50 €</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Romeria </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cocotte </t>
-  </si>
-  <si>
-    <t>Ouverture Cannes 2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">La vénus électrique </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Le diable s'habille en Prada 2 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Vol au-dessus d'un nid de coucou </t>
-  </si>
-  <si>
-    <t xml:space="preserve">ChaO </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Vivaldi et moi </t>
-  </si>
-  <si>
-    <t>Vladimir de Fontenay</t>
-  </si>
-  <si>
-    <t>Yûho Ishibashi</t>
-  </si>
-  <si>
-    <t>Philippe Béziat</t>
-  </si>
-  <si>
-    <t>Gore Verbinski</t>
-  </si>
-  <si>
-    <t>G Jugnot</t>
+    <t>La bataille de Gaulle L'âge de fer</t>
+  </si>
+  <si>
+    <t>Ulysse</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Clôture Un certain regard Cannes 2026 </t>
+  </si>
+  <si>
+    <t>Scarlet et l'éternité</t>
+  </si>
+  <si>
+    <t>L'illusion de Yakushima</t>
+  </si>
+  <si>
+    <t>Vincent Garenq</t>
+  </si>
+  <si>
+    <t>Rodrigo Sorogoyen</t>
   </si>
   <si>
     <t>Kid Koala</t>
   </si>
   <si>
-    <t>Olivier Nakache, Eric Toledano</t>
-  </si>
-  <si>
-    <t>Diek Grobler</t>
-  </si>
-  <si>
-    <t>Anastasia Sokolova</t>
-  </si>
-  <si>
-    <t>Eva Libertad Garcia</t>
-  </si>
-  <si>
-    <t>Gus Van Sant</t>
-  </si>
-  <si>
-    <t>Guillaume Nicloux</t>
-  </si>
-  <si>
-    <t>Yann Samuell</t>
-  </si>
-  <si>
-    <t>Ryôta Nakano</t>
-  </si>
-  <si>
-    <t>Aaron Horvarth</t>
-  </si>
-  <si>
-    <t>Lucrecia Martel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Michaël </t>
-  </si>
-  <si>
-    <t>Antoine Fuqua</t>
-  </si>
-  <si>
-    <t>Baptiste Deturche</t>
+    <t> Asghar Farhadi</t>
+  </si>
+  <si>
+    <t>Patrick Cassir</t>
+  </si>
+  <si>
+    <t>Kate Beecroft</t>
+  </si>
+  <si>
+    <t>Leonardo Di Costanzo</t>
+  </si>
+  <si>
+    <t>Rémi Chayé</t>
+  </si>
+  <si>
+    <t>Reem Kherici</t>
+  </si>
+  <si>
+    <t>Georgi M. Unkovski</t>
+  </si>
+  <si>
+    <t>Jeremy Purcell</t>
+  </si>
+  <si>
+    <t>Jon Favreau</t>
+  </si>
+  <si>
+    <t>Yasuhiro Aoki</t>
+  </si>
+  <si>
+    <t>Pedro Almodovar</t>
+  </si>
+  <si>
+    <t>Pierre Salvadori</t>
+  </si>
+  <si>
+    <t>Jérémie Renier</t>
   </si>
   <si>
     <t>Fabien Gorgeart</t>
   </si>
   <si>
-    <t>Claire Denis</t>
-  </si>
-  <si>
-    <t>Gilles de Maistre</t>
-  </si>
-  <si>
-    <t>Nils Skapans</t>
-  </si>
-  <si>
-    <t>Phil Lord</t>
-  </si>
-  <si>
-    <t>Ga Eun Yoon</t>
-  </si>
-  <si>
-    <t>Mahamat-Saleh Aroun</t>
-  </si>
-  <si>
-    <t>Stephen Daldry</t>
-  </si>
-  <si>
-    <t>Ute von Munchow-Pohl</t>
-  </si>
-  <si>
-    <t>Marie-Castille Mention-Schaar</t>
-  </si>
-  <si>
-    <t>Marie Rémond</t>
-  </si>
-  <si>
-    <t>Zeki Demurkubuz</t>
-  </si>
-  <si>
-    <t>Carla Simon</t>
-  </si>
-  <si>
-    <t>György Palfi</t>
-  </si>
-  <si>
-    <t>Pierre Salvadori</t>
-  </si>
-  <si>
-    <t>Milos Forman</t>
-  </si>
-  <si>
-    <t>David Frankel</t>
-  </si>
-  <si>
-    <t>Yasuhiro Aoki</t>
-  </si>
-  <si>
-    <t>Mohammad Ali Soleymanzadeh</t>
-  </si>
-  <si>
-    <t>Wu Tian-Ming</t>
-  </si>
-  <si>
-    <t>Damiano Michieletto</t>
-  </si>
-  <si>
-    <t>The new west, Histoires parallèles, L'abandon, L'être aimé, ChaO, Nous l'orchestre, Star wars The Mandalorian and Grogu, Autofiction, Les goûteuses d'Hitler, Maximilien Kolbe, Vanilla, Mata, L'objet du délit, Tout va super, La virtuose, Father, Le dernier souffle d'un yakusa, La bataille de Gaulle L'âge de fer, The plague, Le garçon qui faisait danser les collines, L'affaire Zanetti...</t>
+    <t>Sang-Ho Yeon</t>
+  </si>
+  <si>
+    <t> Aaron Horvath</t>
+  </si>
+  <si>
+    <t> Agnès Jaoui</t>
+  </si>
+  <si>
+    <t>Quentin Dupieux</t>
+  </si>
+  <si>
+    <t>Steven Soderbergh</t>
+  </si>
+  <si>
+    <t>Cole Webley</t>
+  </si>
+  <si>
+    <t>pedro almodovar</t>
+  </si>
+  <si>
+    <t>Antonin Baudry</t>
+  </si>
+  <si>
+    <t>Laetitia Masson</t>
+  </si>
+  <si>
+    <t>Mamoru Hosoda</t>
+  </si>
+  <si>
+    <t>Naomi Kawase</t>
+  </si>
+  <si>
+    <t>Minuscule</t>
+  </si>
+  <si>
+    <t>Zootopia 2</t>
+  </si>
+  <si>
+    <t>Tout en haut du monde</t>
+  </si>
+  <si>
+    <t>Etablissement La Grange (à partir de 14h)</t>
+  </si>
+  <si>
+    <t>Rencontres vidéos scolaires</t>
   </si>
 </sst>
 </file>
@@ -969,16 +852,15 @@
       <family val="2"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
       <sz val="8"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Montserrat"/>
     </font>
   </fonts>
   <fills count="16">
@@ -1056,13 +938,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5"/>
+        <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9"/>
+        <fgColor theme="5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1267,7 +1149,7 @@
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="241">
+  <cellXfs count="244">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -1689,12 +1571,8 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1757,15 +1635,12 @@
     <xf numFmtId="8" fontId="8" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="14" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="13" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -1775,40 +1650,10 @@
     <xf numFmtId="0" fontId="6" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="14" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="6" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="6" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="6" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="6" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="6" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="5" fillId="13" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1820,9 +1665,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -1839,9 +1681,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="2" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1883,39 +1722,70 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="6" fontId="8" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="4" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="14" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="14" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="13" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="13" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="14" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="13" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf numFmtId="0" fontId="5" fillId="14" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="15" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1923,30 +1793,45 @@
     <xf numFmtId="0" fontId="9" fillId="15" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="15" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="12" fillId="15" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="15" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="15" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="6" fontId="8" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="6" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="6" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="6" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="6" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="6" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="6" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="2"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="2" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Lien hypertexte" xfId="2" builtinId="8"/>
@@ -1981,9 +1866,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Thème Office 2013 – 2022">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Thème Office">
   <a:themeElements>
-    <a:clrScheme name="Office 2013 - 2022">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -2021,7 +1906,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2013 - 2022">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -2127,7 +2012,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2013 - 2022">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -2269,7 +2154,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -2281,62 +2166,54 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:O114"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="10.88671875" style="159" customWidth="1"/>
-    <col min="3" max="3" width="8.33203125" customWidth="1"/>
+    <col min="2" max="2" width="10.85546875" style="157" customWidth="1"/>
+    <col min="3" max="3" width="8.28515625" customWidth="1"/>
     <col min="4" max="4" width="5" style="112" customWidth="1"/>
-    <col min="5" max="5" width="69.5546875" style="3" customWidth="1"/>
-    <col min="6" max="6" width="7.33203125" style="85" customWidth="1"/>
-    <col min="7" max="7" width="6.88671875" style="85" customWidth="1"/>
-    <col min="8" max="8" width="33.5546875" style="3" customWidth="1"/>
-    <col min="9" max="9" width="79.109375" style="3" customWidth="1"/>
-    <col min="10" max="10" width="35.21875" style="2" customWidth="1"/>
-    <col min="11" max="11" width="20.77734375" style="2" customWidth="1"/>
+    <col min="5" max="5" width="69.5703125" style="3" customWidth="1"/>
+    <col min="6" max="6" width="7.28515625" style="85" customWidth="1"/>
+    <col min="7" max="7" width="6.85546875" style="85" customWidth="1"/>
+    <col min="8" max="8" width="33.5703125" style="3" customWidth="1"/>
+    <col min="9" max="9" width="79.140625" style="3" customWidth="1"/>
+    <col min="10" max="10" width="35.28515625" style="2" customWidth="1"/>
+    <col min="11" max="11" width="20.7109375" style="2" customWidth="1"/>
     <col min="12" max="12" width="54" style="2" customWidth="1"/>
-    <col min="13" max="13" width="59.21875" style="2" customWidth="1"/>
-    <col min="14" max="14" width="92.5546875" customWidth="1"/>
-    <col min="15" max="15" width="43.88671875" customWidth="1"/>
+    <col min="13" max="13" width="59.28515625" style="2" customWidth="1"/>
+    <col min="14" max="14" width="92.5703125" customWidth="1"/>
+    <col min="15" max="15" width="43.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
       <c r="E1" s="101" t="s">
-        <v>86</v>
-      </c>
-      <c r="F1" s="103" t="s">
-        <v>84</v>
-      </c>
+        <v>81</v>
+      </c>
+      <c r="F1" s="103"/>
       <c r="G1" s="102"/>
       <c r="H1" s="103"/>
       <c r="I1" s="101"/>
-      <c r="J1" s="101" t="s">
-        <v>168</v>
-      </c>
-      <c r="K1" s="155"/>
+      <c r="J1" s="101"/>
+      <c r="K1" s="153"/>
       <c r="L1" s="101"/>
     </row>
-    <row r="2" spans="1:14" s="1" customFormat="1" ht="15.45" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B2" s="160"/>
+    <row r="2" spans="1:14" s="1" customFormat="1" ht="15.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B2" s="158"/>
       <c r="D2" s="113"/>
       <c r="E2" s="101" t="s">
-        <v>87</v>
-      </c>
-      <c r="F2" s="193" t="s">
-        <v>85</v>
-      </c>
+        <v>82</v>
+      </c>
+      <c r="F2" s="180"/>
       <c r="G2" s="104"/>
       <c r="H2" s="105"/>
       <c r="I2" s="101"/>
-      <c r="J2" s="101" t="s">
-        <v>169</v>
-      </c>
-      <c r="K2" s="155"/>
+      <c r="J2" s="101"/>
+      <c r="K2" s="153"/>
       <c r="L2" s="101"/>
       <c r="M2" s="6"/>
     </row>
-    <row r="3" spans="1:14" s="71" customFormat="1" ht="21.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:14" s="71" customFormat="1" ht="21.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="1"/>
-      <c r="B3" s="160"/>
+      <c r="B3" s="158"/>
       <c r="D3" s="114"/>
       <c r="E3" s="72" t="s">
         <v>14</v>
@@ -2348,10 +2225,10 @@
         <v>13</v>
       </c>
       <c r="H3" s="121" t="s">
+        <v>31</v>
+      </c>
+      <c r="I3" s="75" t="s">
         <v>32</v>
-      </c>
-      <c r="I3" s="75" t="s">
-        <v>33</v>
       </c>
       <c r="J3" s="73" t="s">
         <v>15</v>
@@ -2364,12 +2241,12 @@
       </c>
       <c r="M3" s="74"/>
     </row>
-    <row r="4" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="161" t="s">
+    <row r="4" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="159" t="s">
         <v>0</v>
       </c>
-      <c r="B4" s="162">
-        <v>46155</v>
+      <c r="B4" s="160">
+        <v>46183</v>
       </c>
       <c r="C4" s="7"/>
       <c r="D4" s="8"/>
@@ -2382,53 +2259,41 @@
       <c r="K4" s="70"/>
       <c r="L4" s="70"/>
       <c r="M4" s="62">
-        <v>46127</v>
+        <v>46155</v>
       </c>
       <c r="N4" s="63" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A5" s="163" t="s">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A5" s="161" t="s">
         <v>1</v>
       </c>
-      <c r="B5" s="164">
-        <v>46155</v>
-      </c>
-      <c r="C5" s="229" t="s">
-        <v>178</v>
-      </c>
+      <c r="B5" s="162">
+        <v>46183</v>
+      </c>
+      <c r="C5" s="206"/>
       <c r="D5" s="12"/>
-      <c r="E5" s="230" t="s">
-        <v>174</v>
-      </c>
+      <c r="E5" s="81"/>
       <c r="F5" s="123"/>
       <c r="G5" s="123"/>
-      <c r="H5" s="42" t="s">
-        <v>182</v>
-      </c>
+      <c r="H5" s="42"/>
       <c r="I5" s="42"/>
-      <c r="J5" s="42" t="s">
-        <v>179</v>
-      </c>
-      <c r="K5" s="13" t="s">
-        <v>91</v>
-      </c>
-      <c r="L5" s="13" t="s">
-        <v>181</v>
-      </c>
+      <c r="J5" s="42"/>
+      <c r="K5" s="13"/>
+      <c r="L5" s="13"/>
       <c r="M5" s="55" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="N5" s="22" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.3">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A6" s="27"/>
-      <c r="B6" s="165"/>
+      <c r="B6" s="163"/>
       <c r="C6" s="14"/>
-      <c r="D6" s="198"/>
+      <c r="D6" s="184"/>
       <c r="E6" s="15"/>
       <c r="F6" s="124"/>
       <c r="G6" s="124"/>
@@ -2438,17 +2303,17 @@
       <c r="K6" s="15"/>
       <c r="L6" s="15"/>
       <c r="M6" s="55" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="N6" s="22" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.3">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A7" s="27"/>
-      <c r="B7" s="165"/>
+      <c r="B7" s="163"/>
       <c r="C7" s="14"/>
-      <c r="D7" s="198"/>
+      <c r="D7" s="184"/>
       <c r="E7" s="15"/>
       <c r="F7" s="124"/>
       <c r="G7" s="124"/>
@@ -2457,187 +2322,197 @@
       <c r="J7" s="38"/>
       <c r="K7" s="15"/>
       <c r="L7" s="15"/>
-      <c r="M7" s="55" t="s">
-        <v>102</v>
-      </c>
-      <c r="N7" s="26" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="8" spans="1:14" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="M7" s="55"/>
+      <c r="N7" s="66" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="41"/>
-      <c r="B8" s="166"/>
+      <c r="B8" s="164"/>
       <c r="C8" s="16" t="s">
         <v>3</v>
       </c>
-      <c r="D8" s="231"/>
-      <c r="E8" s="237" t="s">
-        <v>186</v>
+      <c r="D8" s="17"/>
+      <c r="E8" s="55" t="s">
+        <v>152</v>
       </c>
       <c r="F8" s="125" t="s">
-        <v>31</v>
+        <v>150</v>
       </c>
       <c r="G8" s="125"/>
-      <c r="H8" s="192" t="s">
-        <v>220</v>
-      </c>
-      <c r="I8" s="37"/>
-      <c r="J8" s="43" t="s">
-        <v>184</v>
-      </c>
+      <c r="H8" s="179" t="s">
+        <v>153</v>
+      </c>
+      <c r="I8" s="37" t="s">
+        <v>151</v>
+      </c>
+      <c r="J8" s="43"/>
       <c r="K8" s="18"/>
       <c r="L8" s="100"/>
       <c r="M8" s="20" t="s">
-        <v>114</v>
-      </c>
-      <c r="N8" s="66" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A9" s="182" t="s">
+        <v>62</v>
+      </c>
+      <c r="N8" s="61" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A9" s="165" t="s">
         <v>2</v>
       </c>
-      <c r="B9" s="183">
-        <v>46156</v>
+      <c r="B9" s="162">
+        <v>46184</v>
       </c>
       <c r="C9" s="11"/>
       <c r="D9" s="12"/>
-      <c r="E9" s="126"/>
+      <c r="E9" s="174"/>
       <c r="F9" s="127"/>
       <c r="G9" s="127"/>
       <c r="H9" s="128"/>
       <c r="I9" s="128"/>
       <c r="J9" s="44"/>
       <c r="K9" s="19"/>
-      <c r="L9" s="174"/>
-      <c r="M9" s="32" t="s">
-        <v>58</v>
-      </c>
-      <c r="N9" s="22" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A10" s="184"/>
-      <c r="B10" s="190"/>
+      <c r="L9" s="172"/>
+      <c r="M9" s="22" t="s">
+        <v>92</v>
+      </c>
+      <c r="N9" s="61" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A10" s="56"/>
+      <c r="B10" s="163"/>
       <c r="C10" s="14"/>
-      <c r="D10" s="198"/>
-      <c r="E10" s="20"/>
+      <c r="D10" s="184"/>
+      <c r="E10" s="212"/>
       <c r="F10" s="83"/>
       <c r="G10" s="83"/>
       <c r="H10" s="67"/>
       <c r="I10" s="67"/>
       <c r="J10" s="45"/>
-      <c r="K10" s="154"/>
+      <c r="K10" s="152"/>
       <c r="M10" s="22" t="s">
-        <v>115</v>
-      </c>
-      <c r="N10" s="120" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="11" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="184"/>
-      <c r="B11" s="185"/>
+        <v>108</v>
+      </c>
+      <c r="N10" s="66" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="56"/>
+      <c r="B11" s="166"/>
       <c r="C11" s="14"/>
-      <c r="D11" s="198"/>
-      <c r="E11" s="26"/>
+      <c r="D11" s="184"/>
+      <c r="E11" s="173"/>
       <c r="F11" s="125"/>
       <c r="G11" s="125"/>
       <c r="H11" s="37"/>
-      <c r="I11" s="37"/>
+      <c r="I11" s="22"/>
       <c r="J11" s="40"/>
       <c r="K11" s="26"/>
       <c r="L11" s="26"/>
       <c r="M11" s="22" t="s">
-        <v>156</v>
-      </c>
-      <c r="N11" s="22" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="12" spans="1:14" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="186"/>
-      <c r="B12" s="187"/>
+        <v>109</v>
+      </c>
+      <c r="N11" s="26" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="41"/>
+      <c r="B12" s="164"/>
       <c r="C12" s="16" t="s">
         <v>3</v>
       </c>
-      <c r="D12" s="17"/>
-      <c r="E12" s="56" t="s">
-        <v>187</v>
-      </c>
-      <c r="F12" s="129" t="s">
-        <v>31</v>
-      </c>
-      <c r="G12" s="129" t="s">
-        <v>170</v>
-      </c>
-      <c r="H12" s="192" t="s">
-        <v>221</v>
-      </c>
-      <c r="I12" s="78"/>
-      <c r="J12" s="43" t="s">
-        <v>184</v>
-      </c>
+      <c r="D12" s="227"/>
+      <c r="E12" s="22" t="s">
+        <v>140</v>
+      </c>
+      <c r="F12" s="129"/>
+      <c r="G12" s="129"/>
+      <c r="H12" s="179" t="s">
+        <v>189</v>
+      </c>
+      <c r="I12" s="78" t="s">
+        <v>155</v>
+      </c>
+      <c r="J12" s="43"/>
       <c r="K12" s="18"/>
       <c r="L12" s="18"/>
       <c r="M12" s="22" t="s">
-        <v>150</v>
-      </c>
-      <c r="N12" s="61" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A13" s="182" t="s">
+        <v>149</v>
+      </c>
+      <c r="N12" s="66" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A13" s="165" t="s">
         <v>4</v>
       </c>
-      <c r="B13" s="183">
-        <v>46157</v>
-      </c>
-      <c r="C13" s="11"/>
+      <c r="B13" s="162">
+        <v>46185</v>
+      </c>
+      <c r="C13" s="11" t="s">
+        <v>141</v>
+      </c>
       <c r="D13" s="12"/>
-      <c r="E13" s="24"/>
-      <c r="F13" s="199"/>
-      <c r="G13" s="200"/>
+      <c r="E13" s="221" t="s">
+        <v>217</v>
+      </c>
+      <c r="F13" s="185"/>
+      <c r="G13" s="186"/>
       <c r="H13"/>
       <c r="I13" s="31"/>
-      <c r="J13" s="46"/>
-      <c r="K13" s="154"/>
+      <c r="J13" s="46" t="s">
+        <v>142</v>
+      </c>
+      <c r="K13" s="152" t="s">
+        <v>144</v>
+      </c>
       <c r="L13" s="24"/>
       <c r="M13" s="20" t="s">
-        <v>57</v>
-      </c>
-      <c r="N13" s="22" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="14" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="195"/>
-      <c r="B14" s="185"/>
-      <c r="C14" s="14"/>
-      <c r="D14" s="198"/>
-      <c r="E14" s="26"/>
+        <v>111</v>
+      </c>
+      <c r="N13" s="25" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="25"/>
+      <c r="B14" s="166"/>
+      <c r="C14" s="14" t="s">
+        <v>143</v>
+      </c>
+      <c r="D14" s="184"/>
+      <c r="E14" s="222" t="s">
+        <v>218</v>
+      </c>
       <c r="F14" s="130"/>
-      <c r="G14" s="201"/>
-      <c r="H14"/>
+      <c r="G14" s="187"/>
+      <c r="H14" s="241"/>
       <c r="I14" s="146"/>
-      <c r="J14" s="40"/>
-      <c r="K14" s="26"/>
-      <c r="L14" s="23"/>
+      <c r="J14" s="40" t="s">
+        <v>142</v>
+      </c>
+      <c r="K14" s="152" t="s">
+        <v>144</v>
+      </c>
+      <c r="L14" s="26"/>
       <c r="M14" s="22" t="s">
-        <v>117</v>
-      </c>
-      <c r="N14" s="22" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="15" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="196"/>
-      <c r="B15" s="185"/>
+        <v>112</v>
+      </c>
+      <c r="N14" s="120" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="27"/>
+      <c r="B15" s="166"/>
       <c r="C15" s="14"/>
-      <c r="D15" s="198"/>
+      <c r="D15" s="184"/>
       <c r="E15" s="26"/>
       <c r="F15" s="129"/>
       <c r="G15" s="129"/>
@@ -2646,157 +2521,132 @@
       <c r="J15" s="40"/>
       <c r="K15" s="26"/>
       <c r="L15" s="23"/>
-      <c r="M15" s="56" t="s">
-        <v>116</v>
-      </c>
-      <c r="N15" s="66" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="16" spans="1:14" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="186"/>
-      <c r="B16" s="187"/>
+      <c r="M15" s="56"/>
+      <c r="N15" s="22" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="41"/>
+      <c r="B16" s="164"/>
       <c r="C16" s="16" t="s">
         <v>3</v>
       </c>
-      <c r="D16" s="231"/>
-      <c r="E16" s="237" t="s">
-        <v>188</v>
+      <c r="D16" s="227"/>
+      <c r="E16" s="22" t="s">
+        <v>157</v>
       </c>
       <c r="F16" s="129"/>
-      <c r="G16" s="152"/>
-      <c r="H16" s="202" t="s">
-        <v>222</v>
-      </c>
-      <c r="I16" s="40"/>
-      <c r="J16" s="97" t="s">
-        <v>185</v>
-      </c>
+      <c r="G16" s="150"/>
+      <c r="H16" s="188" t="s">
+        <v>190</v>
+      </c>
+      <c r="I16" s="40" t="s">
+        <v>156</v>
+      </c>
+      <c r="J16" s="97"/>
       <c r="K16" s="77"/>
       <c r="L16" s="100"/>
-      <c r="M16" s="21" t="s">
-        <v>118</v>
-      </c>
-      <c r="N16" s="66" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="17" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A17" s="182" t="s">
+      <c r="M16" s="21"/>
+      <c r="N16" s="171" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A17" s="165" t="s">
         <v>5</v>
       </c>
-      <c r="B17" s="183">
-        <v>46158</v>
+      <c r="B17" s="162">
+        <v>46186</v>
       </c>
       <c r="C17" s="11"/>
       <c r="D17" s="12"/>
-      <c r="E17" s="203"/>
-      <c r="F17" s="204"/>
-      <c r="G17" s="204"/>
-      <c r="H17" s="205"/>
-      <c r="I17" s="205"/>
+      <c r="E17" s="210"/>
+      <c r="F17" s="189"/>
+      <c r="G17" s="189"/>
+      <c r="H17" s="190"/>
+      <c r="I17" s="190"/>
       <c r="J17" s="42"/>
       <c r="K17" s="122"/>
       <c r="L17" s="13"/>
-      <c r="M17" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="N17" s="61" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="18" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A18" s="184"/>
-      <c r="B18" s="190"/>
+      <c r="N17" s="66" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="18" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A18" s="56"/>
+      <c r="B18" s="163"/>
       <c r="C18" s="14" t="s">
-        <v>152</v>
-      </c>
-      <c r="D18" s="198"/>
-      <c r="E18" s="22" t="s">
-        <v>190</v>
-      </c>
+        <v>11</v>
+      </c>
+      <c r="D18" s="184"/>
+      <c r="E18" s="175"/>
       <c r="F18" s="125"/>
       <c r="G18" s="125"/>
-      <c r="H18" s="25" t="s">
-        <v>228</v>
-      </c>
+      <c r="H18" s="25"/>
       <c r="I18" s="37"/>
       <c r="J18" s="45" t="s">
         <v>25</v>
       </c>
       <c r="K18" s="15" t="s">
-        <v>189</v>
+        <v>83</v>
       </c>
       <c r="L18" s="15"/>
-      <c r="M18" s="57" t="s">
-        <v>120</v>
-      </c>
-      <c r="N18" s="22" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="19" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="184"/>
-      <c r="B19" s="185"/>
+      <c r="M18" s="57"/>
+      <c r="N18" s="66" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="19" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="56"/>
+      <c r="B19" s="166"/>
       <c r="C19" s="14" t="s">
         <v>6</v>
       </c>
-      <c r="D19" s="232"/>
-      <c r="E19" s="22" t="s">
-        <v>93</v>
-      </c>
-      <c r="F19" s="83" t="s">
-        <v>31</v>
-      </c>
+      <c r="D19" s="184"/>
+      <c r="E19" s="175"/>
+      <c r="F19" s="83"/>
       <c r="G19" s="83"/>
-      <c r="H19" s="67" t="s">
-        <v>223</v>
-      </c>
+      <c r="H19" s="67"/>
       <c r="I19" s="67"/>
-      <c r="J19" s="191" t="s">
-        <v>82</v>
+      <c r="J19" s="178" t="s">
+        <v>90</v>
       </c>
       <c r="K19" s="15" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="L19" s="15"/>
-      <c r="M19" s="22" t="s">
-        <v>121</v>
-      </c>
+      <c r="M19" s="22"/>
       <c r="N19" s="22" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="20" spans="1:14" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="186"/>
-      <c r="B20" s="187"/>
+        <v>69</v>
+      </c>
+    </row>
+    <row r="20" spans="1:14" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="41"/>
+      <c r="B20" s="164"/>
       <c r="C20" s="16" t="s">
         <v>3</v>
       </c>
       <c r="D20" s="17"/>
-      <c r="E20" s="131" t="s">
-        <v>73</v>
-      </c>
+      <c r="E20" s="211"/>
       <c r="F20" s="125"/>
       <c r="G20" s="125"/>
-      <c r="H20" s="37" t="s">
-        <v>224</v>
-      </c>
+      <c r="H20" s="37"/>
       <c r="I20" s="37"/>
       <c r="J20" s="47"/>
       <c r="K20" s="18"/>
       <c r="L20" s="108"/>
       <c r="M20" s="20"/>
       <c r="N20" s="22" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="21" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A21" s="182" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="21" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A21" s="165" t="s">
         <v>7</v>
       </c>
-      <c r="B21" s="183">
-        <v>46159</v>
+      <c r="B21" s="162">
+        <v>46187</v>
       </c>
       <c r="C21" s="28"/>
       <c r="D21" s="29"/>
@@ -2809,24 +2659,24 @@
       <c r="K21" s="13"/>
       <c r="L21" s="136"/>
       <c r="M21" s="26"/>
-      <c r="N21" s="26" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="22" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="184"/>
-      <c r="B22" s="190"/>
+      <c r="N21" s="120" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="22" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="56"/>
+      <c r="B22" s="163"/>
       <c r="C22" s="14" t="s">
         <v>11</v>
       </c>
-      <c r="D22" s="198"/>
+      <c r="D22" s="184"/>
       <c r="E22" s="61" t="s">
-        <v>191</v>
+        <v>158</v>
       </c>
       <c r="F22" s="125"/>
       <c r="G22" s="125"/>
-      <c r="H22" s="37" t="s">
-        <v>225</v>
+      <c r="H22" s="241" t="s">
+        <v>191</v>
       </c>
       <c r="I22" s="37"/>
       <c r="J22" s="45" t="s">
@@ -2835,77 +2685,85 @@
       <c r="K22" s="15"/>
       <c r="L22" s="21"/>
       <c r="M22" s="27"/>
-      <c r="N22" s="66" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="23" spans="1:14" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="184"/>
-      <c r="B23" s="185"/>
+      <c r="N22" s="26" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="23" spans="1:14" ht="13.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="56"/>
+      <c r="B23" s="166"/>
       <c r="C23" s="14" t="s">
         <v>6</v>
       </c>
-      <c r="D23" s="232"/>
-      <c r="E23" s="20" t="s">
-        <v>151</v>
+      <c r="D23" s="228"/>
+      <c r="E23" s="22" t="s">
+        <v>159</v>
       </c>
       <c r="F23" s="125"/>
       <c r="G23" s="125"/>
-      <c r="H23" s="37" t="s">
-        <v>226</v>
-      </c>
-      <c r="I23" s="37"/>
+      <c r="H23" s="241" t="s">
+        <v>192</v>
+      </c>
+      <c r="I23" s="37" t="s">
+        <v>160</v>
+      </c>
       <c r="J23" s="45"/>
       <c r="K23" s="15"/>
       <c r="L23" s="27"/>
       <c r="M23" s="56"/>
-      <c r="N23" s="22" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="24" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A24" s="186"/>
-      <c r="B24" s="187"/>
-      <c r="C24" s="17"/>
+      <c r="N23" s="66" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="24" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="41"/>
+      <c r="B24" s="164"/>
+      <c r="C24" s="16" t="s">
+        <v>3</v>
+      </c>
       <c r="D24" s="17"/>
-      <c r="E24" s="26"/>
-      <c r="F24" s="206"/>
-      <c r="G24" s="207"/>
-      <c r="H24" s="208"/>
-      <c r="I24" s="208"/>
+      <c r="E24" s="55" t="s">
+        <v>98</v>
+      </c>
+      <c r="F24" s="191"/>
+      <c r="G24" s="192"/>
+      <c r="H24" s="242" t="s">
+        <v>193</v>
+      </c>
+      <c r="I24" s="193"/>
       <c r="J24" s="39"/>
       <c r="K24" s="78"/>
       <c r="L24" s="78"/>
       <c r="M24" s="22"/>
-      <c r="N24" s="22" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="25" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A25" s="167" t="s">
+      <c r="N24" s="66" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="25" spans="1:14" ht="15.75" x14ac:dyDescent="0.3">
+      <c r="A25" s="165" t="s">
         <v>8</v>
       </c>
-      <c r="B25" s="164">
-        <v>46160</v>
+      <c r="B25" s="162">
+        <v>46188</v>
       </c>
       <c r="C25" s="11"/>
       <c r="D25" s="12"/>
       <c r="E25" s="19"/>
       <c r="F25" s="132"/>
-      <c r="G25" s="209"/>
-      <c r="H25"/>
+      <c r="G25" s="194"/>
+      <c r="H25" s="243"/>
       <c r="I25" s="44"/>
       <c r="J25" s="44"/>
-      <c r="K25" s="157"/>
+      <c r="K25" s="155"/>
       <c r="L25" s="19"/>
       <c r="M25" s="26"/>
-      <c r="N25" s="22" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="26" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="N25" s="171" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="26" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A26" s="108"/>
-      <c r="B26" s="169"/>
+      <c r="B26" s="167"/>
       <c r="C26" s="16"/>
       <c r="D26" s="17"/>
       <c r="E26" s="18"/>
@@ -2915,51 +2773,39 @@
       <c r="I26" s="43"/>
       <c r="J26" s="43"/>
       <c r="K26" s="116"/>
-      <c r="L26" s="18"/>
+      <c r="L26" s="100"/>
       <c r="M26" s="26"/>
-      <c r="N26" s="66" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="27" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N26" s="22" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="27" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="31" t="s">
         <v>9</v>
       </c>
-      <c r="B27" s="164">
-        <v>46161</v>
-      </c>
-      <c r="C27" s="11" t="s">
-        <v>157</v>
-      </c>
+      <c r="B27" s="162">
+        <v>46189</v>
+      </c>
+      <c r="C27" s="11"/>
       <c r="D27" s="12"/>
-      <c r="E27" s="227" t="s">
-        <v>158</v>
-      </c>
+      <c r="E27" s="13"/>
       <c r="F27" s="123"/>
       <c r="G27" s="123"/>
-      <c r="H27" s="42" t="s">
-        <v>227</v>
-      </c>
+      <c r="H27" s="42"/>
       <c r="I27" s="42"/>
-      <c r="J27" s="46" t="s">
-        <v>159</v>
-      </c>
-      <c r="K27" s="118">
-        <v>3</v>
-      </c>
-      <c r="L27" s="24" t="s">
-        <v>160</v>
-      </c>
+      <c r="J27" s="46"/>
+      <c r="K27" s="118"/>
+      <c r="L27" s="24"/>
       <c r="M27" s="22"/>
-      <c r="N27" s="26" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="28" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N27" s="66" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="28" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A28" s="56"/>
-      <c r="B28" s="165"/>
+      <c r="B28" s="163"/>
       <c r="C28" s="14"/>
-      <c r="D28" s="198"/>
+      <c r="D28" s="184"/>
       <c r="E28" s="26"/>
       <c r="F28" s="134"/>
       <c r="G28" s="134"/>
@@ -2970,57 +2816,59 @@
       <c r="L28" s="21"/>
       <c r="M28" s="22"/>
       <c r="N28" s="22" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="29" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="29" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="56"/>
-      <c r="B29" s="168"/>
+      <c r="B29" s="166"/>
       <c r="C29" s="14"/>
-      <c r="D29" s="198"/>
+      <c r="D29" s="184"/>
       <c r="E29" s="15"/>
       <c r="F29" s="124"/>
       <c r="G29" s="124"/>
       <c r="H29" s="38"/>
       <c r="I29" s="38"/>
       <c r="J29" s="49"/>
-      <c r="K29" s="156"/>
+      <c r="K29" s="154"/>
       <c r="L29" s="79"/>
       <c r="M29" s="27"/>
-      <c r="N29" s="22"/>
-    </row>
-    <row r="30" spans="1:14" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="N29" s="171" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="30" spans="1:14" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A30" s="41"/>
-      <c r="B30" s="166"/>
+      <c r="B30" s="164"/>
       <c r="C30" s="16" t="s">
         <v>3</v>
       </c>
       <c r="D30" s="17"/>
-      <c r="E30" s="237" t="s">
-        <v>192</v>
+      <c r="E30" s="22" t="s">
+        <v>161</v>
       </c>
       <c r="F30" s="129" t="s">
-        <v>31</v>
+        <v>150</v>
       </c>
       <c r="G30" s="129"/>
-      <c r="H30" s="40" t="s">
-        <v>229</v>
+      <c r="H30" s="241" t="s">
+        <v>194</v>
       </c>
       <c r="I30" s="40"/>
-      <c r="J30" s="43" t="s">
-        <v>183</v>
-      </c>
+      <c r="J30" s="43"/>
       <c r="K30" s="18"/>
       <c r="L30" s="100"/>
       <c r="M30" s="58"/>
-      <c r="N30" s="22"/>
-    </row>
-    <row r="31" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A31" s="161" t="s">
+      <c r="N30" s="220" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="31" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A31" s="159" t="s">
         <v>0</v>
       </c>
-      <c r="B31" s="170">
-        <v>46162</v>
+      <c r="B31" s="168">
+        <v>46190</v>
       </c>
       <c r="C31" s="7"/>
       <c r="D31" s="8"/>
@@ -3033,16 +2881,18 @@
       <c r="K31" s="10"/>
       <c r="L31" s="10"/>
       <c r="M31" s="59">
-        <v>46134</v>
-      </c>
-      <c r="N31" s="61"/>
-    </row>
-    <row r="32" spans="1:14" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="167" t="s">
+        <v>46162</v>
+      </c>
+      <c r="N31" s="61" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="32" spans="1:14" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="165" t="s">
         <v>1</v>
       </c>
-      <c r="B32" s="164">
-        <v>46162</v>
+      <c r="B32" s="162">
+        <v>46190</v>
       </c>
       <c r="C32" s="12"/>
       <c r="D32" s="12"/>
@@ -3055,15 +2905,15 @@
       <c r="K32" s="34"/>
       <c r="L32" s="34"/>
       <c r="M32" s="55" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="N32" s="25"/>
     </row>
-    <row r="33" spans="1:15" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:15" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="56"/>
-      <c r="B33" s="168"/>
+      <c r="B33" s="166"/>
       <c r="C33" s="14"/>
-      <c r="D33" s="198"/>
+      <c r="D33" s="184"/>
       <c r="E33" s="22"/>
       <c r="F33" s="130"/>
       <c r="G33" s="130"/>
@@ -3073,17 +2923,17 @@
       <c r="K33" s="26"/>
       <c r="L33" s="26"/>
       <c r="M33" s="55" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="N33" s="64" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="34" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="56"/>
-      <c r="B34" s="168"/>
+      <c r="B34" s="166"/>
       <c r="C34" s="14"/>
-      <c r="D34" s="198"/>
+      <c r="D34" s="184"/>
       <c r="E34" s="15"/>
       <c r="F34" s="124"/>
       <c r="G34" s="124"/>
@@ -3093,54 +2943,48 @@
       <c r="K34" s="27"/>
       <c r="L34" s="27"/>
       <c r="M34" s="60" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="N34" s="26" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="35" spans="1:15" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="35" spans="1:15" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A35" s="41"/>
-      <c r="B35" s="166"/>
+      <c r="B35" s="164"/>
       <c r="C35" s="16" t="s">
         <v>3</v>
       </c>
-      <c r="D35" s="233"/>
-      <c r="E35" s="22" t="s">
-        <v>194</v>
-      </c>
-      <c r="F35" s="129" t="s">
-        <v>31</v>
-      </c>
+      <c r="D35" s="215"/>
+      <c r="E35" s="55" t="s">
+        <v>100</v>
+      </c>
+      <c r="F35" s="129"/>
       <c r="G35" s="129"/>
-      <c r="H35" s="40" t="s">
-        <v>230</v>
-      </c>
-      <c r="I35" s="210"/>
-      <c r="J35" s="97" t="s">
-        <v>183</v>
-      </c>
+      <c r="H35" s="241" t="s">
+        <v>195</v>
+      </c>
+      <c r="I35" s="195"/>
+      <c r="J35" s="97"/>
       <c r="K35" s="77"/>
-      <c r="L35" s="77" t="s">
-        <v>193</v>
-      </c>
+      <c r="L35" s="99"/>
       <c r="M35" s="22" t="s">
-        <v>123</v>
+        <v>110</v>
       </c>
       <c r="N35" s="22" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="36" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A36" s="167" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="36" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A36" s="165" t="s">
         <v>2</v>
       </c>
-      <c r="B36" s="164">
-        <v>46163</v>
+      <c r="B36" s="218">
+        <v>46191</v>
       </c>
       <c r="C36" s="119"/>
       <c r="D36" s="12"/>
-      <c r="E36" s="13"/>
+      <c r="E36" s="209"/>
       <c r="F36" s="123"/>
       <c r="G36" s="123"/>
       <c r="H36" s="42"/>
@@ -3149,20 +2993,18 @@
       <c r="K36" s="80"/>
       <c r="L36" s="80"/>
       <c r="M36" s="22" t="s">
-        <v>59</v>
+        <v>113</v>
       </c>
       <c r="N36" s="61" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="37" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="37" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="56"/>
-      <c r="B37" s="168"/>
+      <c r="B37" s="166"/>
       <c r="C37" s="35"/>
-      <c r="D37" s="198"/>
-      <c r="E37" s="178" t="s">
-        <v>98</v>
-      </c>
+      <c r="D37" s="184"/>
+      <c r="E37" s="175"/>
       <c r="F37" s="125"/>
       <c r="G37" s="125"/>
       <c r="H37" s="67"/>
@@ -3171,18 +3013,18 @@
       <c r="K37" s="32"/>
       <c r="L37" s="32"/>
       <c r="M37" s="22" t="s">
-        <v>124</v>
-      </c>
-      <c r="N37" s="173" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="38" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+        <v>114</v>
+      </c>
+      <c r="N37" s="171" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="38" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="56"/>
-      <c r="B38" s="168"/>
+      <c r="B38" s="166"/>
       <c r="C38" s="35"/>
-      <c r="D38" s="198"/>
-      <c r="E38" s="224"/>
+      <c r="D38" s="184"/>
+      <c r="E38" s="204"/>
       <c r="F38" s="137"/>
       <c r="G38" s="137"/>
       <c r="H38" s="52"/>
@@ -3191,95 +3033,103 @@
       <c r="K38" s="32"/>
       <c r="L38" s="23"/>
       <c r="M38" s="26" t="s">
-        <v>125</v>
-      </c>
-      <c r="N38" s="22" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="39" spans="1:15" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+        <v>115</v>
+      </c>
+      <c r="N38" s="182" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="39" spans="1:15" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A39" s="41"/>
-      <c r="B39" s="166"/>
+      <c r="B39" s="164"/>
       <c r="C39" s="16" t="s">
         <v>3</v>
       </c>
-      <c r="D39" s="17"/>
-      <c r="E39" s="237" t="s">
-        <v>195</v>
+      <c r="D39" s="227"/>
+      <c r="E39" s="22" t="s">
+        <v>159</v>
       </c>
       <c r="F39" s="129"/>
       <c r="G39" s="129"/>
-      <c r="H39" s="192" t="s">
-        <v>231</v>
-      </c>
-      <c r="I39" s="40"/>
-      <c r="J39" s="97" t="s">
-        <v>184</v>
-      </c>
+      <c r="H39" s="241" t="s">
+        <v>192</v>
+      </c>
+      <c r="I39" s="40" t="s">
+        <v>162</v>
+      </c>
+      <c r="J39" s="97"/>
       <c r="K39" s="77"/>
-      <c r="L39" s="77" t="s">
-        <v>193</v>
-      </c>
+      <c r="L39" s="99"/>
       <c r="M39" s="22" t="s">
-        <v>126</v>
-      </c>
-      <c r="N39" s="195" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="40" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A40" s="167" t="s">
+        <v>116</v>
+      </c>
+      <c r="N39" s="25"/>
+    </row>
+    <row r="40" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A40" s="165" t="s">
         <v>4</v>
       </c>
-      <c r="B40" s="164">
-        <v>46164</v>
-      </c>
-      <c r="C40" s="36"/>
+      <c r="B40" s="218">
+        <v>46192</v>
+      </c>
+      <c r="C40" s="36" t="s">
+        <v>145</v>
+      </c>
       <c r="D40" s="12"/>
-      <c r="E40" s="126"/>
+      <c r="E40" s="223" t="s">
+        <v>219</v>
+      </c>
       <c r="F40" s="127"/>
       <c r="G40" s="127"/>
-      <c r="H40" s="128"/>
+      <c r="H40" s="241" t="s">
+        <v>196</v>
+      </c>
       <c r="I40" s="128"/>
-      <c r="J40" s="53"/>
-      <c r="K40" s="117"/>
+      <c r="J40" s="53" t="s">
+        <v>142</v>
+      </c>
+      <c r="K40" s="117" t="s">
+        <v>144</v>
+      </c>
       <c r="L40" s="80"/>
       <c r="M40" s="22" t="s">
-        <v>102</v>
+        <v>117</v>
       </c>
       <c r="N40" s="65"/>
     </row>
-    <row r="41" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="56"/>
-      <c r="B41" s="168"/>
+      <c r="B41" s="166"/>
       <c r="C41" s="35" t="s">
         <v>12</v>
       </c>
-      <c r="D41" s="198"/>
-      <c r="E41" s="22" t="s">
-        <v>70</v>
+      <c r="D41" s="184"/>
+      <c r="E41" s="26" t="s">
+        <v>75</v>
       </c>
       <c r="F41" s="130"/>
       <c r="G41" s="130"/>
-      <c r="H41" s="54" t="s">
-        <v>232</v>
+      <c r="H41" s="241" t="s">
+        <v>197</v>
       </c>
       <c r="I41" s="54"/>
       <c r="J41" s="40" t="s">
-        <v>37</v>
-      </c>
-      <c r="K41" s="26"/>
+        <v>36</v>
+      </c>
+      <c r="K41" s="26" t="s">
+        <v>87</v>
+      </c>
       <c r="L41" s="26"/>
-      <c r="M41" s="66" t="s">
-        <v>127</v>
+      <c r="M41" s="22" t="s">
+        <v>118</v>
       </c>
       <c r="N41" s="61"/>
     </row>
-    <row r="42" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="56"/>
-      <c r="B42" s="168"/>
+      <c r="B42" s="166"/>
       <c r="C42" s="14"/>
-      <c r="D42" s="198"/>
+      <c r="D42" s="184"/>
       <c r="E42" s="15"/>
       <c r="F42" s="124"/>
       <c r="G42" s="124"/>
@@ -3288,52 +3138,46 @@
       <c r="J42" s="52"/>
       <c r="K42" s="27"/>
       <c r="L42" s="27"/>
-      <c r="M42" s="22" t="s">
-        <v>128</v>
-      </c>
-      <c r="N42" s="153"/>
+      <c r="M42" s="22"/>
+      <c r="N42" s="151"/>
       <c r="O42" s="5"/>
     </row>
-    <row r="43" spans="1:15" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:15" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A43" s="41"/>
-      <c r="B43" s="166"/>
+      <c r="B43" s="164"/>
       <c r="C43" s="33" t="s">
         <v>3</v>
       </c>
-      <c r="D43" s="17"/>
-      <c r="E43" s="238" t="s">
-        <v>196</v>
+      <c r="D43" s="227"/>
+      <c r="E43" s="55" t="s">
+        <v>164</v>
       </c>
       <c r="F43" s="129" t="s">
-        <v>31</v>
-      </c>
-      <c r="G43" s="129" t="s">
-        <v>171</v>
-      </c>
-      <c r="H43" s="37" t="s">
-        <v>233</v>
-      </c>
-      <c r="I43" s="40"/>
-      <c r="J43" s="97" t="s">
-        <v>184</v>
-      </c>
+        <v>150</v>
+      </c>
+      <c r="G43" s="129"/>
+      <c r="H43" s="241" t="s">
+        <v>198</v>
+      </c>
+      <c r="I43" s="40" t="s">
+        <v>163</v>
+      </c>
+      <c r="J43" s="97"/>
       <c r="K43" s="77"/>
       <c r="L43" s="99"/>
-      <c r="M43" s="66" t="s">
-        <v>129</v>
-      </c>
+      <c r="M43" s="22"/>
       <c r="N43" s="22"/>
     </row>
-    <row r="44" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A44" s="182" t="s">
+    <row r="44" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A44" s="165" t="s">
         <v>5</v>
       </c>
-      <c r="B44" s="183">
-        <v>46165</v>
+      <c r="B44" s="162">
+        <v>46193</v>
       </c>
       <c r="C44" s="11"/>
       <c r="D44" s="12"/>
-      <c r="E44" s="211"/>
+      <c r="E44" s="196"/>
       <c r="F44" s="138"/>
       <c r="G44" s="138"/>
       <c r="H44" s="139"/>
@@ -3341,175 +3185,163 @@
       <c r="J44" s="46"/>
       <c r="K44" s="24"/>
       <c r="L44" s="24"/>
-      <c r="M44" s="22" t="s">
-        <v>130</v>
-      </c>
+      <c r="M44" s="22"/>
       <c r="N44" s="26"/>
       <c r="O44" s="4"/>
     </row>
-    <row r="45" spans="1:15" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A45" s="184"/>
-      <c r="B45" s="185"/>
+    <row r="45" spans="1:15" ht="13.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A45" s="56"/>
+      <c r="B45" s="166"/>
       <c r="C45" s="35" t="s">
-        <v>11</v>
-      </c>
-      <c r="D45" s="212"/>
-      <c r="E45" s="22" t="s">
-        <v>201</v>
+        <v>138</v>
+      </c>
+      <c r="D45" s="197"/>
+      <c r="E45" s="60" t="s">
+        <v>165</v>
       </c>
       <c r="F45" s="140"/>
       <c r="G45" s="140"/>
-      <c r="H45" s="25" t="s">
-        <v>234</v>
+      <c r="H45" s="242" t="s">
+        <v>199</v>
       </c>
       <c r="I45" s="141"/>
-      <c r="J45" s="45" t="s">
-        <v>25</v>
+      <c r="J45" s="37" t="s">
+        <v>80</v>
       </c>
       <c r="K45" s="22"/>
       <c r="L45" s="22"/>
-      <c r="M45" s="120" t="s">
-        <v>131</v>
-      </c>
+      <c r="M45" s="26"/>
       <c r="N45" s="61"/>
     </row>
-    <row r="46" spans="1:15" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A46" s="184"/>
-      <c r="B46" s="185"/>
+    <row r="46" spans="1:15" ht="13.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A46" s="56"/>
+      <c r="B46" s="166"/>
       <c r="C46" s="35" t="s">
         <v>6</v>
       </c>
-      <c r="D46" s="234"/>
+      <c r="D46" s="229"/>
       <c r="E46" s="22" t="s">
-        <v>202</v>
+        <v>166</v>
       </c>
       <c r="F46" s="83" t="s">
-        <v>31</v>
+        <v>167</v>
       </c>
       <c r="G46" s="83"/>
-      <c r="H46" s="67" t="s">
-        <v>235</v>
-      </c>
-      <c r="I46" s="67"/>
+      <c r="H46" s="142" t="s">
+        <v>200</v>
+      </c>
+      <c r="I46" s="22"/>
       <c r="J46" s="38" t="s">
-        <v>51</v>
+        <v>89</v>
       </c>
       <c r="K46" s="15" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="L46" s="15"/>
       <c r="M46" s="61"/>
       <c r="N46" s="61"/>
     </row>
-    <row r="47" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A47" s="186"/>
-      <c r="B47" s="187"/>
+    <row r="47" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A47" s="41"/>
+      <c r="B47" s="164"/>
       <c r="C47" s="16" t="s">
         <v>3</v>
       </c>
-      <c r="D47" s="17"/>
+      <c r="D47" s="227"/>
       <c r="E47" s="22" t="s">
-        <v>236</v>
-      </c>
-      <c r="F47" s="213" t="s">
-        <v>31</v>
-      </c>
-      <c r="G47" s="214"/>
-      <c r="H47" s="142" t="s">
-        <v>237</v>
-      </c>
-      <c r="I47" s="215"/>
+        <v>140</v>
+      </c>
+      <c r="F47" s="198"/>
+      <c r="G47" s="199"/>
+      <c r="H47" s="179" t="s">
+        <v>189</v>
+      </c>
+      <c r="I47" s="200"/>
       <c r="J47" s="39"/>
       <c r="K47" s="78"/>
-      <c r="L47" s="78"/>
-      <c r="N47" s="153"/>
-    </row>
-    <row r="48" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A48" s="182" t="s">
+      <c r="L47" s="30"/>
+      <c r="N47" s="151"/>
+    </row>
+    <row r="48" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A48" s="165" t="s">
         <v>7</v>
       </c>
-      <c r="B48" s="183">
-        <v>46166</v>
+      <c r="B48" s="162">
+        <v>46194</v>
       </c>
       <c r="C48" s="12"/>
       <c r="D48" s="12"/>
-      <c r="E48" s="216"/>
-      <c r="F48" s="217"/>
-      <c r="G48" s="217"/>
+      <c r="E48" s="201"/>
+      <c r="F48" s="202"/>
+      <c r="G48" s="202"/>
       <c r="H48" s="25"/>
-      <c r="I48" s="218"/>
+      <c r="I48" s="203"/>
       <c r="J48" s="25"/>
-      <c r="K48" s="153"/>
+      <c r="K48" s="151"/>
       <c r="L48" s="25"/>
       <c r="M48" s="61"/>
       <c r="N48" s="25"/>
     </row>
-    <row r="49" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A49" s="184"/>
-      <c r="B49" s="185"/>
+    <row r="49" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A49" s="56"/>
+      <c r="B49" s="166"/>
       <c r="C49" s="35" t="s">
         <v>11</v>
       </c>
-      <c r="D49" s="219"/>
+      <c r="D49" s="216"/>
       <c r="E49" s="22" t="s">
-        <v>203</v>
+        <v>168</v>
       </c>
       <c r="F49" s="83"/>
       <c r="G49" s="83"/>
-      <c r="H49" s="67" t="s">
-        <v>238</v>
+      <c r="H49" s="241" t="s">
+        <v>201</v>
       </c>
       <c r="I49" s="67"/>
       <c r="J49" s="38" t="s">
-        <v>200</v>
+        <v>84</v>
       </c>
       <c r="K49" s="15"/>
       <c r="L49" s="15"/>
       <c r="M49" s="27"/>
       <c r="N49" s="61"/>
     </row>
-    <row r="50" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A50" s="184"/>
-      <c r="B50" s="185"/>
+    <row r="50" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A50" s="56"/>
+      <c r="B50" s="166"/>
       <c r="C50" s="35" t="s">
         <v>6</v>
       </c>
-      <c r="D50" s="234"/>
-      <c r="E50" s="237" t="s">
-        <v>104</v>
-      </c>
-      <c r="F50" s="125"/>
+      <c r="D50" s="229"/>
+      <c r="E50" s="22" t="s">
+        <v>169</v>
+      </c>
+      <c r="F50" s="125" t="s">
+        <v>150</v>
+      </c>
       <c r="G50" s="125"/>
       <c r="H50" s="37" t="s">
-        <v>239</v>
-      </c>
-      <c r="I50" s="22"/>
+        <v>202</v>
+      </c>
+      <c r="I50" s="22" t="s">
+        <v>162</v>
+      </c>
       <c r="J50" s="98"/>
       <c r="K50" s="81"/>
       <c r="L50" s="81"/>
       <c r="N50" s="61"/>
     </row>
-    <row r="51" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A51" s="186"/>
-      <c r="B51" s="187"/>
-      <c r="C51" s="16" t="s">
-        <v>3</v>
-      </c>
+    <row r="51" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A51" s="41"/>
+      <c r="B51" s="164"/>
+      <c r="C51" s="16"/>
       <c r="D51" s="17"/>
-      <c r="E51" s="22" t="s">
-        <v>198</v>
-      </c>
-      <c r="F51" s="144" t="s">
-        <v>31</v>
-      </c>
+      <c r="E51" s="22"/>
+      <c r="F51" s="144"/>
       <c r="G51" s="144"/>
-      <c r="H51" s="131" t="s">
-        <v>240</v>
-      </c>
+      <c r="H51" s="131"/>
       <c r="I51" s="131"/>
-      <c r="J51" s="41" t="s">
-        <v>183</v>
-      </c>
+      <c r="J51" s="41"/>
       <c r="K51" s="108"/>
       <c r="L51" s="41"/>
       <c r="M51" s="22"/>
@@ -3517,28 +3349,28 @@
         <v>18</v>
       </c>
     </row>
-    <row r="52" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A52" s="182" t="s">
+    <row r="52" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A52" s="165" t="s">
         <v>8</v>
       </c>
-      <c r="B52" s="183">
-        <v>46167</v>
-      </c>
-      <c r="C52" s="11" t="s">
-        <v>152</v>
-      </c>
-      <c r="D52" s="235"/>
-      <c r="E52" s="19" t="s">
-        <v>199</v>
+      <c r="B52" s="218">
+        <v>46195</v>
+      </c>
+      <c r="C52" s="12" t="s">
+        <v>147</v>
+      </c>
+      <c r="D52" s="12"/>
+      <c r="E52" s="224" t="s">
+        <v>220</v>
       </c>
       <c r="F52" s="132"/>
       <c r="G52" s="132"/>
-      <c r="H52" s="44" t="s">
-        <v>241</v>
-      </c>
-      <c r="I52" s="44"/>
+      <c r="H52" s="44"/>
+      <c r="I52" s="44" t="s">
+        <v>170</v>
+      </c>
       <c r="J52" s="44" t="s">
-        <v>197</v>
+        <v>148</v>
       </c>
       <c r="K52" s="19"/>
       <c r="L52" s="19"/>
@@ -3547,158 +3379,138 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="53" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A53" s="188"/>
-      <c r="B53" s="189"/>
+    <row r="53" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A53" s="108"/>
+      <c r="B53" s="167"/>
       <c r="C53" s="16"/>
       <c r="D53" s="17"/>
-      <c r="E53" s="18"/>
+      <c r="E53" s="205"/>
       <c r="F53" s="133"/>
       <c r="G53" s="133"/>
       <c r="H53" s="43"/>
       <c r="I53" s="43"/>
       <c r="J53" s="43"/>
-      <c r="K53" s="15"/>
-      <c r="L53" s="15"/>
+      <c r="K53" s="18"/>
+      <c r="L53" s="18"/>
       <c r="M53" s="26"/>
       <c r="N53" s="21" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="54" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="31" t="s">
         <v>9</v>
       </c>
-      <c r="B54" s="164">
-        <v>46168</v>
+      <c r="B54" s="162">
+        <v>46196</v>
       </c>
       <c r="C54" s="11" t="s">
-        <v>157</v>
+        <v>145</v>
       </c>
       <c r="D54" s="12"/>
-      <c r="E54" s="227" t="s">
-        <v>161</v>
+      <c r="E54" s="225" t="s">
+        <v>221</v>
       </c>
       <c r="F54" s="123"/>
       <c r="G54" s="123"/>
-      <c r="H54" s="42" t="s">
-        <v>242</v>
-      </c>
+      <c r="H54" s="42"/>
       <c r="I54" s="42"/>
       <c r="J54" s="24" t="s">
-        <v>159</v>
-      </c>
-      <c r="K54" s="239">
-        <v>3</v>
-      </c>
-      <c r="L54" s="26" t="s">
-        <v>162</v>
-      </c>
+        <v>146</v>
+      </c>
+      <c r="K54" s="207"/>
+      <c r="L54" s="26"/>
       <c r="M54" s="22"/>
       <c r="N54" s="21" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="55" spans="1:14" x14ac:dyDescent="0.3">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="55" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A55" s="56"/>
-      <c r="B55" s="165"/>
-      <c r="C55" s="14" t="s">
-        <v>173</v>
-      </c>
-      <c r="D55" s="198"/>
-      <c r="E55" s="230" t="s">
-        <v>174</v>
-      </c>
+      <c r="B55" s="163"/>
+      <c r="C55" s="14"/>
+      <c r="D55" s="184"/>
+      <c r="E55" s="81"/>
       <c r="F55" s="134"/>
       <c r="G55" s="134"/>
-      <c r="H55" s="37" t="s">
-        <v>182</v>
-      </c>
+      <c r="H55" s="37"/>
       <c r="I55" s="135"/>
-      <c r="J55" s="38" t="s">
-        <v>179</v>
-      </c>
-      <c r="K55" s="15" t="s">
-        <v>91</v>
-      </c>
-      <c r="L55" s="15" t="s">
-        <v>180</v>
-      </c>
+      <c r="J55" s="38"/>
+      <c r="K55" s="15"/>
+      <c r="L55" s="15"/>
       <c r="M55" s="22"/>
       <c r="N55" s="106" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="56" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="56" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="56"/>
-      <c r="B56" s="168"/>
+      <c r="B56" s="166"/>
       <c r="C56" s="14"/>
-      <c r="D56" s="198"/>
+      <c r="D56" s="184"/>
       <c r="E56" s="15"/>
       <c r="F56" s="124"/>
       <c r="G56" s="124"/>
       <c r="H56" s="38"/>
       <c r="I56" s="38"/>
       <c r="J56" s="49"/>
-      <c r="K56" s="156"/>
+      <c r="K56" s="154"/>
       <c r="L56" s="79"/>
       <c r="M56" s="27"/>
       <c r="N56" s="92"/>
     </row>
-    <row r="57" spans="1:14" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:14" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A57" s="41"/>
-      <c r="B57" s="166"/>
-      <c r="C57" s="17" t="s">
-        <v>155</v>
-      </c>
-      <c r="D57" s="231"/>
+      <c r="B57" s="164"/>
+      <c r="C57" s="16" t="s">
+        <v>3</v>
+      </c>
+      <c r="D57" s="17"/>
       <c r="E57" s="22" t="s">
-        <v>204</v>
-      </c>
-      <c r="F57" s="129" t="s">
-        <v>31</v>
-      </c>
+        <v>171</v>
+      </c>
+      <c r="F57" s="129"/>
       <c r="G57" s="129"/>
-      <c r="H57" s="220" t="s">
-        <v>243</v>
-      </c>
-      <c r="I57" s="40"/>
-      <c r="J57" s="43" t="s">
-        <v>183</v>
-      </c>
+      <c r="H57" s="242" t="s">
+        <v>203</v>
+      </c>
+      <c r="I57" s="40" t="s">
+        <v>86</v>
+      </c>
+      <c r="J57" s="43"/>
       <c r="K57" s="18"/>
       <c r="L57" s="100"/>
       <c r="M57" s="58"/>
       <c r="N57" s="91"/>
     </row>
-    <row r="58" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A58" s="161" t="s">
+    <row r="58" spans="1:14" ht="16.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A58" s="159" t="s">
         <v>0</v>
       </c>
-      <c r="B58" s="170">
-        <v>46169</v>
+      <c r="B58" s="168">
+        <v>46197</v>
       </c>
       <c r="C58" s="7"/>
       <c r="D58" s="8"/>
       <c r="E58" s="9"/>
       <c r="F58" s="84"/>
       <c r="G58" s="84"/>
-      <c r="H58" s="68"/>
+      <c r="H58" s="243"/>
       <c r="I58" s="68"/>
       <c r="J58" s="50"/>
       <c r="K58" s="10"/>
       <c r="L58" s="10"/>
       <c r="M58" s="59">
-        <v>46141</v>
+        <v>46169</v>
       </c>
       <c r="N58" s="92"/>
     </row>
-    <row r="59" spans="1:14" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A59" s="167" t="s">
+    <row r="59" spans="1:14" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A59" s="165" t="s">
         <v>1</v>
       </c>
-      <c r="B59" s="164">
-        <v>46169</v>
+      <c r="B59" s="162">
+        <v>46197</v>
       </c>
       <c r="C59" s="11"/>
       <c r="D59" s="12"/>
@@ -3711,15 +3523,15 @@
       <c r="K59" s="118"/>
       <c r="L59" s="24"/>
       <c r="M59" s="55" t="s">
-        <v>108</v>
+        <v>139</v>
       </c>
       <c r="N59" s="21"/>
     </row>
-    <row r="60" spans="1:14" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:14" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" s="56"/>
-      <c r="B60" s="168"/>
+      <c r="B60" s="166"/>
       <c r="C60" s="14"/>
-      <c r="D60" s="198"/>
+      <c r="D60" s="184"/>
       <c r="E60" s="32"/>
       <c r="F60" s="130"/>
       <c r="G60" s="130"/>
@@ -3729,70 +3541,62 @@
       <c r="K60" s="26"/>
       <c r="L60" s="26"/>
       <c r="M60" s="55" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="N60" s="90"/>
     </row>
-    <row r="61" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="56"/>
-      <c r="B61" s="168"/>
-      <c r="C61" s="14" t="s">
-        <v>90</v>
-      </c>
-      <c r="D61" s="198"/>
-      <c r="E61" s="222" t="s">
-        <v>207</v>
-      </c>
+      <c r="B61" s="166"/>
+      <c r="C61" s="14"/>
+      <c r="D61" s="184"/>
+      <c r="E61" s="15"/>
       <c r="F61" s="124"/>
       <c r="G61" s="124"/>
       <c r="H61" s="38"/>
-      <c r="I61" s="38" t="s">
-        <v>92</v>
-      </c>
+      <c r="I61" s="38"/>
       <c r="J61" s="52"/>
-      <c r="K61" s="27" t="s">
-        <v>91</v>
-      </c>
-      <c r="L61" s="27" t="s">
-        <v>206</v>
-      </c>
-      <c r="M61" s="60"/>
+      <c r="K61" s="27"/>
+      <c r="L61" s="27"/>
+      <c r="M61" s="60" t="s">
+        <v>103</v>
+      </c>
       <c r="N61" s="90"/>
     </row>
-    <row r="62" spans="1:14" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:14" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A62" s="41"/>
-      <c r="B62" s="166"/>
+      <c r="B62" s="164"/>
       <c r="C62" s="33" t="s">
         <v>3</v>
       </c>
-      <c r="D62" s="17"/>
-      <c r="E62" s="237" t="s">
-        <v>205</v>
+      <c r="D62" s="227"/>
+      <c r="E62" s="22" t="s">
+        <v>172</v>
       </c>
       <c r="F62" s="129" t="s">
-        <v>31</v>
+        <v>150</v>
       </c>
       <c r="G62" s="129"/>
-      <c r="H62" s="192" t="s">
-        <v>244</v>
-      </c>
-      <c r="I62" s="40"/>
-      <c r="J62" s="97" t="s">
-        <v>184</v>
-      </c>
+      <c r="H62" s="188" t="s">
+        <v>190</v>
+      </c>
+      <c r="I62" s="40" t="s">
+        <v>162</v>
+      </c>
+      <c r="J62" s="97"/>
       <c r="K62" s="77"/>
       <c r="L62" s="99"/>
-      <c r="M62" s="226" t="s">
-        <v>133</v>
+      <c r="M62" s="2" t="s">
+        <v>119</v>
       </c>
       <c r="N62" s="27"/>
     </row>
-    <row r="63" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A63" s="167" t="s">
+    <row r="63" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A63" s="165" t="s">
         <v>2</v>
       </c>
-      <c r="B63" s="164">
-        <v>46170</v>
+      <c r="B63" s="162">
+        <v>46198</v>
       </c>
       <c r="C63" s="31"/>
       <c r="D63" s="12"/>
@@ -3805,17 +3609,17 @@
       <c r="K63" s="80"/>
       <c r="L63" s="80"/>
       <c r="M63" s="22" t="s">
-        <v>132</v>
+        <v>120</v>
       </c>
       <c r="N63" s="93" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="64" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" s="56"/>
-      <c r="B64" s="168"/>
+      <c r="B64" s="166"/>
       <c r="C64" s="35"/>
-      <c r="D64" s="198"/>
+      <c r="D64" s="184"/>
       <c r="E64" s="22"/>
       <c r="F64" s="125"/>
       <c r="G64" s="125"/>
@@ -3825,17 +3629,17 @@
       <c r="K64" s="15"/>
       <c r="L64" s="15"/>
       <c r="M64" s="22" t="s">
-        <v>101</v>
+        <v>121</v>
       </c>
       <c r="N64" s="22" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="65" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" s="56"/>
-      <c r="B65" s="168"/>
+      <c r="B65" s="166"/>
       <c r="C65" s="35"/>
-      <c r="D65" s="198"/>
+      <c r="D65" s="184"/>
       <c r="E65" s="27"/>
       <c r="F65" s="137"/>
       <c r="G65" s="137"/>
@@ -3845,108 +3649,98 @@
       <c r="K65" s="32"/>
       <c r="L65" s="23"/>
       <c r="M65" s="26" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="N65" s="22" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="66" spans="1:15" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:15" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A66" s="41"/>
-      <c r="B66" s="166"/>
+      <c r="B66" s="164"/>
       <c r="C66" s="16" t="s">
         <v>3</v>
       </c>
-      <c r="D66" s="231"/>
-      <c r="E66" s="22" t="s">
-        <v>208</v>
-      </c>
-      <c r="F66" s="129" t="s">
-        <v>31</v>
-      </c>
+      <c r="D66" s="17"/>
+      <c r="E66" s="55" t="s">
+        <v>173</v>
+      </c>
+      <c r="F66" s="129"/>
       <c r="G66" s="129"/>
-      <c r="H66" s="40" t="s">
-        <v>245</v>
+      <c r="H66" s="241" t="s">
+        <v>204</v>
       </c>
       <c r="I66" s="40"/>
-      <c r="J66" s="97" t="s">
-        <v>184</v>
-      </c>
+      <c r="J66" s="97"/>
       <c r="K66" s="77"/>
       <c r="L66" s="99"/>
       <c r="M66" s="22" t="s">
-        <v>134</v>
+        <v>122</v>
       </c>
       <c r="N66" s="22" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="67" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A67" s="167" t="s">
+    <row r="67" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A67" s="165" t="s">
         <v>4</v>
       </c>
-      <c r="B67" s="164">
-        <v>46171</v>
-      </c>
-      <c r="C67" s="36" t="s">
-        <v>61</v>
-      </c>
+      <c r="B67" s="162">
+        <v>46199</v>
+      </c>
+      <c r="C67" s="36"/>
       <c r="D67" s="12"/>
-      <c r="E67" s="175" t="s">
-        <v>95</v>
-      </c>
-      <c r="F67" s="127" t="s">
-        <v>83</v>
-      </c>
+      <c r="E67" s="126"/>
+      <c r="F67" s="127"/>
       <c r="G67" s="127"/>
-      <c r="H67" s="128" t="s">
-        <v>246</v>
-      </c>
+      <c r="H67" s="128"/>
       <c r="I67" s="128"/>
-      <c r="J67" s="53" t="s">
-        <v>60</v>
-      </c>
-      <c r="K67" s="80" t="s">
-        <v>94</v>
-      </c>
-      <c r="L67" s="80" t="s">
-        <v>96</v>
-      </c>
+      <c r="J67" s="53"/>
+      <c r="K67" s="80"/>
+      <c r="L67" s="80"/>
       <c r="M67" s="22" t="s">
-        <v>135</v>
+        <v>123</v>
       </c>
       <c r="N67" s="22" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="68" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="68" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68" s="56"/>
-      <c r="B68" s="168"/>
-      <c r="C68" s="14"/>
-      <c r="D68" s="198"/>
-      <c r="E68" s="178" t="s">
-        <v>97</v>
+      <c r="B68" s="166"/>
+      <c r="C68" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="D68" s="184"/>
+      <c r="E68" s="22" t="s">
+        <v>63</v>
       </c>
       <c r="F68" s="130"/>
       <c r="G68" s="130"/>
-      <c r="H68" s="54"/>
+      <c r="H68" s="241" t="s">
+        <v>205</v>
+      </c>
       <c r="I68" s="54"/>
-      <c r="J68" s="40"/>
-      <c r="K68" s="26"/>
+      <c r="J68" s="40" t="s">
+        <v>36</v>
+      </c>
+      <c r="K68" s="26" t="s">
+        <v>87</v>
+      </c>
       <c r="L68" s="26"/>
-      <c r="M68" s="66" t="s">
-        <v>136</v>
+      <c r="M68" s="22" t="s">
+        <v>124</v>
       </c>
       <c r="N68" s="65" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="69" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69" s="56"/>
-      <c r="B69" s="168"/>
+      <c r="B69" s="166"/>
       <c r="C69" s="14"/>
-      <c r="D69" s="198"/>
-      <c r="E69" s="223"/>
+      <c r="D69" s="184"/>
+      <c r="E69" s="217"/>
       <c r="F69" s="124"/>
       <c r="G69" s="124"/>
       <c r="H69" s="38"/>
@@ -3955,51 +3749,53 @@
       <c r="K69" s="27"/>
       <c r="L69" s="27"/>
       <c r="M69" s="22" t="s">
-        <v>137</v>
+        <v>125</v>
       </c>
       <c r="N69" s="25" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="O69" s="5"/>
     </row>
-    <row r="70" spans="1:15" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:15" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A70" s="41"/>
-      <c r="B70" s="166"/>
+      <c r="B70" s="164"/>
       <c r="C70" s="16" t="s">
         <v>3</v>
       </c>
-      <c r="D70" s="231"/>
-      <c r="E70" s="20" t="s">
-        <v>151</v>
-      </c>
-      <c r="F70" s="129"/>
+      <c r="D70" s="227"/>
+      <c r="E70" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="F70" s="129" t="s">
+        <v>150</v>
+      </c>
       <c r="G70" s="129"/>
-      <c r="H70" s="37" t="s">
-        <v>226</v>
-      </c>
-      <c r="I70" s="40"/>
+      <c r="H70" s="241" t="s">
+        <v>206</v>
+      </c>
+      <c r="I70" s="40" t="s">
+        <v>154</v>
+      </c>
       <c r="J70" s="97"/>
       <c r="K70" s="77"/>
       <c r="L70" s="78"/>
-      <c r="M70" s="66" t="s">
-        <v>138</v>
+      <c r="M70" s="22" t="s">
+        <v>126</v>
       </c>
       <c r="N70" s="25" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="71" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A71" s="167" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="71" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A71" s="165" t="s">
         <v>5</v>
       </c>
-      <c r="B71" s="164">
-        <v>46172</v>
+      <c r="B71" s="218">
+        <v>46200</v>
       </c>
       <c r="C71" s="11"/>
       <c r="D71" s="12"/>
-      <c r="E71" s="180" t="s">
-        <v>177</v>
-      </c>
+      <c r="E71" s="176"/>
       <c r="F71" s="138"/>
       <c r="G71" s="138"/>
       <c r="H71" s="139"/>
@@ -4008,21 +3804,21 @@
       <c r="K71" s="24"/>
       <c r="L71" s="34"/>
       <c r="M71" s="22" t="s">
-        <v>139</v>
+        <v>127</v>
       </c>
       <c r="N71" s="22" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="O71" s="4"/>
     </row>
-    <row r="72" spans="1:15" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:15" ht="13.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A72" s="56"/>
-      <c r="B72" s="168"/>
+      <c r="B72" s="166"/>
       <c r="C72" s="14" t="s">
         <v>11</v>
       </c>
-      <c r="D72" s="212"/>
-      <c r="E72" s="176"/>
+      <c r="D72" s="197"/>
+      <c r="E72" s="173"/>
       <c r="F72" s="140"/>
       <c r="G72" s="140"/>
       <c r="H72" s="141"/>
@@ -4032,47 +3828,47 @@
       </c>
       <c r="K72" s="22"/>
       <c r="L72" s="22"/>
-      <c r="M72" s="120" t="s">
-        <v>140</v>
+      <c r="M72" s="26" t="s">
+        <v>128</v>
       </c>
       <c r="N72" s="25" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="73" spans="1:15" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="73" spans="1:15" ht="13.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A73" s="56"/>
-      <c r="B73" s="168"/>
+      <c r="B73" s="166"/>
       <c r="C73" s="14" t="s">
         <v>6</v>
       </c>
-      <c r="D73" s="212"/>
-      <c r="E73" s="178"/>
+      <c r="D73" s="197"/>
+      <c r="E73" s="175"/>
       <c r="F73" s="109"/>
       <c r="G73" s="83"/>
       <c r="H73" s="67"/>
       <c r="I73" s="67"/>
       <c r="J73" s="37" t="s">
-        <v>88</v>
+        <v>59</v>
       </c>
       <c r="K73" s="15" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="L73" s="26"/>
       <c r="M73" s="61"/>
       <c r="N73" s="25" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="74" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="74" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A74" s="41"/>
-      <c r="B74" s="166"/>
+      <c r="B74" s="164"/>
       <c r="C74" s="16" t="s">
         <v>3</v>
       </c>
       <c r="D74" s="17"/>
-      <c r="E74" s="176"/>
+      <c r="E74" s="173"/>
       <c r="F74" s="145"/>
-      <c r="G74" s="194"/>
+      <c r="G74" s="181"/>
       <c r="H74" s="142"/>
       <c r="I74" s="142"/>
       <c r="J74" s="39"/>
@@ -4080,15 +3876,15 @@
       <c r="L74" s="78"/>
       <c r="M74" s="61"/>
       <c r="N74" s="61" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="75" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A75" s="167" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="75" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A75" s="165" t="s">
         <v>7</v>
       </c>
-      <c r="B75" s="164">
-        <v>46173</v>
+      <c r="B75" s="162">
+        <v>46201</v>
       </c>
       <c r="C75" s="36"/>
       <c r="D75" s="12"/>
@@ -4096,97 +3892,99 @@
       <c r="F75" s="143"/>
       <c r="G75" s="143"/>
       <c r="H75" s="25"/>
-      <c r="I75" s="218"/>
+      <c r="I75" s="203"/>
       <c r="J75" s="25"/>
-      <c r="K75" s="153"/>
+      <c r="K75" s="151"/>
       <c r="L75" s="25"/>
       <c r="M75" s="61"/>
       <c r="N75" s="22" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="76" spans="1:15" x14ac:dyDescent="0.3">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="76" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A76" s="56"/>
-      <c r="B76" s="168"/>
+      <c r="B76" s="166"/>
       <c r="C76" s="35" t="s">
         <v>11</v>
       </c>
-      <c r="D76" s="219"/>
-      <c r="E76" s="22" t="s">
-        <v>209</v>
+      <c r="D76" s="216"/>
+      <c r="E76" s="25" t="s">
+        <v>175</v>
       </c>
       <c r="F76" s="83"/>
       <c r="G76" s="83"/>
-      <c r="H76" s="37" t="s">
-        <v>247</v>
+      <c r="H76" s="241" t="s">
+        <v>207</v>
       </c>
       <c r="I76" s="67"/>
       <c r="J76" s="38" t="s">
-        <v>50</v>
-      </c>
-      <c r="K76" s="15" t="s">
-        <v>211</v>
-      </c>
+        <v>45</v>
+      </c>
+      <c r="K76" s="15"/>
       <c r="L76" s="15"/>
       <c r="M76" s="27"/>
       <c r="N76" s="56" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="77" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="77" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A77" s="56"/>
-      <c r="B77" s="168"/>
+      <c r="B77" s="166"/>
       <c r="C77" s="35" t="s">
         <v>6</v>
       </c>
-      <c r="D77" s="234"/>
+      <c r="D77" s="229"/>
       <c r="E77" s="22" t="s">
-        <v>124</v>
+        <v>176</v>
       </c>
       <c r="F77" s="125"/>
       <c r="G77" s="125"/>
-      <c r="H77" s="37" t="s">
-        <v>248</v>
-      </c>
-      <c r="I77" s="37"/>
+      <c r="H77" s="241" t="s">
+        <v>208</v>
+      </c>
+      <c r="I77" s="37" t="s">
+        <v>177</v>
+      </c>
       <c r="J77" s="98"/>
       <c r="K77" s="81"/>
       <c r="L77" s="81"/>
       <c r="M77" s="22"/>
       <c r="N77" s="65" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="78" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="78" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A78" s="41"/>
-      <c r="B78" s="166"/>
+      <c r="B78" s="164"/>
       <c r="C78" s="16" t="s">
         <v>3</v>
       </c>
-      <c r="D78" s="17"/>
-      <c r="E78" s="237" t="s">
-        <v>108</v>
+      <c r="D78" s="227"/>
+      <c r="E78" s="55" t="s">
+        <v>178</v>
       </c>
       <c r="F78" s="144"/>
       <c r="G78" s="144"/>
-      <c r="H78" t="s">
-        <v>249</v>
-      </c>
-      <c r="I78" s="131"/>
+      <c r="H78" s="241" t="s">
+        <v>209</v>
+      </c>
+      <c r="I78" s="131" t="s">
+        <v>179</v>
+      </c>
       <c r="J78" s="41"/>
       <c r="K78" s="108"/>
       <c r="L78" s="41"/>
       <c r="M78" s="26"/>
       <c r="N78" s="27" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="79" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A79" s="167" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="79" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A79" s="165" t="s">
         <v>8</v>
       </c>
-      <c r="B79" s="164">
-        <v>46174</v>
+      <c r="B79" s="162">
+        <v>46202</v>
       </c>
       <c r="C79" s="11"/>
       <c r="D79" s="12"/>
@@ -4200,12 +3998,12 @@
       <c r="L79" s="19"/>
       <c r="M79" s="26"/>
       <c r="N79" s="22" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="80" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="80" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A80" s="108"/>
-      <c r="B80" s="169"/>
+      <c r="B80" s="167"/>
       <c r="C80" s="16"/>
       <c r="D80" s="17"/>
       <c r="E80" s="18"/>
@@ -4217,14 +4015,16 @@
       <c r="K80" s="18"/>
       <c r="L80" s="18"/>
       <c r="M80" s="26"/>
-      <c r="N80" s="22"/>
-    </row>
-    <row r="81" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N80" s="22" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="81" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" s="31" t="s">
         <v>9</v>
       </c>
-      <c r="B81" s="164">
-        <v>46175</v>
+      <c r="B81" s="162">
+        <v>46203</v>
       </c>
       <c r="C81" s="11"/>
       <c r="D81" s="12"/>
@@ -4239,94 +4039,92 @@
       <c r="M81" s="22"/>
       <c r="N81" s="21"/>
     </row>
-    <row r="82" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A82" s="56"/>
-      <c r="B82" s="165"/>
+      <c r="B82" s="163"/>
       <c r="C82" s="14"/>
-      <c r="D82" s="198"/>
+      <c r="D82" s="184"/>
       <c r="E82" s="27"/>
       <c r="F82" s="137"/>
       <c r="G82" s="134"/>
       <c r="H82" s="52"/>
       <c r="I82" s="135"/>
       <c r="J82" s="45"/>
-      <c r="K82" s="158"/>
+      <c r="K82" s="156"/>
       <c r="L82" s="21"/>
       <c r="M82" s="22"/>
       <c r="N82" s="96" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="83" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A83" s="56"/>
-      <c r="B83" s="168"/>
+      <c r="B83" s="166"/>
       <c r="C83" s="14"/>
-      <c r="D83" s="198"/>
+      <c r="D83" s="184"/>
       <c r="E83" s="15"/>
       <c r="F83" s="124"/>
       <c r="G83" s="124"/>
       <c r="H83" s="38"/>
       <c r="I83" s="38"/>
       <c r="J83" s="49"/>
-      <c r="K83" s="156"/>
+      <c r="K83" s="154"/>
       <c r="L83" s="79"/>
       <c r="M83" s="27"/>
       <c r="N83" s="88"/>
     </row>
-    <row r="84" spans="1:15" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:15" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A84" s="41"/>
-      <c r="B84" s="166"/>
-      <c r="C84" s="17" t="s">
-        <v>155</v>
-      </c>
-      <c r="D84" s="231"/>
-      <c r="E84" s="2" t="s">
+      <c r="B84" s="164"/>
+      <c r="C84" s="16" t="s">
+        <v>3</v>
+      </c>
+      <c r="D84" s="17"/>
+      <c r="E84" s="60" t="s">
+        <v>180</v>
+      </c>
+      <c r="F84" s="129" t="s">
+        <v>150</v>
+      </c>
+      <c r="G84" s="129"/>
+      <c r="H84" s="242" t="s">
         <v>210</v>
       </c>
-      <c r="F84" s="129" t="s">
-        <v>31</v>
-      </c>
-      <c r="G84" s="129"/>
-      <c r="H84" s="40" t="s">
-        <v>250</v>
-      </c>
       <c r="I84" s="40"/>
-      <c r="J84" s="43" t="s">
-        <v>183</v>
-      </c>
+      <c r="J84" s="43"/>
       <c r="K84" s="18"/>
       <c r="L84" s="18"/>
       <c r="M84" s="58"/>
       <c r="N84" s="25"/>
     </row>
-    <row r="85" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A85" s="161" t="s">
+    <row r="85" spans="1:15" ht="16.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A85" s="159" t="s">
         <v>0</v>
       </c>
-      <c r="B85" s="170">
-        <v>46176</v>
+      <c r="B85" s="168">
+        <v>46204</v>
       </c>
       <c r="C85" s="7"/>
       <c r="D85" s="8"/>
       <c r="E85" s="9"/>
       <c r="F85" s="84"/>
       <c r="G85" s="84"/>
-      <c r="H85" s="68"/>
+      <c r="H85" s="243"/>
       <c r="I85" s="68"/>
       <c r="J85" s="50"/>
       <c r="K85" s="10"/>
       <c r="L85" s="10"/>
       <c r="M85" s="59">
-        <v>46148</v>
+        <v>46176</v>
       </c>
       <c r="N85" s="25"/>
     </row>
-    <row r="86" spans="1:15" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A86" s="167" t="s">
+    <row r="86" spans="1:15" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A86" s="165" t="s">
         <v>1</v>
       </c>
-      <c r="B86" s="164">
-        <v>46176</v>
+      <c r="B86" s="162">
+        <v>46204</v>
       </c>
       <c r="C86" s="11"/>
       <c r="D86" s="12"/>
@@ -4339,15 +4137,15 @@
       <c r="K86" s="34"/>
       <c r="L86" s="34"/>
       <c r="M86" s="55" t="s">
-        <v>154</v>
+        <v>107</v>
       </c>
       <c r="N86" s="25"/>
     </row>
-    <row r="87" spans="1:15" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:15" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A87" s="56"/>
-      <c r="B87" s="168"/>
+      <c r="B87" s="166"/>
       <c r="C87" s="14"/>
-      <c r="D87" s="198"/>
+      <c r="D87" s="184"/>
       <c r="E87" s="32"/>
       <c r="F87" s="130"/>
       <c r="G87" s="130"/>
@@ -4357,15 +4155,15 @@
       <c r="K87" s="26"/>
       <c r="L87" s="26"/>
       <c r="M87" s="55" t="s">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="N87" s="25"/>
     </row>
-    <row r="88" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A88" s="56"/>
-      <c r="B88" s="168"/>
+      <c r="B88" s="166"/>
       <c r="C88" s="35"/>
-      <c r="D88" s="198"/>
+      <c r="D88" s="184"/>
       <c r="E88" s="15"/>
       <c r="F88" s="124"/>
       <c r="G88" s="124"/>
@@ -4375,85 +4173,85 @@
       <c r="K88" s="27"/>
       <c r="L88" s="27"/>
       <c r="M88" s="60" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="N88" s="25"/>
     </row>
-    <row r="89" spans="1:15" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:15" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A89" s="41"/>
-      <c r="B89" s="166"/>
+      <c r="B89" s="164"/>
       <c r="C89" s="33" t="s">
         <v>3</v>
       </c>
-      <c r="D89" s="231"/>
-      <c r="E89" s="22" t="s">
-        <v>212</v>
+      <c r="D89" s="17"/>
+      <c r="E89" s="60" t="s">
+        <v>182</v>
       </c>
       <c r="F89" s="129" t="s">
-        <v>31</v>
+        <v>150</v>
       </c>
       <c r="G89" s="129"/>
-      <c r="H89" s="40" t="s">
-        <v>251</v>
-      </c>
-      <c r="I89" s="40"/>
-      <c r="J89" s="97" t="s">
-        <v>184</v>
-      </c>
+      <c r="H89" s="242" t="s">
+        <v>211</v>
+      </c>
+      <c r="I89" s="40" t="s">
+        <v>181</v>
+      </c>
+      <c r="J89" s="97"/>
       <c r="K89" s="77"/>
       <c r="L89" s="15"/>
-      <c r="M89" s="66" t="s">
-        <v>143</v>
+      <c r="M89" s="22" t="s">
+        <v>129</v>
       </c>
       <c r="N89" s="25"/>
     </row>
-    <row r="90" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A90" s="167" t="s">
+    <row r="90" spans="1:15" ht="15.75" x14ac:dyDescent="0.3">
+      <c r="A90" s="165" t="s">
         <v>2</v>
       </c>
-      <c r="B90" s="164">
-        <v>46177</v>
+      <c r="B90" s="218">
+        <v>46205</v>
       </c>
       <c r="C90" s="119"/>
       <c r="D90" s="12"/>
       <c r="E90" s="13"/>
       <c r="F90" s="123"/>
       <c r="G90" s="123"/>
-      <c r="H90" s="42"/>
+      <c r="H90" s="243"/>
       <c r="I90" s="42"/>
       <c r="J90" s="46"/>
       <c r="K90" s="118"/>
       <c r="L90" s="24"/>
       <c r="M90" s="22" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="N90" s="87"/>
     </row>
-    <row r="91" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A91" s="56"/>
-      <c r="B91" s="168"/>
+      <c r="B91" s="166"/>
       <c r="C91" s="35"/>
-      <c r="D91" s="198"/>
-      <c r="E91" s="221"/>
+      <c r="D91" s="184"/>
+      <c r="E91" s="213"/>
       <c r="F91" s="125"/>
       <c r="G91" s="125"/>
       <c r="H91" s="37"/>
       <c r="I91" s="26"/>
       <c r="J91" s="54"/>
-      <c r="K91" s="158"/>
+      <c r="K91" s="156"/>
       <c r="L91" s="21"/>
-      <c r="M91" s="66" t="s">
-        <v>144</v>
+      <c r="M91" s="22" t="s">
+        <v>130</v>
       </c>
       <c r="N91" s="107" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="92" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A92" s="56"/>
-      <c r="B92" s="168"/>
-      <c r="D92" s="198"/>
-      <c r="E92" s="27"/>
+      <c r="B92" s="166"/>
+      <c r="D92" s="184"/>
+      <c r="E92" s="204"/>
       <c r="F92" s="137"/>
       <c r="G92" s="137"/>
       <c r="H92" s="52"/>
@@ -4462,54 +4260,42 @@
       <c r="K92" s="32"/>
       <c r="L92" s="32"/>
       <c r="M92" s="26" t="s">
-        <v>145</v>
-      </c>
-      <c r="N92" s="181" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="93" spans="1:15" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+        <v>131</v>
+      </c>
+      <c r="N92" s="177" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="93" spans="1:15" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A93" s="41"/>
-      <c r="B93" s="166"/>
+      <c r="B93" s="164"/>
       <c r="C93" s="16" t="s">
         <v>3</v>
       </c>
       <c r="D93" s="17"/>
-      <c r="E93" s="237" t="s">
-        <v>213</v>
-      </c>
-      <c r="F93" s="129" t="s">
-        <v>31</v>
-      </c>
-      <c r="G93" s="129" t="s">
-        <v>172</v>
-      </c>
-      <c r="H93" s="40" t="s">
-        <v>252</v>
-      </c>
+      <c r="E93" s="173"/>
+      <c r="F93" s="129"/>
+      <c r="G93" s="129"/>
+      <c r="H93" s="40"/>
       <c r="I93" s="40"/>
-      <c r="J93" s="97" t="s">
-        <v>184</v>
-      </c>
+      <c r="J93" s="97"/>
       <c r="K93" s="77"/>
       <c r="L93" s="15"/>
       <c r="M93" s="22" t="s">
-        <v>105</v>
+        <v>132</v>
       </c>
       <c r="N93" s="65"/>
     </row>
-    <row r="94" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A94" s="167" t="s">
+    <row r="94" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A94" s="165" t="s">
         <v>4</v>
       </c>
-      <c r="B94" s="164">
-        <v>46178</v>
+      <c r="B94" s="162">
+        <v>46206</v>
       </c>
       <c r="C94" s="36"/>
       <c r="D94" s="12"/>
-      <c r="E94" s="177" t="s">
-        <v>99</v>
-      </c>
+      <c r="E94" s="126"/>
       <c r="F94" s="127"/>
       <c r="G94" s="127"/>
       <c r="H94" s="128"/>
@@ -4518,38 +4304,34 @@
       <c r="K94" s="80"/>
       <c r="L94" s="80"/>
       <c r="M94" s="22" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="N94" s="65"/>
     </row>
-    <row r="95" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A95" s="56"/>
-      <c r="B95" s="168"/>
-      <c r="C95" s="35" t="s">
-        <v>12</v>
-      </c>
-      <c r="D95" s="198"/>
-      <c r="E95" s="178"/>
+      <c r="B95" s="166"/>
+      <c r="C95" s="35"/>
+      <c r="D95" s="184"/>
+      <c r="E95" s="22"/>
       <c r="F95" s="130"/>
       <c r="G95" s="130"/>
       <c r="H95" s="54"/>
       <c r="I95" s="54"/>
-      <c r="J95" s="40" t="s">
-        <v>37</v>
-      </c>
+      <c r="J95" s="40"/>
       <c r="K95" s="26"/>
       <c r="L95" s="26"/>
-      <c r="M95" s="66" t="s">
-        <v>146</v>
+      <c r="M95" s="22" t="s">
+        <v>133</v>
       </c>
       <c r="N95" s="25"/>
     </row>
-    <row r="96" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A96" s="56"/>
-      <c r="B96" s="168"/>
+      <c r="B96" s="166"/>
       <c r="C96" s="14"/>
-      <c r="D96" s="198"/>
-      <c r="E96" s="179"/>
+      <c r="D96" s="184"/>
+      <c r="E96" s="15"/>
       <c r="F96" s="124"/>
       <c r="G96" s="124"/>
       <c r="H96" s="148"/>
@@ -4558,49 +4340,49 @@
       <c r="K96" s="27"/>
       <c r="L96" s="27"/>
       <c r="M96" s="22" t="s">
-        <v>109</v>
+        <v>102</v>
       </c>
       <c r="N96" s="65"/>
       <c r="O96" s="5"/>
     </row>
-    <row r="97" spans="1:15" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:15" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A97" s="41"/>
-      <c r="B97" s="166"/>
+      <c r="B97" s="164"/>
       <c r="C97" s="16" t="s">
         <v>3</v>
       </c>
-      <c r="D97" s="231"/>
-      <c r="E97" s="238" t="s">
-        <v>215</v>
-      </c>
-      <c r="F97" s="129"/>
+      <c r="D97" s="227"/>
+      <c r="E97" s="22" t="s">
+        <v>169</v>
+      </c>
+      <c r="F97" s="129" t="s">
+        <v>150</v>
+      </c>
       <c r="G97" s="129"/>
       <c r="H97" s="40" t="s">
-        <v>253</v>
-      </c>
-      <c r="I97" s="40"/>
-      <c r="J97" s="97" t="s">
-        <v>183</v>
-      </c>
+        <v>212</v>
+      </c>
+      <c r="I97" s="40" t="s">
+        <v>162</v>
+      </c>
+      <c r="J97" s="97"/>
       <c r="K97" s="77"/>
-      <c r="L97" s="77" t="s">
-        <v>214</v>
-      </c>
-      <c r="M97" s="173" t="s">
-        <v>147</v>
+      <c r="L97" s="77"/>
+      <c r="M97" s="22" t="s">
+        <v>134</v>
       </c>
       <c r="N97" s="27"/>
     </row>
-    <row r="98" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A98" s="167" t="s">
+    <row r="98" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A98" s="230" t="s">
         <v>5</v>
       </c>
-      <c r="B98" s="164">
-        <v>46179</v>
+      <c r="B98" s="231">
+        <v>46207</v>
       </c>
       <c r="C98" s="11"/>
       <c r="D98" s="12"/>
-      <c r="E98" s="211"/>
+      <c r="E98" s="176"/>
       <c r="F98" s="138"/>
       <c r="G98" s="138"/>
       <c r="H98" s="139"/>
@@ -4609,83 +4391,81 @@
       <c r="K98" s="24"/>
       <c r="L98" s="34"/>
       <c r="M98" s="22" t="s">
-        <v>148</v>
+        <v>135</v>
       </c>
       <c r="N98" s="25"/>
       <c r="O98" s="4"/>
     </row>
-    <row r="99" spans="1:15" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A99" s="56"/>
-      <c r="B99" s="168"/>
+    <row r="99" spans="1:15" ht="13.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A99" s="232"/>
+      <c r="B99" s="233"/>
       <c r="C99" s="14" t="s">
-        <v>11</v>
-      </c>
-      <c r="D99" s="212"/>
-      <c r="E99" s="61" t="s">
-        <v>67</v>
+        <v>138</v>
+      </c>
+      <c r="D99" s="197"/>
+      <c r="E99" s="22" t="s">
+        <v>165</v>
       </c>
       <c r="F99" s="140"/>
       <c r="G99" s="140"/>
-      <c r="H99" s="141" t="s">
-        <v>225</v>
+      <c r="H99" s="242" t="s">
+        <v>211</v>
       </c>
       <c r="I99" s="141"/>
-      <c r="J99" s="37" t="s">
-        <v>153</v>
-      </c>
+      <c r="J99" s="37"/>
       <c r="K99" s="22" t="s">
-        <v>211</v>
+        <v>85</v>
       </c>
       <c r="L99" s="22"/>
       <c r="M99" s="26" t="s">
-        <v>149</v>
+        <v>137</v>
       </c>
       <c r="N99" s="25"/>
     </row>
-    <row r="100" spans="1:15" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A100" s="56"/>
-      <c r="B100" s="168"/>
+    <row r="100" spans="1:15" ht="13.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A100" s="232"/>
+      <c r="B100" s="233"/>
       <c r="C100" s="14" t="s">
         <v>6</v>
       </c>
-      <c r="D100" s="212"/>
-      <c r="E100" s="25" t="s">
-        <v>217</v>
+      <c r="D100" s="229"/>
+      <c r="E100" s="22" t="s">
+        <v>166</v>
       </c>
       <c r="F100" s="83" t="s">
-        <v>31</v>
+        <v>183</v>
       </c>
       <c r="G100" s="83"/>
-      <c r="H100" s="67" t="s">
-        <v>254</v>
+      <c r="H100" s="142" t="s">
+        <v>200</v>
       </c>
       <c r="I100" s="67"/>
       <c r="J100" s="37" t="s">
         <v>88</v>
       </c>
       <c r="K100" s="15" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="L100" s="15"/>
-      <c r="M100" s="61"/>
+      <c r="M100" s="61" t="s">
+        <v>136</v>
+      </c>
       <c r="N100" s="25"/>
     </row>
-    <row r="101" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A101" s="41"/>
-      <c r="B101" s="166"/>
+    <row r="101" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A101" s="234"/>
+      <c r="B101" s="235"/>
       <c r="C101" s="16" t="s">
         <v>3</v>
       </c>
-      <c r="D101" s="17"/>
+      <c r="D101" s="227"/>
       <c r="E101" s="22" t="s">
-        <v>216</v>
-      </c>
-      <c r="F101" s="145" t="s">
-        <v>83</v>
-      </c>
-      <c r="G101" s="194"/>
-      <c r="H101" s="142" t="s">
-        <v>255</v>
+        <v>184</v>
+      </c>
+      <c r="F101" s="145"/>
+      <c r="G101" s="181"/>
+      <c r="H101" s="242" t="s">
+        <v>213</v>
       </c>
       <c r="I101" s="131"/>
       <c r="J101" s="39"/>
@@ -4694,19 +4474,19 @@
       <c r="M101" s="61"/>
       <c r="N101" s="61"/>
     </row>
-    <row r="102" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A102" s="167" t="s">
+    <row r="102" spans="1:15" ht="15.75" x14ac:dyDescent="0.3">
+      <c r="A102" s="230" t="s">
         <v>7</v>
       </c>
-      <c r="B102" s="164">
-        <v>46180</v>
+      <c r="B102" s="236">
+        <v>46208</v>
       </c>
       <c r="C102" s="11"/>
       <c r="D102" s="12"/>
-      <c r="E102" s="31"/>
+      <c r="E102" s="214"/>
       <c r="F102" s="143"/>
       <c r="G102" s="143"/>
-      <c r="H102" s="149"/>
+      <c r="H102" s="243"/>
       <c r="I102" s="25"/>
       <c r="J102" s="25"/>
       <c r="K102" s="126"/>
@@ -4714,112 +4494,94 @@
       <c r="M102" s="61"/>
       <c r="N102" s="22"/>
     </row>
-    <row r="103" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A103" s="56"/>
-      <c r="B103" s="168"/>
+    <row r="103" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A103" s="232"/>
+      <c r="B103" s="233"/>
       <c r="C103" s="14" t="s">
         <v>11</v>
       </c>
-      <c r="D103" s="236"/>
-      <c r="E103" s="237" t="s">
-        <v>218</v>
-      </c>
+      <c r="D103" s="219"/>
+      <c r="E103" s="173"/>
       <c r="F103" s="83"/>
       <c r="G103" s="83"/>
-      <c r="H103" s="67" t="s">
-        <v>256</v>
-      </c>
+      <c r="H103" s="67"/>
       <c r="I103" s="67"/>
-      <c r="J103" s="38" t="s">
-        <v>50</v>
-      </c>
+      <c r="J103" s="38"/>
       <c r="K103" s="15"/>
       <c r="L103" s="15"/>
       <c r="M103" s="27"/>
       <c r="N103" s="25"/>
     </row>
-    <row r="104" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A104" s="56"/>
-      <c r="B104" s="168"/>
+    <row r="104" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A104" s="232"/>
+      <c r="B104" s="233"/>
       <c r="C104" s="14" t="s">
         <v>6</v>
       </c>
-      <c r="D104" s="234"/>
-      <c r="E104" s="238" t="s">
-        <v>215</v>
-      </c>
+      <c r="D104" s="197"/>
+      <c r="E104" s="175"/>
       <c r="F104" s="125"/>
       <c r="G104" s="125"/>
-      <c r="H104" s="37" t="s">
-        <v>253</v>
-      </c>
-      <c r="I104" s="150"/>
-      <c r="J104" s="98" t="s">
-        <v>183</v>
-      </c>
+      <c r="H104" s="37"/>
+      <c r="I104" s="149"/>
+      <c r="J104" s="98"/>
       <c r="K104" s="81"/>
-      <c r="L104" s="81" t="s">
-        <v>214</v>
-      </c>
+      <c r="L104" s="81"/>
       <c r="M104" s="22"/>
       <c r="N104" s="65"/>
     </row>
-    <row r="105" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A105" s="41"/>
-      <c r="B105" s="166"/>
-      <c r="C105" s="16"/>
-      <c r="D105" s="17"/>
-      <c r="E105" s="22"/>
+    <row r="105" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A105" s="234"/>
+      <c r="B105" s="235"/>
+      <c r="C105" s="16" t="s">
+        <v>3</v>
+      </c>
+      <c r="D105" s="227"/>
+      <c r="E105" s="60" t="s">
+        <v>185</v>
+      </c>
       <c r="F105" s="144"/>
       <c r="G105" s="144"/>
-      <c r="H105" s="131"/>
-      <c r="I105" s="131"/>
+      <c r="H105" s="241" t="s">
+        <v>214</v>
+      </c>
+      <c r="I105" s="131" t="s">
+        <v>186</v>
+      </c>
       <c r="J105" s="41"/>
       <c r="K105" s="108"/>
       <c r="L105" s="41"/>
       <c r="M105" s="26"/>
       <c r="N105" s="27"/>
     </row>
-    <row r="106" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A106" s="167" t="s">
+    <row r="106" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A106" s="230" t="s">
         <v>8</v>
       </c>
-      <c r="B106" s="164">
-        <v>46181</v>
-      </c>
-      <c r="C106" s="11" t="s">
-        <v>157</v>
-      </c>
+      <c r="B106" s="231">
+        <v>46209</v>
+      </c>
+      <c r="C106" s="11"/>
       <c r="D106" s="12"/>
-      <c r="E106" s="228" t="s">
-        <v>175</v>
-      </c>
+      <c r="E106" s="19"/>
       <c r="F106" s="132"/>
       <c r="G106" s="132"/>
-      <c r="H106" s="240" t="s">
-        <v>257</v>
-      </c>
+      <c r="H106" s="208"/>
       <c r="I106" s="44"/>
-      <c r="J106" s="44" t="s">
-        <v>163</v>
-      </c>
-      <c r="K106" s="157">
+      <c r="J106" s="44"/>
+      <c r="K106" s="155">
         <v>4</v>
       </c>
-      <c r="L106" s="19" t="s">
-        <v>164</v>
-      </c>
+      <c r="L106" s="19"/>
       <c r="M106" s="26"/>
       <c r="N106" s="22"/>
     </row>
-    <row r="107" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A107" s="108"/>
-      <c r="B107" s="169"/>
+    <row r="107" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A107" s="237"/>
+      <c r="B107" s="238"/>
       <c r="C107" s="16"/>
       <c r="D107" s="17"/>
-      <c r="E107" s="225" t="s">
-        <v>176</v>
-      </c>
+      <c r="E107" s="18"/>
       <c r="F107" s="133"/>
       <c r="G107" s="133"/>
       <c r="H107" s="43"/>
@@ -4830,118 +4592,135 @@
       <c r="M107" s="26"/>
       <c r="N107" s="22"/>
     </row>
-    <row r="108" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A108" s="31" t="s">
+    <row r="108" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A108" s="239" t="s">
         <v>9</v>
       </c>
-      <c r="B108" s="164">
-        <v>46182</v>
-      </c>
-      <c r="C108" s="11" t="s">
-        <v>157</v>
-      </c>
+      <c r="B108" s="231">
+        <v>46210</v>
+      </c>
+      <c r="C108" s="11"/>
       <c r="D108" s="12"/>
-      <c r="E108" s="227" t="s">
-        <v>165</v>
-      </c>
+      <c r="E108" s="13"/>
       <c r="F108" s="123"/>
       <c r="G108" s="123"/>
-      <c r="H108" s="42" t="s">
-        <v>258</v>
-      </c>
+      <c r="H108" s="42"/>
       <c r="I108" s="42"/>
-      <c r="J108" s="46" t="s">
-        <v>166</v>
-      </c>
-      <c r="K108" s="171">
+      <c r="J108" s="46"/>
+      <c r="K108" s="169">
         <v>2.8</v>
       </c>
-      <c r="L108" s="24" t="s">
-        <v>167</v>
-      </c>
+      <c r="L108" s="24"/>
       <c r="M108" s="22"/>
       <c r="N108" s="21"/>
     </row>
-    <row r="109" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A109" s="56"/>
-      <c r="B109" s="165"/>
-      <c r="C109" s="14"/>
-      <c r="D109" s="198"/>
-      <c r="E109" s="179" t="s">
-        <v>100</v>
+    <row r="109" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A109" s="232"/>
+      <c r="B109" s="240"/>
+      <c r="C109" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="D109" s="184"/>
+      <c r="E109" s="22" t="s">
+        <v>187</v>
       </c>
       <c r="F109" s="134"/>
       <c r="G109" s="134"/>
-      <c r="H109" s="151"/>
+      <c r="H109" s="241" t="s">
+        <v>215</v>
+      </c>
       <c r="I109" s="135"/>
       <c r="J109" s="40"/>
-      <c r="K109" s="172"/>
+      <c r="K109" s="170"/>
       <c r="L109" s="21"/>
       <c r="M109" s="22"/>
       <c r="N109" s="57"/>
     </row>
-    <row r="110" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A110" s="56"/>
-      <c r="B110" s="168"/>
+    <row r="110" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A110" s="232"/>
+      <c r="B110" s="233"/>
       <c r="C110" s="14"/>
-      <c r="D110" s="198"/>
-      <c r="E110" s="179"/>
+      <c r="D110" s="184"/>
+      <c r="E110" s="15"/>
       <c r="F110" s="124"/>
       <c r="G110" s="124"/>
       <c r="H110" s="38"/>
       <c r="I110" s="38"/>
       <c r="J110" s="49"/>
-      <c r="K110" s="156"/>
+      <c r="K110" s="154"/>
       <c r="L110" s="79"/>
       <c r="M110" s="27"/>
       <c r="N110" s="88"/>
     </row>
-    <row r="111" spans="1:15" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A111" s="41"/>
-      <c r="B111" s="166"/>
+    <row r="111" spans="1:15" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A111" s="234"/>
+      <c r="B111" s="235"/>
       <c r="C111" s="16" t="s">
         <v>3</v>
       </c>
-      <c r="D111" s="231"/>
-      <c r="E111" s="131" t="s">
-        <v>219</v>
-      </c>
-      <c r="F111" s="152" t="s">
-        <v>31</v>
-      </c>
-      <c r="G111" s="152"/>
-      <c r="H111" s="78" t="s">
-        <v>259</v>
+      <c r="D111" s="17"/>
+      <c r="E111" s="226" t="s">
+        <v>188</v>
+      </c>
+      <c r="F111" s="150" t="s">
+        <v>150</v>
+      </c>
+      <c r="G111" s="150"/>
+      <c r="H111" s="241" t="s">
+        <v>216</v>
       </c>
       <c r="I111" s="78"/>
-      <c r="J111" s="43" t="s">
-        <v>184</v>
-      </c>
+      <c r="J111" s="43"/>
       <c r="K111" s="18"/>
-      <c r="L111" s="197"/>
+      <c r="L111" s="183"/>
       <c r="M111" s="94"/>
       <c r="N111" s="95"/>
     </row>
-    <row r="113" spans="5:5" x14ac:dyDescent="0.3">
+    <row r="113" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E113" s="110" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="114" spans="5:5" ht="110.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="E114" s="111" t="s">
-        <v>260</v>
-      </c>
+    <row r="114" spans="5:5" ht="110.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E114" s="111"/>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="H22" r:id="rId1" display="https://www.allocine.fr/personne/fichepersonne_gen_cpersonne=745759.html" xr:uid="{D102DE13-2E86-4BBA-BB2F-4AC636EDE4DB}"/>
+    <hyperlink ref="H23" r:id="rId2" display="https://www.allocine.fr/personne/fichepersonne_gen_cpersonne=104291.html" xr:uid="{554F26B6-42B7-41CE-B26E-4FB1ADC9FDF5}"/>
+    <hyperlink ref="H24" r:id="rId3" display="https://www.allocine.fr/personne/fichepersonne_gen_cpersonne=824218.html" xr:uid="{D9589355-F6B0-4947-87F2-26B3F9D6F988}"/>
+    <hyperlink ref="H30" r:id="rId4" display="https://www.allocine.fr/personne/fichepersonne_gen_cpersonne=816044.html" xr:uid="{2C65D40A-1871-4C37-A909-5A367C0CED9D}"/>
+    <hyperlink ref="H35" r:id="rId5" display="https://www.allocine.fr/personne/fichepersonne_gen_cpersonne=26775.html" xr:uid="{E99DA839-9EAE-46C8-9966-8157BE556500}"/>
+    <hyperlink ref="H39" r:id="rId6" display="https://www.allocine.fr/personne/fichepersonne_gen_cpersonne=104291.html" xr:uid="{22AE17EF-CD25-4EC9-B854-8039426D8BDB}"/>
+    <hyperlink ref="H40" r:id="rId7" display="https://www.allocine.fr/personne/fichepersonne_gen_cpersonne=250774.html" xr:uid="{F6B24DBD-649F-4907-81AD-ED0573F0AD82}"/>
+    <hyperlink ref="H41" r:id="rId8" display="https://www.allocine.fr/personne/fichepersonne_gen_cpersonne=253074.html" xr:uid="{A9A5BD63-BA19-4C1D-803A-3F70DA0B7D2D}"/>
+    <hyperlink ref="H43" r:id="rId9" display="https://www.allocine.fr/personne/fichepersonne_gen_cpersonne=1000027639.html" xr:uid="{06A588E2-B740-4E9A-AE88-7E7B14EEB3A7}"/>
+    <hyperlink ref="H45" r:id="rId10" display="https://www.allocine.fr/personne/fichepersonne_gen_cpersonne=990126.html" xr:uid="{5D1340E0-BC03-4805-BCF3-AC059BC4A7E5}"/>
+    <hyperlink ref="H49" r:id="rId11" display="https://www.allocine.fr/personne/fichepersonne_gen_cpersonne=433596.html" xr:uid="{DBDA1A8A-0174-45DA-B890-3E8A2083A289}"/>
+    <hyperlink ref="H57" r:id="rId12" display="https://www.allocine.fr/personne/fichepersonne_gen_cpersonne=11282.html" xr:uid="{19095CDA-1362-4C52-B0EB-F25D1C4DA6EC}"/>
+    <hyperlink ref="H66" r:id="rId13" display="https://www.allocine.fr/personne/fichepersonne_gen_cpersonne=24248.html" xr:uid="{D435704D-57FD-4D64-A80C-3FB5769690EA}"/>
+    <hyperlink ref="H68" r:id="rId14" display="https://www.allocine.fr/personne/fichepersonne_gen_cpersonne=600795.html" xr:uid="{79FC6525-DE11-4E21-893F-2FD308A3249A}"/>
+    <hyperlink ref="H70" r:id="rId15" display="https://www.allocine.fr/personne/fichepersonne_gen_cpersonne=588933.html" xr:uid="{F79AC834-FA50-4FA3-BB34-CF0340424B5B}"/>
+    <hyperlink ref="H76" r:id="rId16" display="https://www.allocine.fr/personne/fichepersonne_gen_cpersonne=692388.html" xr:uid="{0865C441-72E3-4C69-89BB-BECCE1FCEE47}"/>
+    <hyperlink ref="H77" r:id="rId17" display="https://www.allocine.fr/personne/fichepersonne_gen_cpersonne=8400.html" xr:uid="{E4F31BF2-49D4-49B1-80B9-F2756FF0D2A4}"/>
+    <hyperlink ref="H78" r:id="rId18" display="https://www.allocine.fr/personne/fichepersonne_gen_cpersonne=146639.html" xr:uid="{0D3ACA65-D1C8-449A-9B0A-EDA503AA0CCD}"/>
+    <hyperlink ref="H84" r:id="rId19" display="https://www.allocine.fr/personne/fichepersonne_gen_cpersonne=11732.html" xr:uid="{178B91DA-3501-4B85-A8A1-FA531BFCF581}"/>
+    <hyperlink ref="H89" r:id="rId20" display="https://www.allocine.fr/personne/fichepersonne_gen_cpersonne=579873.html" xr:uid="{E2395DDC-9F0A-43A0-834C-3A30AAB6EAEC}"/>
+    <hyperlink ref="H99" r:id="rId21" display="https://www.allocine.fr/personne/fichepersonne_gen_cpersonne=579873.html" xr:uid="{66DC094A-D44A-42AE-9294-5E96086C33FA}"/>
+    <hyperlink ref="H101" r:id="rId22" display="https://www.allocine.fr/personne/fichepersonne_gen_cpersonne=658205.html" xr:uid="{FADFA2EE-7C7E-4BC1-AECA-BDED4215825C}"/>
+    <hyperlink ref="H105" r:id="rId23" display="https://www.allocine.fr/personne/fichepersonne_gen_cpersonne=14352.html" xr:uid="{5B50020C-4F64-408A-84D4-6D4D2092B7B1}"/>
+    <hyperlink ref="H109" r:id="rId24" display="https://www.allocine.fr/personne/fichepersonne_gen_cpersonne=55361.html" xr:uid="{A1F69754-CD4B-47AC-A844-21F4E227CD58}"/>
+    <hyperlink ref="H111" r:id="rId25" display="https://www.allocine.fr/personne/fichepersonne_gen_cpersonne=20968.html" xr:uid="{0D6889D5-2497-4E96-8590-8D1DAF79BDF0}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" scale="37" orientation="portrait" horizontalDpi="4294967293" verticalDpi="4294967293" r:id="rId1"/>
+  <pageSetup paperSize="9" scale="37" orientation="portrait" horizontalDpi="4294967293" verticalDpi="4294967293" r:id="rId26"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{19D8F6E0-B935-4442-A9F9-93EFDE55CF19}">
   <dimension ref="A1"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/outils/input/source.xlsx
+++ b/outils/input/source.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\_Boulots\Cine Carbonne\Site\Site_Github_rep\outils\input\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A1B0632B-A064-4C93-9166-939838591789}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16E972F6-8499-48D8-8AE5-B20A05972935}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" tabRatio="587" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="21840" windowHeight="13740" tabRatio="587" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="325" uniqueCount="222">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="326" uniqueCount="222">
   <si>
     <t>Semaine</t>
   </si>
@@ -2536,7 +2536,9 @@
       <c r="E16" s="22" t="s">
         <v>157</v>
       </c>
-      <c r="F16" s="129"/>
+      <c r="F16" s="129" t="s">
+        <v>150</v>
+      </c>
       <c r="G16" s="150"/>
       <c r="H16" s="188" t="s">
         <v>190</v>

--- a/outils/input/source.xlsx
+++ b/outils/input/source.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="26924"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\_Boulots\Cine Carbonne\Site\Site_Github_rep\outils\input\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\didie\OneDrive\000 CINE CARBONNE 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16E972F6-8499-48D8-8AE5-B20A05972935}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{2662CD5E-519A-41A8-A7C5-B98056FE6086}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="21840" windowHeight="13740" tabRatio="587" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="587" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="326" uniqueCount="222">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="317" uniqueCount="202">
   <si>
     <t>Semaine</t>
   </si>
@@ -120,9 +120,6 @@
     <t>Séances spéciales</t>
   </si>
   <si>
-    <t>Prochainement</t>
-  </si>
-  <si>
     <t>VO/VF</t>
   </si>
   <si>
@@ -219,6 +216,9 @@
     <t xml:space="preserve">Scarlet et l'éternité JP ados à partir de 9/10 ans </t>
   </si>
   <si>
+    <t>Théâtre 107</t>
+  </si>
+  <si>
     <t>Sorda VO</t>
   </si>
   <si>
@@ -285,18 +285,30 @@
     <t>CM6 : Plan V - Documentaire - 03'00 (du 3/6 au 7/7)</t>
   </si>
   <si>
-    <t>TU 3 €</t>
-  </si>
-  <si>
-    <t>JP Famille TU 4,50 €</t>
-  </si>
-  <si>
     <t>TU 4,50 €</t>
   </si>
   <si>
     <t>Ouverture Cannes 2026</t>
   </si>
   <si>
+    <t>Ecole Chanfreau</t>
+  </si>
+  <si>
+    <t>Danse à l'école</t>
+  </si>
+  <si>
+    <t>Etablissement La Grange (à partir de 14h)</t>
+  </si>
+  <si>
+    <t>MJC</t>
+  </si>
+  <si>
+    <t>Conférence Marie</t>
+  </si>
+  <si>
+    <t>Danse Cathy-Line</t>
+  </si>
+  <si>
     <t>TU 5 €</t>
   </si>
   <si>
@@ -306,7 +318,10 @@
     <t>Ciné Jeunes du samedi 18h</t>
   </si>
   <si>
-    <t xml:space="preserve">Ciné Jeunes du samedi 18h </t>
+    <t>Com Educ 18h30</t>
+  </si>
+  <si>
+    <t>Fête école</t>
   </si>
   <si>
     <t>Le diable s'habille en Prada 2 VO</t>
@@ -462,27 +477,54 @@
     <t>10h</t>
   </si>
   <si>
+    <t>Minuscule 1</t>
+  </si>
+  <si>
     <t>SCOL</t>
   </si>
   <si>
     <t>14h</t>
   </si>
   <si>
+    <t>Zootopia 2</t>
+  </si>
+  <si>
     <t>Filmo 3,50 €</t>
   </si>
   <si>
+    <t>Ec Marquefave mater</t>
+  </si>
+  <si>
+    <t>Ec Marquefave élem</t>
+  </si>
+  <si>
     <t>9h30</t>
   </si>
   <si>
+    <t>Tout en haut du monde</t>
+  </si>
+  <si>
+    <t>Chanfreau élem</t>
+  </si>
+  <si>
     <t>Gratuit</t>
   </si>
   <si>
+    <t>Film fourni par l'école - film de l'année scolaire (ordi)</t>
+  </si>
+  <si>
     <t>14h?</t>
   </si>
   <si>
     <t>Gratuit - Voir avexc l'école pour précisions</t>
   </si>
   <si>
+    <t>Rencontres vidéos scolaires</t>
+  </si>
+  <si>
+    <t>Film fourni par William circo (ordi)</t>
+  </si>
+  <si>
     <t xml:space="preserve">L'être aimé VO Cannes 2026 Compétition </t>
   </si>
   <si>
@@ -492,214 +534,112 @@
     <t>Prix Sang neuf Reims Polar 2026</t>
   </si>
   <si>
-    <t>Father</t>
-  </si>
-  <si>
-    <t>Tereza Nvotova</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Cannes 2026 Hors compétition</t>
-  </si>
-  <si>
-    <t>Cannes 2026 Hors compétition</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cannes 2026 Compétition </t>
+    <t xml:space="preserve">Father </t>
+  </si>
+  <si>
+    <t xml:space="preserve">L'odyssée de Céleste </t>
+  </si>
+  <si>
+    <t>Cannes 2026 Sélection officielle Compétition</t>
+  </si>
+  <si>
+    <t>Découverte</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The new west </t>
   </si>
   <si>
     <t xml:space="preserve">L'être aimé </t>
   </si>
   <si>
-    <t>L'odyssée de Céleste</t>
-  </si>
-  <si>
-    <t>Histoires parralèles</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Cannes 2026 Compétition</t>
-  </si>
-  <si>
-    <t>The new west</t>
-  </si>
-  <si>
-    <t>Cannes 2026 Compétition</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Prix Carbonne</t>
-  </si>
-  <si>
-    <t>Le garçon qui faisait danser les collines</t>
-  </si>
-  <si>
-    <t>Nouveaux copains à Puffin Rock</t>
-  </si>
-  <si>
-    <t>Star wars The Mandalorian and Grogu</t>
-  </si>
-  <si>
-    <t xml:space="preserve">VO </t>
-  </si>
-  <si>
-    <t>CHaO</t>
-  </si>
-  <si>
-    <t>Autofiction</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> (à partir de 14h)</t>
-  </si>
-  <si>
-    <t>La vénus électrique</t>
-  </si>
-  <si>
-    <t>L'être aimé</t>
-  </si>
-  <si>
-    <t>D'un monde à l'autre</t>
-  </si>
-  <si>
-    <t>Colony</t>
-  </si>
-  <si>
-    <t>Super Mario Galaxy Le film</t>
-  </si>
-  <si>
-    <t>L'objet du délit</t>
-  </si>
-  <si>
-    <t>Cannes 2026 Hors Compétition</t>
+    <t>Coup de cœur</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Histoires parralèles </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nouveaux copains à Puffin Rock </t>
+  </si>
+  <si>
+    <t>3 Prix Festival Carbonne</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le garçon qui faisait danser les collines </t>
+  </si>
+  <si>
+    <t xml:space="preserve">CHaO </t>
+  </si>
+  <si>
+    <t xml:space="preserve">JP Famille </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Autofiction </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Star wars The Mandalorian and Grogu </t>
+  </si>
+  <si>
+    <t>Cannes 2026 Sélection officielle Hors compétition</t>
+  </si>
+  <si>
+    <t xml:space="preserve">La vénus électrique </t>
+  </si>
+  <si>
+    <t xml:space="preserve">D'un monde à l'autre </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Colony </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Super Mario Galaxy Le film </t>
+  </si>
+  <si>
+    <t xml:space="preserve">L'objet du délit </t>
   </si>
   <si>
     <t xml:space="preserve">Le vertige </t>
   </si>
   <si>
-    <t>Cannes 2026 Cannes Quinzaine des cinéastes</t>
-  </si>
-  <si>
-    <t>The Christophers</t>
+    <t xml:space="preserve">The Christophers </t>
+  </si>
+  <si>
+    <t>Cannes 2026 Cannes Quinzaine des cinéastes Compétition</t>
   </si>
   <si>
     <t>Deauville 2025 Prix du jury</t>
   </si>
   <si>
-    <t>Sur la route d'Omaha</t>
+    <t xml:space="preserve">Sur la route d'Omaha </t>
   </si>
   <si>
     <t>VF</t>
   </si>
   <si>
-    <t>La bataille de Gaulle L'âge de fer</t>
-  </si>
-  <si>
-    <t>Ulysse</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Clôture Un certain regard Cannes 2026 </t>
-  </si>
-  <si>
-    <t>Scarlet et l'éternité</t>
-  </si>
-  <si>
-    <t>L'illusion de Yakushima</t>
-  </si>
-  <si>
-    <t>Vincent Garenq</t>
-  </si>
-  <si>
-    <t>Rodrigo Sorogoyen</t>
-  </si>
-  <si>
-    <t>Kid Koala</t>
-  </si>
-  <si>
-    <t> Asghar Farhadi</t>
-  </si>
-  <si>
-    <t>Patrick Cassir</t>
-  </si>
-  <si>
-    <t>Kate Beecroft</t>
-  </si>
-  <si>
-    <t>Leonardo Di Costanzo</t>
-  </si>
-  <si>
-    <t>Rémi Chayé</t>
-  </si>
-  <si>
-    <t>Reem Kherici</t>
-  </si>
-  <si>
-    <t>Georgi M. Unkovski</t>
-  </si>
-  <si>
-    <t>Jeremy Purcell</t>
-  </si>
-  <si>
-    <t>Jon Favreau</t>
-  </si>
-  <si>
-    <t>Yasuhiro Aoki</t>
-  </si>
-  <si>
-    <t>Pedro Almodovar</t>
-  </si>
-  <si>
-    <t>Pierre Salvadori</t>
-  </si>
-  <si>
-    <t>Jérémie Renier</t>
-  </si>
-  <si>
-    <t>Fabien Gorgeart</t>
-  </si>
-  <si>
-    <t>Sang-Ho Yeon</t>
-  </si>
-  <si>
-    <t> Aaron Horvath</t>
-  </si>
-  <si>
-    <t> Agnès Jaoui</t>
-  </si>
-  <si>
-    <t>Quentin Dupieux</t>
-  </si>
-  <si>
-    <t>Steven Soderbergh</t>
-  </si>
-  <si>
-    <t>Cole Webley</t>
-  </si>
-  <si>
-    <t>pedro almodovar</t>
-  </si>
-  <si>
-    <t>Antonin Baudry</t>
-  </si>
-  <si>
-    <t>Laetitia Masson</t>
-  </si>
-  <si>
-    <t>Mamoru Hosoda</t>
-  </si>
-  <si>
-    <t>Naomi Kawase</t>
-  </si>
-  <si>
-    <t>Minuscule</t>
-  </si>
-  <si>
-    <t>Zootopia 2</t>
-  </si>
-  <si>
-    <t>Tout en haut du monde</t>
-  </si>
-  <si>
-    <t>Etablissement La Grange (à partir de 14h)</t>
-  </si>
-  <si>
-    <t>Rencontres vidéos scolaires</t>
+    <t xml:space="preserve">La bataille de Gaulle L'âge de fer </t>
+  </si>
+  <si>
+    <t>TU4,50 €</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cannes 2026 Un certain regard </t>
+  </si>
+  <si>
+    <t xml:space="preserve">JP ados à partir de 9/10 ans </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Scarlet et l'éternité </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ulysse </t>
+  </si>
+  <si>
+    <t xml:space="preserve">L'illusion de Yakushima </t>
+  </si>
+  <si>
+    <t>DOC - Découverte</t>
+  </si>
+  <si>
+    <t>Le dernier souffle d'un yakusa, Disclosure day, Fils de personne, Ma famille chérie, Jim queen, Toy story 5, Shana, Des Minions et des monstres, Les caprices de l'enfant-roi, Sham, Les parfait(s) Arnaques en famille, Seuls les rebelles, Permis de détruire, La bataille de Gaulle J'écris ton nom, In waves, On l'appelait Robin des Bois...</t>
   </si>
 </sst>
 </file>
@@ -852,15 +792,16 @@
       <family val="2"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
       <sz val="8"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="Montserrat"/>
     </font>
   </fonts>
   <fills count="16">
@@ -1571,8 +1512,12 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1632,9 +1577,6 @@
     <xf numFmtId="8" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="8" fontId="8" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="13" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -1714,21 +1656,21 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="6" fontId="8" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1784,9 +1726,6 @@
     <xf numFmtId="0" fontId="5" fillId="14" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="15" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1827,11 +1766,15 @@
     <xf numFmtId="164" fontId="0" fillId="6" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="2"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="2" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Lien hypertexte" xfId="2" builtinId="8"/>
@@ -1866,9 +1809,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Thème Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Thème Office 2013 – 2022">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1906,7 +1849,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -2012,7 +1955,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -2154,7 +2097,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -2166,25 +2109,25 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:O114"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="10.85546875" style="157" customWidth="1"/>
-    <col min="3" max="3" width="8.28515625" customWidth="1"/>
+    <col min="2" max="2" width="10.88671875" style="159" customWidth="1"/>
+    <col min="3" max="3" width="8.33203125" customWidth="1"/>
     <col min="4" max="4" width="5" style="112" customWidth="1"/>
-    <col min="5" max="5" width="69.5703125" style="3" customWidth="1"/>
-    <col min="6" max="6" width="7.28515625" style="85" customWidth="1"/>
-    <col min="7" max="7" width="6.85546875" style="85" customWidth="1"/>
-    <col min="8" max="8" width="33.5703125" style="3" customWidth="1"/>
-    <col min="9" max="9" width="79.140625" style="3" customWidth="1"/>
-    <col min="10" max="10" width="35.28515625" style="2" customWidth="1"/>
-    <col min="11" max="11" width="20.7109375" style="2" customWidth="1"/>
+    <col min="5" max="5" width="69.5546875" style="3" customWidth="1"/>
+    <col min="6" max="6" width="7.33203125" style="85" customWidth="1"/>
+    <col min="7" max="7" width="6.88671875" style="85" customWidth="1"/>
+    <col min="8" max="8" width="33.5546875" style="3" customWidth="1"/>
+    <col min="9" max="9" width="79.109375" style="3" customWidth="1"/>
+    <col min="10" max="10" width="35.21875" style="2" customWidth="1"/>
+    <col min="11" max="11" width="20.77734375" style="2" customWidth="1"/>
     <col min="12" max="12" width="54" style="2" customWidth="1"/>
-    <col min="13" max="13" width="59.28515625" style="2" customWidth="1"/>
-    <col min="14" max="14" width="92.5703125" customWidth="1"/>
-    <col min="15" max="15" width="43.85546875" customWidth="1"/>
+    <col min="13" max="13" width="59.21875" style="2" customWidth="1"/>
+    <col min="14" max="14" width="92.5546875" customWidth="1"/>
+    <col min="15" max="15" width="43.88671875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="E1" s="101" t="s">
         <v>81</v>
       </c>
@@ -2193,42 +2136,42 @@
       <c r="H1" s="103"/>
       <c r="I1" s="101"/>
       <c r="J1" s="101"/>
-      <c r="K1" s="153"/>
+      <c r="K1" s="155"/>
       <c r="L1" s="101"/>
     </row>
-    <row r="2" spans="1:14" s="1" customFormat="1" ht="15.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="158"/>
+    <row r="2" spans="1:14" s="1" customFormat="1" ht="15.45" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B2" s="160"/>
       <c r="D2" s="113"/>
       <c r="E2" s="101" t="s">
         <v>82</v>
       </c>
-      <c r="F2" s="180"/>
+      <c r="F2" s="181"/>
       <c r="G2" s="104"/>
       <c r="H2" s="105"/>
       <c r="I2" s="101"/>
       <c r="J2" s="101"/>
-      <c r="K2" s="153"/>
+      <c r="K2" s="155"/>
       <c r="L2" s="101"/>
       <c r="M2" s="6"/>
     </row>
-    <row r="3" spans="1:14" s="71" customFormat="1" ht="21.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:14" s="71" customFormat="1" ht="21.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
-      <c r="B3" s="158"/>
+      <c r="B3" s="160"/>
       <c r="D3" s="114"/>
       <c r="E3" s="72" t="s">
         <v>14</v>
       </c>
       <c r="F3" s="115" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G3" s="86" t="s">
         <v>13</v>
       </c>
       <c r="H3" s="121" t="s">
+        <v>30</v>
+      </c>
+      <c r="I3" s="75" t="s">
         <v>31</v>
-      </c>
-      <c r="I3" s="75" t="s">
-        <v>32</v>
       </c>
       <c r="J3" s="73" t="s">
         <v>15</v>
@@ -2241,11 +2184,11 @@
       </c>
       <c r="M3" s="74"/>
     </row>
-    <row r="4" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="159" t="s">
+    <row r="4" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="161" t="s">
         <v>0</v>
       </c>
-      <c r="B4" s="160">
+      <c r="B4" s="162">
         <v>46183</v>
       </c>
       <c r="C4" s="7"/>
@@ -2265,14 +2208,14 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A5" s="161" t="s">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A5" s="163" t="s">
         <v>1</v>
       </c>
-      <c r="B5" s="162">
+      <c r="B5" s="164">
         <v>46183</v>
       </c>
-      <c r="C5" s="206"/>
+      <c r="C5" s="207"/>
       <c r="D5" s="12"/>
       <c r="E5" s="81"/>
       <c r="F5" s="123"/>
@@ -2283,17 +2226,17 @@
       <c r="K5" s="13"/>
       <c r="L5" s="13"/>
       <c r="M5" s="55" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="N5" s="22" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A6" s="27"/>
-      <c r="B6" s="163"/>
+      <c r="B6" s="165"/>
       <c r="C6" s="14"/>
-      <c r="D6" s="184"/>
+      <c r="D6" s="185"/>
       <c r="E6" s="15"/>
       <c r="F6" s="124"/>
       <c r="G6" s="124"/>
@@ -2303,17 +2246,17 @@
       <c r="K6" s="15"/>
       <c r="L6" s="15"/>
       <c r="M6" s="55" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="N6" s="22" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A7" s="27"/>
-      <c r="B7" s="163"/>
+      <c r="B7" s="165"/>
       <c r="C7" s="14"/>
-      <c r="D7" s="184"/>
+      <c r="D7" s="185"/>
       <c r="E7" s="15"/>
       <c r="F7" s="124"/>
       <c r="G7" s="124"/>
@@ -2324,88 +2267,90 @@
       <c r="L7" s="15"/>
       <c r="M7" s="55"/>
       <c r="N7" s="66" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="8" spans="1:14" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A8" s="41"/>
-      <c r="B8" s="164"/>
+      <c r="B8" s="166"/>
       <c r="C8" s="16" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="17"/>
-      <c r="E8" s="55" t="s">
-        <v>152</v>
+      <c r="E8" s="241" t="s">
+        <v>166</v>
       </c>
       <c r="F8" s="125" t="s">
-        <v>150</v>
+        <v>164</v>
       </c>
       <c r="G8" s="125"/>
-      <c r="H8" s="179" t="s">
-        <v>153</v>
-      </c>
+      <c r="H8" s="180"/>
       <c r="I8" s="37" t="s">
-        <v>151</v>
-      </c>
-      <c r="J8" s="43"/>
+        <v>165</v>
+      </c>
+      <c r="J8" s="43" t="s">
+        <v>172</v>
+      </c>
       <c r="K8" s="18"/>
       <c r="L8" s="100"/>
       <c r="M8" s="20" t="s">
         <v>62</v>
       </c>
       <c r="N8" s="61" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A9" s="165" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A9" s="167" t="s">
         <v>2</v>
       </c>
-      <c r="B9" s="162">
+      <c r="B9" s="164">
         <v>46184</v>
       </c>
       <c r="C9" s="11"/>
       <c r="D9" s="12"/>
-      <c r="E9" s="174"/>
+      <c r="E9" s="175" t="s">
+        <v>86</v>
+      </c>
       <c r="F9" s="127"/>
       <c r="G9" s="127"/>
       <c r="H9" s="128"/>
       <c r="I9" s="128"/>
       <c r="J9" s="44"/>
       <c r="K9" s="19"/>
-      <c r="L9" s="172"/>
+      <c r="L9" s="173"/>
       <c r="M9" s="22" t="s">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="N9" s="61" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A10" s="56"/>
-      <c r="B10" s="163"/>
+      <c r="B10" s="165"/>
       <c r="C10" s="14"/>
-      <c r="D10" s="184"/>
-      <c r="E10" s="212"/>
+      <c r="D10" s="185"/>
+      <c r="E10" s="213"/>
       <c r="F10" s="83"/>
       <c r="G10" s="83"/>
       <c r="H10" s="67"/>
       <c r="I10" s="67"/>
       <c r="J10" s="45"/>
-      <c r="K10" s="152"/>
+      <c r="K10" s="154"/>
       <c r="M10" s="22" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="N10" s="66" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="11" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="56"/>
-      <c r="B11" s="166"/>
+      <c r="B11" s="168"/>
       <c r="C11" s="14"/>
-      <c r="D11" s="184"/>
-      <c r="E11" s="173"/>
+      <c r="D11" s="185"/>
+      <c r="E11" s="174"/>
       <c r="F11" s="125"/>
       <c r="G11" s="125"/>
       <c r="H11" s="37"/>
@@ -2414,105 +2359,107 @@
       <c r="K11" s="26"/>
       <c r="L11" s="26"/>
       <c r="M11" s="22" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="N11" s="26" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="12" spans="1:14" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A12" s="41"/>
-      <c r="B12" s="164"/>
+      <c r="B12" s="166"/>
       <c r="C12" s="16" t="s">
         <v>3</v>
       </c>
       <c r="D12" s="227"/>
       <c r="E12" s="22" t="s">
-        <v>140</v>
+        <v>113</v>
       </c>
       <c r="F12" s="129"/>
       <c r="G12" s="129"/>
-      <c r="H12" s="179" t="s">
-        <v>189</v>
-      </c>
+      <c r="H12" s="180"/>
       <c r="I12" s="78" t="s">
-        <v>155</v>
+        <v>181</v>
       </c>
       <c r="J12" s="43"/>
       <c r="K12" s="18"/>
       <c r="L12" s="18"/>
       <c r="M12" s="22" t="s">
-        <v>149</v>
+        <v>163</v>
       </c>
       <c r="N12" s="66" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A13" s="165" t="s">
+    <row r="13" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A13" s="167" t="s">
         <v>4</v>
       </c>
-      <c r="B13" s="162">
+      <c r="B13" s="164">
         <v>46185</v>
       </c>
       <c r="C13" s="11" t="s">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="D13" s="12"/>
-      <c r="E13" s="221" t="s">
-        <v>217</v>
-      </c>
-      <c r="F13" s="185"/>
-      <c r="G13" s="186"/>
+      <c r="E13" s="222" t="s">
+        <v>147</v>
+      </c>
+      <c r="F13" s="186"/>
+      <c r="G13" s="187"/>
       <c r="H13"/>
       <c r="I13" s="31"/>
       <c r="J13" s="46" t="s">
-        <v>142</v>
-      </c>
-      <c r="K13" s="152" t="s">
-        <v>144</v>
-      </c>
-      <c r="L13" s="24"/>
+        <v>148</v>
+      </c>
+      <c r="K13" s="154" t="s">
+        <v>151</v>
+      </c>
+      <c r="L13" s="24" t="s">
+        <v>152</v>
+      </c>
       <c r="M13" s="20" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="N13" s="25" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="14" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="25"/>
-      <c r="B14" s="166"/>
+      <c r="B14" s="168"/>
       <c r="C14" s="14" t="s">
-        <v>143</v>
-      </c>
-      <c r="D14" s="184"/>
-      <c r="E14" s="222" t="s">
-        <v>218</v>
+        <v>149</v>
+      </c>
+      <c r="D14" s="185"/>
+      <c r="E14" s="223" t="s">
+        <v>150</v>
       </c>
       <c r="F14" s="130"/>
-      <c r="G14" s="187"/>
-      <c r="H14" s="241"/>
+      <c r="G14" s="188"/>
+      <c r="H14"/>
       <c r="I14" s="146"/>
       <c r="J14" s="40" t="s">
-        <v>142</v>
-      </c>
-      <c r="K14" s="152" t="s">
-        <v>144</v>
-      </c>
-      <c r="L14" s="26"/>
+        <v>148</v>
+      </c>
+      <c r="K14" s="154" t="s">
+        <v>151</v>
+      </c>
+      <c r="L14" s="26" t="s">
+        <v>153</v>
+      </c>
       <c r="M14" s="22" t="s">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="N14" s="120" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="15" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="27"/>
-      <c r="B15" s="166"/>
+      <c r="B15" s="168"/>
       <c r="C15" s="14"/>
-      <c r="D15" s="184"/>
+      <c r="D15" s="185"/>
       <c r="E15" s="26"/>
       <c r="F15" s="129"/>
       <c r="G15" s="129"/>
@@ -2526,48 +2473,48 @@
         <v>63</v>
       </c>
     </row>
-    <row r="16" spans="1:14" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:14" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A16" s="41"/>
-      <c r="B16" s="164"/>
+      <c r="B16" s="166"/>
       <c r="C16" s="16" t="s">
         <v>3</v>
       </c>
       <c r="D16" s="227"/>
       <c r="E16" s="22" t="s">
-        <v>157</v>
+        <v>171</v>
       </c>
       <c r="F16" s="129" t="s">
-        <v>150</v>
-      </c>
-      <c r="G16" s="150"/>
-      <c r="H16" s="188" t="s">
-        <v>190</v>
-      </c>
+        <v>164</v>
+      </c>
+      <c r="G16" s="152"/>
+      <c r="H16" s="189"/>
       <c r="I16" s="40" t="s">
-        <v>156</v>
+        <v>168</v>
       </c>
       <c r="J16" s="97"/>
       <c r="K16" s="77"/>
       <c r="L16" s="100"/>
       <c r="M16" s="21"/>
-      <c r="N16" s="171" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="17" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A17" s="165" t="s">
+      <c r="N16" s="172" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A17" s="167" t="s">
         <v>5</v>
       </c>
-      <c r="B17" s="162">
+      <c r="B17" s="164">
         <v>46186</v>
       </c>
       <c r="C17" s="11"/>
       <c r="D17" s="12"/>
-      <c r="E17" s="210"/>
-      <c r="F17" s="189"/>
-      <c r="G17" s="189"/>
-      <c r="H17" s="190"/>
-      <c r="I17" s="190"/>
+      <c r="E17" s="211" t="s">
+        <v>60</v>
+      </c>
+      <c r="F17" s="190"/>
+      <c r="G17" s="190"/>
+      <c r="H17" s="191"/>
+      <c r="I17" s="191"/>
       <c r="J17" s="42"/>
       <c r="K17" s="122"/>
       <c r="L17" s="13"/>
@@ -2575,62 +2522,54 @@
         <v>68</v>
       </c>
     </row>
-    <row r="18" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A18" s="56"/>
-      <c r="B18" s="163"/>
+      <c r="B18" s="165"/>
       <c r="C18" s="14" t="s">
         <v>11</v>
       </c>
-      <c r="D18" s="184"/>
-      <c r="E18" s="175"/>
+      <c r="D18" s="185"/>
+      <c r="E18" s="176"/>
       <c r="F18" s="125"/>
       <c r="G18" s="125"/>
       <c r="H18" s="25"/>
       <c r="I18" s="37"/>
-      <c r="J18" s="45" t="s">
-        <v>25</v>
-      </c>
-      <c r="K18" s="15" t="s">
-        <v>83</v>
-      </c>
+      <c r="J18" s="45"/>
+      <c r="K18" s="15"/>
       <c r="L18" s="15"/>
       <c r="M18" s="57"/>
       <c r="N18" s="66" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="19" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="56"/>
-      <c r="B19" s="166"/>
+      <c r="B19" s="168"/>
       <c r="C19" s="14" t="s">
         <v>6</v>
       </c>
-      <c r="D19" s="184"/>
-      <c r="E19" s="175"/>
+      <c r="D19" s="185"/>
+      <c r="E19" s="176"/>
       <c r="F19" s="83"/>
       <c r="G19" s="83"/>
       <c r="H19" s="67"/>
       <c r="I19" s="67"/>
-      <c r="J19" s="178" t="s">
-        <v>90</v>
-      </c>
-      <c r="K19" s="15" t="s">
-        <v>34</v>
-      </c>
+      <c r="J19" s="179"/>
+      <c r="K19" s="15"/>
       <c r="L19" s="15"/>
       <c r="M19" s="22"/>
       <c r="N19" s="22" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="20" spans="1:14" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:14" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A20" s="41"/>
-      <c r="B20" s="164"/>
+      <c r="B20" s="166"/>
       <c r="C20" s="16" t="s">
         <v>3</v>
       </c>
       <c r="D20" s="17"/>
-      <c r="E20" s="211"/>
+      <c r="E20" s="212"/>
       <c r="F20" s="125"/>
       <c r="G20" s="125"/>
       <c r="H20" s="37"/>
@@ -2643,11 +2582,11 @@
         <v>71</v>
       </c>
     </row>
-    <row r="21" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A21" s="165" t="s">
+    <row r="21" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A21" s="167" t="s">
         <v>7</v>
       </c>
-      <c r="B21" s="162">
+      <c r="B21" s="164">
         <v>46187</v>
       </c>
       <c r="C21" s="28"/>
@@ -2665,74 +2604,70 @@
         <v>72</v>
       </c>
     </row>
-    <row r="22" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="56"/>
-      <c r="B22" s="163"/>
+      <c r="B22" s="165"/>
       <c r="C22" s="14" t="s">
         <v>11</v>
       </c>
-      <c r="D22" s="184"/>
+      <c r="D22" s="185"/>
       <c r="E22" s="61" t="s">
-        <v>158</v>
+        <v>167</v>
       </c>
       <c r="F22" s="125"/>
       <c r="G22" s="125"/>
-      <c r="H22" s="241" t="s">
-        <v>191</v>
-      </c>
+      <c r="H22" s="37"/>
       <c r="I22" s="37"/>
       <c r="J22" s="45" t="s">
         <v>25</v>
       </c>
-      <c r="K22" s="15"/>
+      <c r="K22" s="15" t="s">
+        <v>194</v>
+      </c>
       <c r="L22" s="21"/>
       <c r="M22" s="27"/>
       <c r="N22" s="26" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="23" spans="1:14" ht="13.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:14" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="56"/>
-      <c r="B23" s="166"/>
+      <c r="B23" s="168"/>
       <c r="C23" s="14" t="s">
         <v>6</v>
       </c>
       <c r="D23" s="228"/>
       <c r="E23" s="22" t="s">
-        <v>159</v>
+        <v>173</v>
       </c>
       <c r="F23" s="125"/>
       <c r="G23" s="125"/>
-      <c r="H23" s="241" t="s">
-        <v>192</v>
-      </c>
+      <c r="H23" s="37"/>
       <c r="I23" s="37" t="s">
-        <v>160</v>
+        <v>168</v>
       </c>
       <c r="J23" s="45"/>
       <c r="K23" s="15"/>
       <c r="L23" s="27"/>
       <c r="M23" s="56"/>
       <c r="N23" s="66" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="24" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="24" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A24" s="41"/>
-      <c r="B24" s="164"/>
+      <c r="B24" s="166"/>
       <c r="C24" s="16" t="s">
         <v>3</v>
       </c>
       <c r="D24" s="17"/>
-      <c r="E24" s="55" t="s">
-        <v>98</v>
-      </c>
-      <c r="F24" s="191"/>
-      <c r="G24" s="192"/>
-      <c r="H24" s="242" t="s">
-        <v>193</v>
-      </c>
-      <c r="I24" s="193"/>
+      <c r="E24" s="241" t="s">
+        <v>103</v>
+      </c>
+      <c r="F24" s="192"/>
+      <c r="G24" s="193"/>
+      <c r="H24" s="194"/>
+      <c r="I24" s="194"/>
       <c r="J24" s="39"/>
       <c r="K24" s="78"/>
       <c r="L24" s="78"/>
@@ -2741,31 +2676,31 @@
         <v>76</v>
       </c>
     </row>
-    <row r="25" spans="1:14" ht="15.75" x14ac:dyDescent="0.3">
-      <c r="A25" s="165" t="s">
+    <row r="25" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A25" s="167" t="s">
         <v>8</v>
       </c>
-      <c r="B25" s="162">
+      <c r="B25" s="164">
         <v>46188</v>
       </c>
       <c r="C25" s="11"/>
       <c r="D25" s="12"/>
       <c r="E25" s="19"/>
       <c r="F25" s="132"/>
-      <c r="G25" s="194"/>
-      <c r="H25" s="243"/>
+      <c r="G25" s="195"/>
+      <c r="H25"/>
       <c r="I25" s="44"/>
       <c r="J25" s="44"/>
-      <c r="K25" s="155"/>
+      <c r="K25" s="157"/>
       <c r="L25" s="19"/>
       <c r="M25" s="26"/>
-      <c r="N25" s="171" t="s">
+      <c r="N25" s="172" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="26" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A26" s="108"/>
-      <c r="B26" s="167"/>
+      <c r="B26" s="169"/>
       <c r="C26" s="16"/>
       <c r="D26" s="17"/>
       <c r="E26" s="18"/>
@@ -2781,11 +2716,11 @@
         <v>78</v>
       </c>
     </row>
-    <row r="27" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="31" t="s">
         <v>9</v>
       </c>
-      <c r="B27" s="162">
+      <c r="B27" s="164">
         <v>46189</v>
       </c>
       <c r="C27" s="11"/>
@@ -2803,11 +2738,11 @@
         <v>75</v>
       </c>
     </row>
-    <row r="28" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A28" s="56"/>
-      <c r="B28" s="163"/>
+      <c r="B28" s="165"/>
       <c r="C28" s="14"/>
-      <c r="D28" s="184"/>
+      <c r="D28" s="185"/>
       <c r="E28" s="26"/>
       <c r="F28" s="134"/>
       <c r="G28" s="134"/>
@@ -2821,55 +2756,55 @@
         <v>61</v>
       </c>
     </row>
-    <row r="29" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="56"/>
-      <c r="B29" s="166"/>
+      <c r="B29" s="168"/>
       <c r="C29" s="14"/>
-      <c r="D29" s="184"/>
+      <c r="D29" s="185"/>
       <c r="E29" s="15"/>
       <c r="F29" s="124"/>
       <c r="G29" s="124"/>
       <c r="H29" s="38"/>
       <c r="I29" s="38"/>
       <c r="J29" s="49"/>
-      <c r="K29" s="154"/>
+      <c r="K29" s="156"/>
       <c r="L29" s="79"/>
       <c r="M29" s="27"/>
-      <c r="N29" s="171" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="30" spans="1:14" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="N29" s="172" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="30" spans="1:14" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A30" s="41"/>
-      <c r="B30" s="164"/>
+      <c r="B30" s="166"/>
       <c r="C30" s="16" t="s">
         <v>3</v>
       </c>
       <c r="D30" s="17"/>
       <c r="E30" s="22" t="s">
-        <v>161</v>
+        <v>170</v>
       </c>
       <c r="F30" s="129" t="s">
-        <v>150</v>
+        <v>164</v>
       </c>
       <c r="G30" s="129"/>
-      <c r="H30" s="241" t="s">
-        <v>194</v>
-      </c>
+      <c r="H30" s="40"/>
       <c r="I30" s="40"/>
-      <c r="J30" s="43"/>
+      <c r="J30" s="43" t="s">
+        <v>169</v>
+      </c>
       <c r="K30" s="18"/>
       <c r="L30" s="100"/>
       <c r="M30" s="58"/>
-      <c r="N30" s="220" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="31" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="159" t="s">
+      <c r="N30" s="221" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="31" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A31" s="161" t="s">
         <v>0</v>
       </c>
-      <c r="B31" s="168">
+      <c r="B31" s="170">
         <v>46190</v>
       </c>
       <c r="C31" s="7"/>
@@ -2886,14 +2821,14 @@
         <v>46162</v>
       </c>
       <c r="N31" s="61" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="32" spans="1:14" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="165" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="32" spans="1:14" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A32" s="167" t="s">
         <v>1</v>
       </c>
-      <c r="B32" s="162">
+      <c r="B32" s="164">
         <v>46190</v>
       </c>
       <c r="C32" s="12"/>
@@ -2907,15 +2842,15 @@
       <c r="K32" s="34"/>
       <c r="L32" s="34"/>
       <c r="M32" s="55" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="N32" s="25"/>
     </row>
-    <row r="33" spans="1:15" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:15" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="56"/>
-      <c r="B33" s="166"/>
+      <c r="B33" s="168"/>
       <c r="C33" s="14"/>
-      <c r="D33" s="184"/>
+      <c r="D33" s="185"/>
       <c r="E33" s="22"/>
       <c r="F33" s="130"/>
       <c r="G33" s="130"/>
@@ -2925,17 +2860,17 @@
       <c r="K33" s="26"/>
       <c r="L33" s="26"/>
       <c r="M33" s="55" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="N33" s="64" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="34" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="56"/>
-      <c r="B34" s="166"/>
+      <c r="B34" s="168"/>
       <c r="C34" s="14"/>
-      <c r="D34" s="184"/>
+      <c r="D34" s="185"/>
       <c r="E34" s="15"/>
       <c r="F34" s="124"/>
       <c r="G34" s="124"/>
@@ -2945,48 +2880,48 @@
       <c r="K34" s="27"/>
       <c r="L34" s="27"/>
       <c r="M34" s="60" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="N34" s="26" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="35" spans="1:15" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="35" spans="1:15" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A35" s="41"/>
-      <c r="B35" s="164"/>
+      <c r="B35" s="166"/>
       <c r="C35" s="16" t="s">
         <v>3</v>
       </c>
-      <c r="D35" s="215"/>
-      <c r="E35" s="55" t="s">
-        <v>100</v>
+      <c r="D35" s="216"/>
+      <c r="E35" s="241" t="s">
+        <v>105</v>
       </c>
       <c r="F35" s="129"/>
       <c r="G35" s="129"/>
-      <c r="H35" s="241" t="s">
-        <v>195</v>
-      </c>
-      <c r="I35" s="195"/>
+      <c r="H35" s="40"/>
+      <c r="I35" s="196"/>
       <c r="J35" s="97"/>
       <c r="K35" s="77"/>
       <c r="L35" s="99"/>
       <c r="M35" s="22" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="N35" s="22" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="36" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A36" s="165" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="36" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A36" s="167" t="s">
         <v>2</v>
       </c>
-      <c r="B36" s="218">
+      <c r="B36" s="219">
         <v>46191</v>
       </c>
       <c r="C36" s="119"/>
       <c r="D36" s="12"/>
-      <c r="E36" s="209"/>
+      <c r="E36" s="210" t="s">
+        <v>85</v>
+      </c>
       <c r="F36" s="123"/>
       <c r="G36" s="123"/>
       <c r="H36" s="42"/>
@@ -2995,18 +2930,18 @@
       <c r="K36" s="80"/>
       <c r="L36" s="80"/>
       <c r="M36" s="22" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="N36" s="61" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="37" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="37" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="56"/>
-      <c r="B37" s="166"/>
+      <c r="B37" s="168"/>
       <c r="C37" s="35"/>
-      <c r="D37" s="184"/>
-      <c r="E37" s="175"/>
+      <c r="D37" s="185"/>
+      <c r="E37" s="176"/>
       <c r="F37" s="125"/>
       <c r="G37" s="125"/>
       <c r="H37" s="67"/>
@@ -3015,18 +2950,18 @@
       <c r="K37" s="32"/>
       <c r="L37" s="32"/>
       <c r="M37" s="22" t="s">
-        <v>114</v>
-      </c>
-      <c r="N37" s="171" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="38" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>119</v>
+      </c>
+      <c r="N37" s="172" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="38" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="56"/>
-      <c r="B38" s="166"/>
+      <c r="B38" s="168"/>
       <c r="C38" s="35"/>
-      <c r="D38" s="184"/>
-      <c r="E38" s="204"/>
+      <c r="D38" s="185"/>
+      <c r="E38" s="205"/>
       <c r="F38" s="137"/>
       <c r="G38" s="137"/>
       <c r="H38" s="52"/>
@@ -3035,103 +2970,99 @@
       <c r="K38" s="32"/>
       <c r="L38" s="23"/>
       <c r="M38" s="26" t="s">
-        <v>115</v>
-      </c>
-      <c r="N38" s="182" t="s">
+        <v>120</v>
+      </c>
+      <c r="N38" s="183" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="39" spans="1:15" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:15" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A39" s="41"/>
-      <c r="B39" s="164"/>
+      <c r="B39" s="166"/>
       <c r="C39" s="16" t="s">
         <v>3</v>
       </c>
       <c r="D39" s="227"/>
       <c r="E39" s="22" t="s">
-        <v>159</v>
+        <v>173</v>
       </c>
       <c r="F39" s="129"/>
       <c r="G39" s="129"/>
-      <c r="H39" s="241" t="s">
-        <v>192</v>
-      </c>
+      <c r="H39" s="180"/>
       <c r="I39" s="40" t="s">
-        <v>162</v>
+        <v>168</v>
       </c>
       <c r="J39" s="97"/>
       <c r="K39" s="77"/>
       <c r="L39" s="99"/>
       <c r="M39" s="22" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="N39" s="25"/>
     </row>
-    <row r="40" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A40" s="165" t="s">
+    <row r="40" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A40" s="167" t="s">
         <v>4</v>
       </c>
-      <c r="B40" s="218">
+      <c r="B40" s="219">
         <v>46192</v>
       </c>
       <c r="C40" s="36" t="s">
-        <v>145</v>
+        <v>154</v>
       </c>
       <c r="D40" s="12"/>
-      <c r="E40" s="223" t="s">
-        <v>219</v>
+      <c r="E40" s="224" t="s">
+        <v>155</v>
       </c>
       <c r="F40" s="127"/>
       <c r="G40" s="127"/>
-      <c r="H40" s="241" t="s">
-        <v>196</v>
-      </c>
+      <c r="H40" s="128"/>
       <c r="I40" s="128"/>
       <c r="J40" s="53" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="K40" s="117" t="s">
-        <v>144</v>
-      </c>
-      <c r="L40" s="80"/>
+        <v>151</v>
+      </c>
+      <c r="L40" s="80" t="s">
+        <v>156</v>
+      </c>
       <c r="M40" s="22" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="N40" s="65"/>
     </row>
-    <row r="41" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="56"/>
-      <c r="B41" s="166"/>
+      <c r="B41" s="168"/>
       <c r="C41" s="35" t="s">
         <v>12</v>
       </c>
-      <c r="D41" s="184"/>
+      <c r="D41" s="185"/>
       <c r="E41" s="26" t="s">
         <v>75</v>
       </c>
       <c r="F41" s="130"/>
       <c r="G41" s="130"/>
-      <c r="H41" s="241" t="s">
-        <v>197</v>
-      </c>
+      <c r="H41" s="54"/>
       <c r="I41" s="54"/>
       <c r="J41" s="40" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="K41" s="26" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="L41" s="26"/>
       <c r="M41" s="22" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="N41" s="61"/>
     </row>
-    <row r="42" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" s="56"/>
-      <c r="B42" s="166"/>
+      <c r="B42" s="168"/>
       <c r="C42" s="14"/>
-      <c r="D42" s="184"/>
+      <c r="D42" s="185"/>
       <c r="E42" s="15"/>
       <c r="F42" s="124"/>
       <c r="G42" s="124"/>
@@ -3141,45 +3072,45 @@
       <c r="K42" s="27"/>
       <c r="L42" s="27"/>
       <c r="M42" s="22"/>
-      <c r="N42" s="151"/>
+      <c r="N42" s="153"/>
       <c r="O42" s="5"/>
     </row>
-    <row r="43" spans="1:15" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:15" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A43" s="41"/>
-      <c r="B43" s="164"/>
+      <c r="B43" s="166"/>
       <c r="C43" s="33" t="s">
         <v>3</v>
       </c>
       <c r="D43" s="227"/>
-      <c r="E43" s="55" t="s">
+      <c r="E43" s="241" t="s">
+        <v>176</v>
+      </c>
+      <c r="F43" s="129" t="s">
         <v>164</v>
       </c>
-      <c r="F43" s="129" t="s">
-        <v>150</v>
-      </c>
       <c r="G43" s="129"/>
-      <c r="H43" s="241" t="s">
-        <v>198</v>
-      </c>
+      <c r="H43" s="37"/>
       <c r="I43" s="40" t="s">
-        <v>163</v>
-      </c>
-      <c r="J43" s="97"/>
+        <v>175</v>
+      </c>
+      <c r="J43" s="97" t="s">
+        <v>172</v>
+      </c>
       <c r="K43" s="77"/>
       <c r="L43" s="99"/>
       <c r="M43" s="22"/>
       <c r="N43" s="22"/>
     </row>
-    <row r="44" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A44" s="165" t="s">
+    <row r="44" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A44" s="167" t="s">
         <v>5</v>
       </c>
-      <c r="B44" s="162">
+      <c r="B44" s="164">
         <v>46193</v>
       </c>
       <c r="C44" s="11"/>
       <c r="D44" s="12"/>
-      <c r="E44" s="196"/>
+      <c r="E44" s="197"/>
       <c r="F44" s="138"/>
       <c r="G44" s="138"/>
       <c r="H44" s="139"/>
@@ -3191,21 +3122,19 @@
       <c r="N44" s="26"/>
       <c r="O44" s="4"/>
     </row>
-    <row r="45" spans="1:15" ht="13.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:15" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A45" s="56"/>
-      <c r="B45" s="166"/>
+      <c r="B45" s="168"/>
       <c r="C45" s="35" t="s">
-        <v>138</v>
-      </c>
-      <c r="D45" s="197"/>
-      <c r="E45" s="60" t="s">
-        <v>165</v>
+        <v>143</v>
+      </c>
+      <c r="D45" s="198"/>
+      <c r="E45" s="242" t="s">
+        <v>174</v>
       </c>
       <c r="F45" s="140"/>
       <c r="G45" s="140"/>
-      <c r="H45" s="242" t="s">
-        <v>199</v>
-      </c>
+      <c r="H45" s="25"/>
       <c r="I45" s="141"/>
       <c r="J45" s="37" t="s">
         <v>80</v>
@@ -3215,60 +3144,58 @@
       <c r="M45" s="26"/>
       <c r="N45" s="61"/>
     </row>
-    <row r="46" spans="1:15" ht="13.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:15" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A46" s="56"/>
-      <c r="B46" s="166"/>
+      <c r="B46" s="168"/>
       <c r="C46" s="35" t="s">
         <v>6</v>
       </c>
       <c r="D46" s="229"/>
       <c r="E46" s="22" t="s">
-        <v>166</v>
+        <v>180</v>
       </c>
       <c r="F46" s="83" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="G46" s="83"/>
-      <c r="H46" s="142" t="s">
-        <v>200</v>
-      </c>
+      <c r="H46" s="67"/>
       <c r="I46" s="22"/>
       <c r="J46" s="38" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="K46" s="15" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="L46" s="15"/>
       <c r="M46" s="61"/>
       <c r="N46" s="61"/>
     </row>
-    <row r="47" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A47" s="41"/>
-      <c r="B47" s="164"/>
+      <c r="B47" s="166"/>
       <c r="C47" s="16" t="s">
         <v>3</v>
       </c>
       <c r="D47" s="227"/>
       <c r="E47" s="22" t="s">
-        <v>140</v>
-      </c>
-      <c r="F47" s="198"/>
-      <c r="G47" s="199"/>
-      <c r="H47" s="179" t="s">
-        <v>189</v>
-      </c>
-      <c r="I47" s="200"/>
+        <v>145</v>
+      </c>
+      <c r="F47" s="199"/>
+      <c r="G47" s="200"/>
+      <c r="H47" s="142"/>
+      <c r="I47" s="78" t="s">
+        <v>181</v>
+      </c>
       <c r="J47" s="39"/>
       <c r="K47" s="78"/>
       <c r="L47" s="30"/>
-      <c r="N47" s="151"/>
-    </row>
-    <row r="48" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A48" s="165" t="s">
+      <c r="N47" s="153"/>
+    </row>
+    <row r="48" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A48" s="167" t="s">
         <v>7</v>
       </c>
-      <c r="B48" s="162">
+      <c r="B48" s="164">
         <v>46194</v>
       </c>
       <c r="C48" s="12"/>
@@ -3279,63 +3206,61 @@
       <c r="H48" s="25"/>
       <c r="I48" s="203"/>
       <c r="J48" s="25"/>
-      <c r="K48" s="151"/>
+      <c r="K48" s="153"/>
       <c r="L48" s="25"/>
       <c r="M48" s="61"/>
       <c r="N48" s="25"/>
     </row>
-    <row r="49" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A49" s="56"/>
-      <c r="B49" s="166"/>
+      <c r="B49" s="168"/>
       <c r="C49" s="35" t="s">
         <v>11</v>
       </c>
-      <c r="D49" s="216"/>
+      <c r="D49" s="217"/>
       <c r="E49" s="22" t="s">
-        <v>168</v>
+        <v>177</v>
       </c>
       <c r="F49" s="83"/>
       <c r="G49" s="83"/>
-      <c r="H49" s="241" t="s">
-        <v>201</v>
-      </c>
+      <c r="H49" s="67"/>
       <c r="I49" s="67"/>
       <c r="J49" s="38" t="s">
-        <v>84</v>
-      </c>
-      <c r="K49" s="15"/>
+        <v>178</v>
+      </c>
+      <c r="K49" s="15" t="s">
+        <v>194</v>
+      </c>
       <c r="L49" s="15"/>
       <c r="M49" s="27"/>
       <c r="N49" s="61"/>
     </row>
-    <row r="50" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A50" s="56"/>
-      <c r="B50" s="166"/>
+      <c r="B50" s="168"/>
       <c r="C50" s="35" t="s">
         <v>6</v>
       </c>
       <c r="D50" s="229"/>
       <c r="E50" s="22" t="s">
-        <v>169</v>
+        <v>179</v>
       </c>
       <c r="F50" s="125" t="s">
-        <v>150</v>
+        <v>164</v>
       </c>
       <c r="G50" s="125"/>
-      <c r="H50" s="37" t="s">
-        <v>202</v>
-      </c>
-      <c r="I50" s="22" t="s">
-        <v>162</v>
+      <c r="H50" s="37"/>
+      <c r="I50" s="37" t="s">
+        <v>168</v>
       </c>
       <c r="J50" s="98"/>
       <c r="K50" s="81"/>
       <c r="L50" s="81"/>
       <c r="N50" s="61"/>
     </row>
-    <row r="51" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A51" s="41"/>
-      <c r="B51" s="164"/>
+      <c r="B51" s="166"/>
       <c r="C51" s="16"/>
       <c r="D51" s="17"/>
       <c r="E51" s="22"/>
@@ -3351,42 +3276,42 @@
         <v>18</v>
       </c>
     </row>
-    <row r="52" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A52" s="165" t="s">
+    <row r="52" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A52" s="167" t="s">
         <v>8</v>
       </c>
-      <c r="B52" s="218">
+      <c r="B52" s="219">
         <v>46195</v>
       </c>
       <c r="C52" s="12" t="s">
-        <v>147</v>
+        <v>159</v>
       </c>
       <c r="D52" s="12"/>
-      <c r="E52" s="224" t="s">
-        <v>220</v>
+      <c r="E52" s="225" t="s">
+        <v>87</v>
       </c>
       <c r="F52" s="132"/>
       <c r="G52" s="132"/>
       <c r="H52" s="44"/>
-      <c r="I52" s="44" t="s">
-        <v>170</v>
-      </c>
+      <c r="I52" s="44"/>
       <c r="J52" s="44" t="s">
-        <v>148</v>
+        <v>160</v>
       </c>
       <c r="K52" s="19"/>
-      <c r="L52" s="19"/>
+      <c r="L52" s="19" t="s">
+        <v>158</v>
+      </c>
       <c r="M52" s="26"/>
       <c r="N52" s="91">
         <v>2026</v>
       </c>
     </row>
-    <row r="53" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A53" s="108"/>
-      <c r="B53" s="167"/>
+      <c r="B53" s="169"/>
       <c r="C53" s="16"/>
       <c r="D53" s="17"/>
-      <c r="E53" s="205"/>
+      <c r="E53" s="206"/>
       <c r="F53" s="133"/>
       <c r="G53" s="133"/>
       <c r="H53" s="43"/>
@@ -3399,39 +3324,41 @@
         <v>19</v>
       </c>
     </row>
-    <row r="54" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A54" s="31" t="s">
         <v>9</v>
       </c>
-      <c r="B54" s="162">
+      <c r="B54" s="164">
         <v>46196</v>
       </c>
       <c r="C54" s="11" t="s">
-        <v>145</v>
+        <v>154</v>
       </c>
       <c r="D54" s="12"/>
-      <c r="E54" s="225" t="s">
-        <v>221</v>
+      <c r="E54" s="226" t="s">
+        <v>161</v>
       </c>
       <c r="F54" s="123"/>
       <c r="G54" s="123"/>
       <c r="H54" s="42"/>
       <c r="I54" s="42"/>
       <c r="J54" s="24" t="s">
-        <v>146</v>
-      </c>
-      <c r="K54" s="207"/>
-      <c r="L54" s="26"/>
+        <v>157</v>
+      </c>
+      <c r="K54" s="208"/>
+      <c r="L54" s="26" t="s">
+        <v>162</v>
+      </c>
       <c r="M54" s="22"/>
       <c r="N54" s="21" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="55" spans="1:14" x14ac:dyDescent="0.25">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="55" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A55" s="56"/>
-      <c r="B55" s="163"/>
+      <c r="B55" s="165"/>
       <c r="C55" s="14"/>
-      <c r="D55" s="184"/>
+      <c r="D55" s="185"/>
       <c r="E55" s="81"/>
       <c r="F55" s="134"/>
       <c r="G55" s="134"/>
@@ -3442,42 +3369,40 @@
       <c r="L55" s="15"/>
       <c r="M55" s="22"/>
       <c r="N55" s="106" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="56" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="56" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A56" s="56"/>
-      <c r="B56" s="166"/>
+      <c r="B56" s="168"/>
       <c r="C56" s="14"/>
-      <c r="D56" s="184"/>
+      <c r="D56" s="185"/>
       <c r="E56" s="15"/>
       <c r="F56" s="124"/>
       <c r="G56" s="124"/>
       <c r="H56" s="38"/>
       <c r="I56" s="38"/>
       <c r="J56" s="49"/>
-      <c r="K56" s="154"/>
+      <c r="K56" s="156"/>
       <c r="L56" s="79"/>
       <c r="M56" s="27"/>
       <c r="N56" s="92"/>
     </row>
-    <row r="57" spans="1:14" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:14" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A57" s="41"/>
-      <c r="B57" s="164"/>
+      <c r="B57" s="166"/>
       <c r="C57" s="16" t="s">
         <v>3</v>
       </c>
       <c r="D57" s="17"/>
       <c r="E57" s="22" t="s">
-        <v>171</v>
+        <v>182</v>
       </c>
       <c r="F57" s="129"/>
       <c r="G57" s="129"/>
-      <c r="H57" s="242" t="s">
-        <v>203</v>
-      </c>
+      <c r="H57" s="204"/>
       <c r="I57" s="40" t="s">
-        <v>86</v>
+        <v>181</v>
       </c>
       <c r="J57" s="43"/>
       <c r="K57" s="18"/>
@@ -3485,11 +3410,11 @@
       <c r="M57" s="58"/>
       <c r="N57" s="91"/>
     </row>
-    <row r="58" spans="1:14" ht="16.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A58" s="159" t="s">
+    <row r="58" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A58" s="161" t="s">
         <v>0</v>
       </c>
-      <c r="B58" s="168">
+      <c r="B58" s="170">
         <v>46197</v>
       </c>
       <c r="C58" s="7"/>
@@ -3497,7 +3422,7 @@
       <c r="E58" s="9"/>
       <c r="F58" s="84"/>
       <c r="G58" s="84"/>
-      <c r="H58" s="243"/>
+      <c r="H58" s="68"/>
       <c r="I58" s="68"/>
       <c r="J58" s="50"/>
       <c r="K58" s="10"/>
@@ -3507,11 +3432,11 @@
       </c>
       <c r="N58" s="92"/>
     </row>
-    <row r="59" spans="1:14" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A59" s="165" t="s">
+    <row r="59" spans="1:14" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A59" s="167" t="s">
         <v>1</v>
       </c>
-      <c r="B59" s="162">
+      <c r="B59" s="164">
         <v>46197</v>
       </c>
       <c r="C59" s="11"/>
@@ -3525,15 +3450,15 @@
       <c r="K59" s="118"/>
       <c r="L59" s="24"/>
       <c r="M59" s="55" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="N59" s="21"/>
     </row>
-    <row r="60" spans="1:14" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:14" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A60" s="56"/>
-      <c r="B60" s="166"/>
+      <c r="B60" s="168"/>
       <c r="C60" s="14"/>
-      <c r="D60" s="184"/>
+      <c r="D60" s="185"/>
       <c r="E60" s="32"/>
       <c r="F60" s="130"/>
       <c r="G60" s="130"/>
@@ -3543,15 +3468,15 @@
       <c r="K60" s="26"/>
       <c r="L60" s="26"/>
       <c r="M60" s="55" t="s">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="N60" s="90"/>
     </row>
-    <row r="61" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A61" s="56"/>
-      <c r="B61" s="166"/>
+      <c r="B61" s="168"/>
       <c r="C61" s="14"/>
-      <c r="D61" s="184"/>
+      <c r="D61" s="185"/>
       <c r="E61" s="15"/>
       <c r="F61" s="124"/>
       <c r="G61" s="124"/>
@@ -3561,43 +3486,43 @@
       <c r="K61" s="27"/>
       <c r="L61" s="27"/>
       <c r="M61" s="60" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="N61" s="90"/>
     </row>
-    <row r="62" spans="1:14" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:14" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A62" s="41"/>
-      <c r="B62" s="164"/>
+      <c r="B62" s="166"/>
       <c r="C62" s="33" t="s">
         <v>3</v>
       </c>
       <c r="D62" s="227"/>
       <c r="E62" s="22" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="F62" s="129" t="s">
-        <v>150</v>
+        <v>164</v>
       </c>
       <c r="G62" s="129"/>
-      <c r="H62" s="188" t="s">
-        <v>190</v>
-      </c>
-      <c r="I62" s="40" t="s">
-        <v>162</v>
+      <c r="H62" s="180"/>
+      <c r="I62" s="37" t="s">
+        <v>168</v>
       </c>
       <c r="J62" s="97"/>
       <c r="K62" s="77"/>
-      <c r="L62" s="99"/>
+      <c r="L62" s="99" t="s">
+        <v>94</v>
+      </c>
       <c r="M62" s="2" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="N62" s="27"/>
     </row>
-    <row r="63" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A63" s="165" t="s">
+    <row r="63" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A63" s="167" t="s">
         <v>2</v>
       </c>
-      <c r="B63" s="162">
+      <c r="B63" s="164">
         <v>46198</v>
       </c>
       <c r="C63" s="31"/>
@@ -3611,17 +3536,17 @@
       <c r="K63" s="80"/>
       <c r="L63" s="80"/>
       <c r="M63" s="22" t="s">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="N63" s="93" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="64" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A64" s="56"/>
-      <c r="B64" s="166"/>
+      <c r="B64" s="168"/>
       <c r="C64" s="35"/>
-      <c r="D64" s="184"/>
+      <c r="D64" s="185"/>
       <c r="E64" s="22"/>
       <c r="F64" s="125"/>
       <c r="G64" s="125"/>
@@ -3631,17 +3556,17 @@
       <c r="K64" s="15"/>
       <c r="L64" s="15"/>
       <c r="M64" s="22" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="N64" s="22" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="65" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A65" s="56"/>
-      <c r="B65" s="166"/>
+      <c r="B65" s="168"/>
       <c r="C65" s="35"/>
-      <c r="D65" s="184"/>
+      <c r="D65" s="185"/>
       <c r="E65" s="27"/>
       <c r="F65" s="137"/>
       <c r="G65" s="137"/>
@@ -3649,45 +3574,47 @@
       <c r="I65" s="52"/>
       <c r="J65" s="54"/>
       <c r="K65" s="32"/>
-      <c r="L65" s="23"/>
+      <c r="L65" s="23" t="s">
+        <v>95</v>
+      </c>
       <c r="M65" s="26" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="N65" s="22" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="66" spans="1:15" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:15" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A66" s="41"/>
-      <c r="B66" s="164"/>
+      <c r="B66" s="166"/>
       <c r="C66" s="16" t="s">
         <v>3</v>
       </c>
       <c r="D66" s="17"/>
-      <c r="E66" s="55" t="s">
-        <v>173</v>
+      <c r="E66" s="241" t="s">
+        <v>183</v>
       </c>
       <c r="F66" s="129"/>
       <c r="G66" s="129"/>
-      <c r="H66" s="241" t="s">
-        <v>204</v>
-      </c>
+      <c r="H66" s="40"/>
       <c r="I66" s="40"/>
-      <c r="J66" s="97"/>
+      <c r="J66" s="97" t="s">
+        <v>200</v>
+      </c>
       <c r="K66" s="77"/>
       <c r="L66" s="99"/>
       <c r="M66" s="22" t="s">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="N66" s="22" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="67" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A67" s="165" t="s">
+    <row r="67" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A67" s="167" t="s">
         <v>4</v>
       </c>
-      <c r="B67" s="162">
+      <c r="B67" s="164">
         <v>46199</v>
       </c>
       <c r="C67" s="36"/>
@@ -3701,48 +3628,46 @@
       <c r="K67" s="80"/>
       <c r="L67" s="80"/>
       <c r="M67" s="22" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="N67" s="22" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="68" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="68" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A68" s="56"/>
-      <c r="B68" s="166"/>
+      <c r="B68" s="168"/>
       <c r="C68" s="14" t="s">
         <v>12</v>
       </c>
-      <c r="D68" s="184"/>
+      <c r="D68" s="185"/>
       <c r="E68" s="22" t="s">
         <v>63</v>
       </c>
       <c r="F68" s="130"/>
       <c r="G68" s="130"/>
-      <c r="H68" s="241" t="s">
-        <v>205</v>
-      </c>
+      <c r="H68" s="54"/>
       <c r="I68" s="54"/>
       <c r="J68" s="40" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="K68" s="26" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="L68" s="26"/>
       <c r="M68" s="22" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="N68" s="65" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="69" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="69" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A69" s="56"/>
-      <c r="B69" s="166"/>
+      <c r="B69" s="168"/>
       <c r="C69" s="14"/>
-      <c r="D69" s="184"/>
-      <c r="E69" s="217"/>
+      <c r="D69" s="185"/>
+      <c r="E69" s="218"/>
       <c r="F69" s="124"/>
       <c r="G69" s="124"/>
       <c r="H69" s="38"/>
@@ -3751,53 +3676,53 @@
       <c r="K69" s="27"/>
       <c r="L69" s="27"/>
       <c r="M69" s="22" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="N69" s="25" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="O69" s="5"/>
     </row>
-    <row r="70" spans="1:15" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:15" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A70" s="41"/>
-      <c r="B70" s="164"/>
+      <c r="B70" s="166"/>
       <c r="C70" s="16" t="s">
         <v>3</v>
       </c>
       <c r="D70" s="227"/>
       <c r="E70" s="2" t="s">
-        <v>174</v>
+        <v>184</v>
       </c>
       <c r="F70" s="129" t="s">
-        <v>150</v>
+        <v>164</v>
       </c>
       <c r="G70" s="129"/>
-      <c r="H70" s="241" t="s">
-        <v>206</v>
-      </c>
-      <c r="I70" s="40" t="s">
-        <v>154</v>
+      <c r="H70" s="37"/>
+      <c r="I70" s="78" t="s">
+        <v>181</v>
       </c>
       <c r="J70" s="97"/>
       <c r="K70" s="77"/>
       <c r="L70" s="78"/>
       <c r="M70" s="22" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="N70" s="25" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="71" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A71" s="165" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="71" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A71" s="167" t="s">
         <v>5</v>
       </c>
-      <c r="B71" s="218">
+      <c r="B71" s="219">
         <v>46200</v>
       </c>
       <c r="C71" s="11"/>
       <c r="D71" s="12"/>
-      <c r="E71" s="176"/>
+      <c r="E71" s="177" t="s">
+        <v>88</v>
+      </c>
       <c r="F71" s="138"/>
       <c r="G71" s="138"/>
       <c r="H71" s="139"/>
@@ -3806,21 +3731,21 @@
       <c r="K71" s="24"/>
       <c r="L71" s="34"/>
       <c r="M71" s="22" t="s">
-        <v>127</v>
+        <v>132</v>
       </c>
       <c r="N71" s="22" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="O71" s="4"/>
     </row>
-    <row r="72" spans="1:15" ht="13.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:15" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A72" s="56"/>
-      <c r="B72" s="166"/>
+      <c r="B72" s="168"/>
       <c r="C72" s="14" t="s">
         <v>11</v>
       </c>
-      <c r="D72" s="197"/>
-      <c r="E72" s="173"/>
+      <c r="D72" s="198"/>
+      <c r="E72" s="174"/>
       <c r="F72" s="140"/>
       <c r="G72" s="140"/>
       <c r="H72" s="141"/>
@@ -3831,46 +3756,46 @@
       <c r="K72" s="22"/>
       <c r="L72" s="22"/>
       <c r="M72" s="26" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="N72" s="25" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="73" spans="1:15" ht="13.9" customHeight="1" x14ac:dyDescent="0.25">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="73" spans="1:15" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A73" s="56"/>
-      <c r="B73" s="166"/>
+      <c r="B73" s="168"/>
       <c r="C73" s="14" t="s">
         <v>6</v>
       </c>
-      <c r="D73" s="197"/>
-      <c r="E73" s="175"/>
+      <c r="D73" s="198"/>
+      <c r="E73" s="176"/>
       <c r="F73" s="109"/>
       <c r="G73" s="83"/>
       <c r="H73" s="67"/>
       <c r="I73" s="67"/>
       <c r="J73" s="37" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="K73" s="15" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="L73" s="26"/>
       <c r="M73" s="61"/>
       <c r="N73" s="25" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="74" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="74" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A74" s="41"/>
-      <c r="B74" s="164"/>
+      <c r="B74" s="166"/>
       <c r="C74" s="16" t="s">
         <v>3</v>
       </c>
       <c r="D74" s="17"/>
-      <c r="E74" s="173"/>
+      <c r="E74" s="174"/>
       <c r="F74" s="145"/>
-      <c r="G74" s="181"/>
+      <c r="G74" s="182"/>
       <c r="H74" s="142"/>
       <c r="I74" s="142"/>
       <c r="J74" s="39"/>
@@ -3878,14 +3803,14 @@
       <c r="L74" s="78"/>
       <c r="M74" s="61"/>
       <c r="N74" s="61" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="75" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A75" s="165" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="75" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A75" s="167" t="s">
         <v>7</v>
       </c>
-      <c r="B75" s="162">
+      <c r="B75" s="164">
         <v>46201</v>
       </c>
       <c r="C75" s="36"/>
@@ -3896,56 +3821,54 @@
       <c r="H75" s="25"/>
       <c r="I75" s="203"/>
       <c r="J75" s="25"/>
-      <c r="K75" s="151"/>
+      <c r="K75" s="153"/>
       <c r="L75" s="25"/>
       <c r="M75" s="61"/>
       <c r="N75" s="22" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="76" spans="1:15" x14ac:dyDescent="0.25">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="76" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A76" s="56"/>
-      <c r="B76" s="166"/>
+      <c r="B76" s="168"/>
       <c r="C76" s="35" t="s">
         <v>11</v>
       </c>
-      <c r="D76" s="216"/>
+      <c r="D76" s="217"/>
       <c r="E76" s="25" t="s">
-        <v>175</v>
+        <v>185</v>
       </c>
       <c r="F76" s="83"/>
       <c r="G76" s="83"/>
-      <c r="H76" s="241" t="s">
-        <v>207</v>
-      </c>
+      <c r="H76" s="37"/>
       <c r="I76" s="67"/>
       <c r="J76" s="38" t="s">
-        <v>45</v>
-      </c>
-      <c r="K76" s="15"/>
+        <v>44</v>
+      </c>
+      <c r="K76" s="15" t="s">
+        <v>83</v>
+      </c>
       <c r="L76" s="15"/>
       <c r="M76" s="27"/>
       <c r="N76" s="56" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="77" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="77" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A77" s="56"/>
-      <c r="B77" s="166"/>
+      <c r="B77" s="168"/>
       <c r="C77" s="35" t="s">
         <v>6</v>
       </c>
       <c r="D77" s="229"/>
       <c r="E77" s="22" t="s">
-        <v>176</v>
+        <v>186</v>
       </c>
       <c r="F77" s="125"/>
       <c r="G77" s="125"/>
-      <c r="H77" s="241" t="s">
-        <v>208</v>
-      </c>
-      <c r="I77" s="37" t="s">
-        <v>177</v>
+      <c r="H77" s="37"/>
+      <c r="I77" s="26" t="s">
+        <v>181</v>
       </c>
       <c r="J77" s="98"/>
       <c r="K77" s="81"/>
@@ -3955,23 +3878,21 @@
         <v>65</v>
       </c>
     </row>
-    <row r="78" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A78" s="41"/>
-      <c r="B78" s="164"/>
+      <c r="B78" s="166"/>
       <c r="C78" s="16" t="s">
         <v>3</v>
       </c>
       <c r="D78" s="227"/>
-      <c r="E78" s="55" t="s">
-        <v>178</v>
+      <c r="E78" s="241" t="s">
+        <v>187</v>
       </c>
       <c r="F78" s="144"/>
       <c r="G78" s="144"/>
-      <c r="H78" s="241" t="s">
-        <v>209</v>
-      </c>
+      <c r="H78"/>
       <c r="I78" s="131" t="s">
-        <v>179</v>
+        <v>189</v>
       </c>
       <c r="J78" s="41"/>
       <c r="K78" s="108"/>
@@ -3981,11 +3902,11 @@
         <v>73</v>
       </c>
     </row>
-    <row r="79" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A79" s="165" t="s">
+    <row r="79" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A79" s="167" t="s">
         <v>8</v>
       </c>
-      <c r="B79" s="162">
+      <c r="B79" s="164">
         <v>46202</v>
       </c>
       <c r="C79" s="11"/>
@@ -4003,9 +3924,9 @@
         <v>74</v>
       </c>
     </row>
-    <row r="80" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A80" s="108"/>
-      <c r="B80" s="167"/>
+      <c r="B80" s="169"/>
       <c r="C80" s="16"/>
       <c r="D80" s="17"/>
       <c r="E80" s="18"/>
@@ -4018,14 +3939,14 @@
       <c r="L80" s="18"/>
       <c r="M80" s="26"/>
       <c r="N80" s="22" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="81" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="81" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A81" s="31" t="s">
         <v>9</v>
       </c>
-      <c r="B81" s="162">
+      <c r="B81" s="164">
         <v>46203</v>
       </c>
       <c r="C81" s="11"/>
@@ -4041,69 +3962,69 @@
       <c r="M81" s="22"/>
       <c r="N81" s="21"/>
     </row>
-    <row r="82" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A82" s="56"/>
-      <c r="B82" s="163"/>
+      <c r="B82" s="165"/>
       <c r="C82" s="14"/>
-      <c r="D82" s="184"/>
+      <c r="D82" s="185"/>
       <c r="E82" s="27"/>
       <c r="F82" s="137"/>
       <c r="G82" s="134"/>
       <c r="H82" s="52"/>
       <c r="I82" s="135"/>
       <c r="J82" s="45"/>
-      <c r="K82" s="156"/>
+      <c r="K82" s="158"/>
       <c r="L82" s="21"/>
       <c r="M82" s="22"/>
       <c r="N82" s="96" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="83" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A83" s="56"/>
-      <c r="B83" s="166"/>
+      <c r="B83" s="168"/>
       <c r="C83" s="14"/>
-      <c r="D83" s="184"/>
+      <c r="D83" s="185"/>
       <c r="E83" s="15"/>
       <c r="F83" s="124"/>
       <c r="G83" s="124"/>
       <c r="H83" s="38"/>
       <c r="I83" s="38"/>
       <c r="J83" s="49"/>
-      <c r="K83" s="154"/>
+      <c r="K83" s="156"/>
       <c r="L83" s="79"/>
       <c r="M83" s="27"/>
       <c r="N83" s="88"/>
     </row>
-    <row r="84" spans="1:15" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:15" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A84" s="41"/>
-      <c r="B84" s="164"/>
+      <c r="B84" s="166"/>
       <c r="C84" s="16" t="s">
         <v>3</v>
       </c>
       <c r="D84" s="17"/>
-      <c r="E84" s="60" t="s">
-        <v>180</v>
+      <c r="E84" s="242" t="s">
+        <v>188</v>
       </c>
       <c r="F84" s="129" t="s">
-        <v>150</v>
+        <v>164</v>
       </c>
       <c r="G84" s="129"/>
-      <c r="H84" s="242" t="s">
-        <v>210</v>
-      </c>
+      <c r="H84" s="40"/>
       <c r="I84" s="40"/>
-      <c r="J84" s="43"/>
+      <c r="J84" s="43" t="s">
+        <v>169</v>
+      </c>
       <c r="K84" s="18"/>
       <c r="L84" s="18"/>
       <c r="M84" s="58"/>
       <c r="N84" s="25"/>
     </row>
-    <row r="85" spans="1:15" ht="16.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A85" s="159" t="s">
+    <row r="85" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A85" s="161" t="s">
         <v>0</v>
       </c>
-      <c r="B85" s="168">
+      <c r="B85" s="170">
         <v>46204</v>
       </c>
       <c r="C85" s="7"/>
@@ -4111,7 +4032,7 @@
       <c r="E85" s="9"/>
       <c r="F85" s="84"/>
       <c r="G85" s="84"/>
-      <c r="H85" s="243"/>
+      <c r="H85" s="68"/>
       <c r="I85" s="68"/>
       <c r="J85" s="50"/>
       <c r="K85" s="10"/>
@@ -4121,11 +4042,11 @@
       </c>
       <c r="N85" s="25"/>
     </row>
-    <row r="86" spans="1:15" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A86" s="165" t="s">
+    <row r="86" spans="1:15" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A86" s="167" t="s">
         <v>1</v>
       </c>
-      <c r="B86" s="162">
+      <c r="B86" s="164">
         <v>46204</v>
       </c>
       <c r="C86" s="11"/>
@@ -4139,15 +4060,15 @@
       <c r="K86" s="34"/>
       <c r="L86" s="34"/>
       <c r="M86" s="55" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="N86" s="25"/>
     </row>
-    <row r="87" spans="1:15" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:15" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A87" s="56"/>
-      <c r="B87" s="166"/>
+      <c r="B87" s="168"/>
       <c r="C87" s="14"/>
-      <c r="D87" s="184"/>
+      <c r="D87" s="185"/>
       <c r="E87" s="32"/>
       <c r="F87" s="130"/>
       <c r="G87" s="130"/>
@@ -4157,15 +4078,15 @@
       <c r="K87" s="26"/>
       <c r="L87" s="26"/>
       <c r="M87" s="55" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="N87" s="25"/>
     </row>
-    <row r="88" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A88" s="56"/>
-      <c r="B88" s="166"/>
+      <c r="B88" s="168"/>
       <c r="C88" s="35"/>
-      <c r="D88" s="184"/>
+      <c r="D88" s="185"/>
       <c r="E88" s="15"/>
       <c r="F88" s="124"/>
       <c r="G88" s="124"/>
@@ -4175,43 +4096,43 @@
       <c r="K88" s="27"/>
       <c r="L88" s="27"/>
       <c r="M88" s="60" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="N88" s="25"/>
     </row>
-    <row r="89" spans="1:15" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:15" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A89" s="41"/>
-      <c r="B89" s="164"/>
+      <c r="B89" s="166"/>
       <c r="C89" s="33" t="s">
         <v>3</v>
       </c>
       <c r="D89" s="17"/>
-      <c r="E89" s="60" t="s">
-        <v>182</v>
+      <c r="E89" s="242" t="s">
+        <v>191</v>
       </c>
       <c r="F89" s="129" t="s">
-        <v>150</v>
+        <v>164</v>
       </c>
       <c r="G89" s="129"/>
-      <c r="H89" s="242" t="s">
-        <v>211</v>
-      </c>
+      <c r="H89" s="40"/>
       <c r="I89" s="40" t="s">
-        <v>181</v>
-      </c>
-      <c r="J89" s="97"/>
+        <v>190</v>
+      </c>
+      <c r="J89" s="97" t="s">
+        <v>172</v>
+      </c>
       <c r="K89" s="77"/>
       <c r="L89" s="15"/>
       <c r="M89" s="22" t="s">
-        <v>129</v>
+        <v>134</v>
       </c>
       <c r="N89" s="25"/>
     </row>
-    <row r="90" spans="1:15" ht="15.75" x14ac:dyDescent="0.3">
-      <c r="A90" s="165" t="s">
+    <row r="90" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A90" s="167" t="s">
         <v>2</v>
       </c>
-      <c r="B90" s="218">
+      <c r="B90" s="219">
         <v>46205</v>
       </c>
       <c r="C90" s="119"/>
@@ -4219,41 +4140,43 @@
       <c r="E90" s="13"/>
       <c r="F90" s="123"/>
       <c r="G90" s="123"/>
-      <c r="H90" s="243"/>
+      <c r="H90" s="42"/>
       <c r="I90" s="42"/>
       <c r="J90" s="46"/>
       <c r="K90" s="118"/>
       <c r="L90" s="24"/>
       <c r="M90" s="22" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="N90" s="87"/>
     </row>
-    <row r="91" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A91" s="56"/>
-      <c r="B91" s="166"/>
+      <c r="B91" s="168"/>
       <c r="C91" s="35"/>
-      <c r="D91" s="184"/>
-      <c r="E91" s="213"/>
+      <c r="D91" s="185"/>
+      <c r="E91" s="214" t="s">
+        <v>89</v>
+      </c>
       <c r="F91" s="125"/>
       <c r="G91" s="125"/>
       <c r="H91" s="37"/>
       <c r="I91" s="26"/>
       <c r="J91" s="54"/>
-      <c r="K91" s="156"/>
+      <c r="K91" s="158"/>
       <c r="L91" s="21"/>
       <c r="M91" s="22" t="s">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="N91" s="107" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="92" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A92" s="56"/>
-      <c r="B92" s="166"/>
-      <c r="D92" s="184"/>
-      <c r="E92" s="204"/>
+      <c r="B92" s="168"/>
+      <c r="D92" s="185"/>
+      <c r="E92" s="205"/>
       <c r="F92" s="137"/>
       <c r="G92" s="137"/>
       <c r="H92" s="52"/>
@@ -4262,20 +4185,20 @@
       <c r="K92" s="32"/>
       <c r="L92" s="32"/>
       <c r="M92" s="26" t="s">
-        <v>131</v>
-      </c>
-      <c r="N92" s="177" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="93" spans="1:15" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+        <v>136</v>
+      </c>
+      <c r="N92" s="178" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="93" spans="1:15" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A93" s="41"/>
-      <c r="B93" s="164"/>
+      <c r="B93" s="166"/>
       <c r="C93" s="16" t="s">
         <v>3</v>
       </c>
       <c r="D93" s="17"/>
-      <c r="E93" s="173"/>
+      <c r="E93" s="174"/>
       <c r="F93" s="129"/>
       <c r="G93" s="129"/>
       <c r="H93" s="40"/>
@@ -4284,15 +4207,15 @@
       <c r="K93" s="77"/>
       <c r="L93" s="15"/>
       <c r="M93" s="22" t="s">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="N93" s="65"/>
     </row>
-    <row r="94" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A94" s="165" t="s">
+    <row r="94" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A94" s="167" t="s">
         <v>4</v>
       </c>
-      <c r="B94" s="162">
+      <c r="B94" s="164">
         <v>46206</v>
       </c>
       <c r="C94" s="36"/>
@@ -4306,15 +4229,15 @@
       <c r="K94" s="80"/>
       <c r="L94" s="80"/>
       <c r="M94" s="22" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="N94" s="65"/>
     </row>
-    <row r="95" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A95" s="56"/>
-      <c r="B95" s="166"/>
+      <c r="B95" s="168"/>
       <c r="C95" s="35"/>
-      <c r="D95" s="184"/>
+      <c r="D95" s="185"/>
       <c r="E95" s="22"/>
       <c r="F95" s="130"/>
       <c r="G95" s="130"/>
@@ -4324,15 +4247,15 @@
       <c r="K95" s="26"/>
       <c r="L95" s="26"/>
       <c r="M95" s="22" t="s">
-        <v>133</v>
+        <v>138</v>
       </c>
       <c r="N95" s="25"/>
     </row>
-    <row r="96" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A96" s="56"/>
-      <c r="B96" s="166"/>
+      <c r="B96" s="168"/>
       <c r="C96" s="14"/>
-      <c r="D96" s="184"/>
+      <c r="D96" s="185"/>
       <c r="E96" s="15"/>
       <c r="F96" s="124"/>
       <c r="G96" s="124"/>
@@ -4342,40 +4265,40 @@
       <c r="K96" s="27"/>
       <c r="L96" s="27"/>
       <c r="M96" s="22" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="N96" s="65"/>
       <c r="O96" s="5"/>
     </row>
-    <row r="97" spans="1:15" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:15" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A97" s="41"/>
-      <c r="B97" s="164"/>
+      <c r="B97" s="166"/>
       <c r="C97" s="16" t="s">
         <v>3</v>
       </c>
       <c r="D97" s="227"/>
       <c r="E97" s="22" t="s">
-        <v>169</v>
+        <v>179</v>
       </c>
       <c r="F97" s="129" t="s">
-        <v>150</v>
+        <v>164</v>
       </c>
       <c r="G97" s="129"/>
-      <c r="H97" s="40" t="s">
-        <v>212</v>
-      </c>
-      <c r="I97" s="40" t="s">
-        <v>162</v>
+      <c r="H97" s="40"/>
+      <c r="I97" s="37" t="s">
+        <v>168</v>
       </c>
       <c r="J97" s="97"/>
       <c r="K97" s="77"/>
-      <c r="L97" s="77"/>
+      <c r="L97" s="77" t="s">
+        <v>84</v>
+      </c>
       <c r="M97" s="22" t="s">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c r="N97" s="27"/>
     </row>
-    <row r="98" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A98" s="230" t="s">
         <v>5</v>
       </c>
@@ -4384,7 +4307,9 @@
       </c>
       <c r="C98" s="11"/>
       <c r="D98" s="12"/>
-      <c r="E98" s="176"/>
+      <c r="E98" s="177" t="s">
+        <v>90</v>
+      </c>
       <c r="F98" s="138"/>
       <c r="G98" s="138"/>
       <c r="H98" s="139"/>
@@ -4393,38 +4318,36 @@
       <c r="K98" s="24"/>
       <c r="L98" s="34"/>
       <c r="M98" s="22" t="s">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="N98" s="25"/>
       <c r="O98" s="4"/>
     </row>
-    <row r="99" spans="1:15" ht="13.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:15" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A99" s="232"/>
       <c r="B99" s="233"/>
       <c r="C99" s="14" t="s">
-        <v>138</v>
-      </c>
-      <c r="D99" s="197"/>
+        <v>143</v>
+      </c>
+      <c r="D99" s="198"/>
       <c r="E99" s="22" t="s">
-        <v>165</v>
+        <v>174</v>
       </c>
       <c r="F99" s="140"/>
       <c r="G99" s="140"/>
-      <c r="H99" s="242" t="s">
-        <v>211</v>
-      </c>
+      <c r="H99" s="141"/>
       <c r="I99" s="141"/>
-      <c r="J99" s="37"/>
-      <c r="K99" s="22" t="s">
-        <v>85</v>
-      </c>
+      <c r="J99" s="37" t="s">
+        <v>44</v>
+      </c>
+      <c r="K99" s="22"/>
       <c r="L99" s="22"/>
       <c r="M99" s="26" t="s">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c r="N99" s="25"/>
     </row>
-    <row r="100" spans="1:15" ht="13.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:15" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A100" s="232"/>
       <c r="B100" s="233"/>
       <c r="C100" s="14" t="s">
@@ -4432,29 +4355,27 @@
       </c>
       <c r="D100" s="229"/>
       <c r="E100" s="22" t="s">
-        <v>166</v>
+        <v>180</v>
       </c>
       <c r="F100" s="83" t="s">
-        <v>183</v>
+        <v>192</v>
       </c>
       <c r="G100" s="83"/>
-      <c r="H100" s="142" t="s">
-        <v>200</v>
-      </c>
+      <c r="H100" s="67"/>
       <c r="I100" s="67"/>
       <c r="J100" s="37" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="K100" s="15" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="L100" s="15"/>
       <c r="M100" s="61" t="s">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="N100" s="25"/>
     </row>
-    <row r="101" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A101" s="234"/>
       <c r="B101" s="235"/>
       <c r="C101" s="16" t="s">
@@ -4462,21 +4383,21 @@
       </c>
       <c r="D101" s="227"/>
       <c r="E101" s="22" t="s">
-        <v>184</v>
+        <v>193</v>
       </c>
       <c r="F101" s="145"/>
-      <c r="G101" s="181"/>
-      <c r="H101" s="242" t="s">
-        <v>213</v>
-      </c>
-      <c r="I101" s="131"/>
+      <c r="G101" s="182"/>
+      <c r="H101" s="142"/>
+      <c r="I101" s="78" t="s">
+        <v>181</v>
+      </c>
       <c r="J101" s="39"/>
       <c r="K101" s="78"/>
       <c r="L101" s="30"/>
       <c r="M101" s="61"/>
       <c r="N101" s="61"/>
     </row>
-    <row r="102" spans="1:15" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A102" s="230" t="s">
         <v>7</v>
       </c>
@@ -4485,10 +4406,12 @@
       </c>
       <c r="C102" s="11"/>
       <c r="D102" s="12"/>
-      <c r="E102" s="214"/>
+      <c r="E102" s="215" t="s">
+        <v>90</v>
+      </c>
       <c r="F102" s="143"/>
       <c r="G102" s="143"/>
-      <c r="H102" s="243"/>
+      <c r="H102" s="149"/>
       <c r="I102" s="25"/>
       <c r="J102" s="25"/>
       <c r="K102" s="126"/>
@@ -4496,14 +4419,14 @@
       <c r="M102" s="61"/>
       <c r="N102" s="22"/>
     </row>
-    <row r="103" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A103" s="232"/>
       <c r="B103" s="233"/>
       <c r="C103" s="14" t="s">
         <v>11</v>
       </c>
-      <c r="D103" s="219"/>
-      <c r="E103" s="173"/>
+      <c r="D103" s="220"/>
+      <c r="E103" s="174"/>
       <c r="F103" s="83"/>
       <c r="G103" s="83"/>
       <c r="H103" s="67"/>
@@ -4514,41 +4437,41 @@
       <c r="M103" s="27"/>
       <c r="N103" s="25"/>
     </row>
-    <row r="104" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A104" s="232"/>
       <c r="B104" s="233"/>
       <c r="C104" s="14" t="s">
         <v>6</v>
       </c>
-      <c r="D104" s="197"/>
-      <c r="E104" s="175"/>
+      <c r="D104" s="198"/>
+      <c r="E104" s="176"/>
       <c r="F104" s="125"/>
       <c r="G104" s="125"/>
       <c r="H104" s="37"/>
-      <c r="I104" s="149"/>
+      <c r="I104" s="150"/>
       <c r="J104" s="98"/>
       <c r="K104" s="81"/>
-      <c r="L104" s="81"/>
+      <c r="L104" s="81" t="s">
+        <v>84</v>
+      </c>
       <c r="M104" s="22"/>
       <c r="N104" s="65"/>
     </row>
-    <row r="105" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A105" s="234"/>
       <c r="B105" s="235"/>
       <c r="C105" s="16" t="s">
         <v>3</v>
       </c>
       <c r="D105" s="227"/>
-      <c r="E105" s="60" t="s">
-        <v>185</v>
+      <c r="E105" s="242" t="s">
+        <v>198</v>
       </c>
       <c r="F105" s="144"/>
       <c r="G105" s="144"/>
-      <c r="H105" s="241" t="s">
-        <v>214</v>
-      </c>
+      <c r="H105" s="131"/>
       <c r="I105" s="131" t="s">
-        <v>186</v>
+        <v>195</v>
       </c>
       <c r="J105" s="41"/>
       <c r="K105" s="108"/>
@@ -4556,7 +4479,7 @@
       <c r="M105" s="26"/>
       <c r="N105" s="27"/>
     </row>
-    <row r="106" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A106" s="230" t="s">
         <v>8</v>
       </c>
@@ -4568,17 +4491,15 @@
       <c r="E106" s="19"/>
       <c r="F106" s="132"/>
       <c r="G106" s="132"/>
-      <c r="H106" s="208"/>
+      <c r="H106" s="209"/>
       <c r="I106" s="44"/>
       <c r="J106" s="44"/>
-      <c r="K106" s="155">
-        <v>4</v>
-      </c>
+      <c r="K106" s="157"/>
       <c r="L106" s="19"/>
       <c r="M106" s="26"/>
       <c r="N106" s="22"/>
     </row>
-    <row r="107" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A107" s="237"/>
       <c r="B107" s="238"/>
       <c r="C107" s="16"/>
@@ -4594,7 +4515,7 @@
       <c r="M107" s="26"/>
       <c r="N107" s="22"/>
     </row>
-    <row r="108" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A108" s="239" t="s">
         <v>9</v>
       </c>
@@ -4609,120 +4530,93 @@
       <c r="H108" s="42"/>
       <c r="I108" s="42"/>
       <c r="J108" s="46"/>
-      <c r="K108" s="169">
-        <v>2.8</v>
-      </c>
+      <c r="K108" s="171"/>
       <c r="L108" s="24"/>
       <c r="M108" s="22"/>
       <c r="N108" s="21"/>
     </row>
-    <row r="109" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A109" s="232"/>
       <c r="B109" s="240"/>
       <c r="C109" s="14" t="s">
         <v>11</v>
       </c>
-      <c r="D109" s="184"/>
+      <c r="D109" s="185"/>
       <c r="E109" s="22" t="s">
-        <v>187</v>
+        <v>197</v>
       </c>
       <c r="F109" s="134"/>
       <c r="G109" s="134"/>
-      <c r="H109" s="241" t="s">
-        <v>215</v>
-      </c>
+      <c r="H109" s="151"/>
       <c r="I109" s="135"/>
-      <c r="J109" s="40"/>
-      <c r="K109" s="170"/>
+      <c r="J109" s="40" t="s">
+        <v>196</v>
+      </c>
+      <c r="K109" s="15" t="s">
+        <v>83</v>
+      </c>
       <c r="L109" s="21"/>
       <c r="M109" s="22"/>
       <c r="N109" s="57"/>
     </row>
-    <row r="110" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A110" s="232"/>
       <c r="B110" s="233"/>
       <c r="C110" s="14"/>
-      <c r="D110" s="184"/>
+      <c r="D110" s="185"/>
       <c r="E110" s="15"/>
       <c r="F110" s="124"/>
       <c r="G110" s="124"/>
       <c r="H110" s="38"/>
       <c r="I110" s="38"/>
       <c r="J110" s="49"/>
-      <c r="K110" s="154"/>
+      <c r="K110" s="156"/>
       <c r="L110" s="79"/>
       <c r="M110" s="27"/>
       <c r="N110" s="88"/>
     </row>
-    <row r="111" spans="1:15" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:15" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A111" s="234"/>
       <c r="B111" s="235"/>
       <c r="C111" s="16" t="s">
         <v>3</v>
       </c>
       <c r="D111" s="17"/>
-      <c r="E111" s="226" t="s">
-        <v>188</v>
-      </c>
-      <c r="F111" s="150" t="s">
-        <v>150</v>
-      </c>
-      <c r="G111" s="150"/>
-      <c r="H111" s="241" t="s">
-        <v>216</v>
-      </c>
+      <c r="E111" s="243" t="s">
+        <v>199</v>
+      </c>
+      <c r="F111" s="152" t="s">
+        <v>164</v>
+      </c>
+      <c r="G111" s="152"/>
+      <c r="H111" s="78"/>
       <c r="I111" s="78"/>
-      <c r="J111" s="43"/>
+      <c r="J111" s="43" t="s">
+        <v>169</v>
+      </c>
       <c r="K111" s="18"/>
-      <c r="L111" s="183"/>
+      <c r="L111" s="184"/>
       <c r="M111" s="94"/>
       <c r="N111" s="95"/>
     </row>
-    <row r="113" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E113" s="110" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="114" spans="5:5" ht="110.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="E114" s="111"/>
+    <row r="113" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E113" s="110"/>
+    </row>
+    <row r="114" spans="5:5" ht="110.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="E114" s="111" t="s">
+        <v>201</v>
+      </c>
     </row>
   </sheetData>
-  <hyperlinks>
-    <hyperlink ref="H22" r:id="rId1" display="https://www.allocine.fr/personne/fichepersonne_gen_cpersonne=745759.html" xr:uid="{D102DE13-2E86-4BBA-BB2F-4AC636EDE4DB}"/>
-    <hyperlink ref="H23" r:id="rId2" display="https://www.allocine.fr/personne/fichepersonne_gen_cpersonne=104291.html" xr:uid="{554F26B6-42B7-41CE-B26E-4FB1ADC9FDF5}"/>
-    <hyperlink ref="H24" r:id="rId3" display="https://www.allocine.fr/personne/fichepersonne_gen_cpersonne=824218.html" xr:uid="{D9589355-F6B0-4947-87F2-26B3F9D6F988}"/>
-    <hyperlink ref="H30" r:id="rId4" display="https://www.allocine.fr/personne/fichepersonne_gen_cpersonne=816044.html" xr:uid="{2C65D40A-1871-4C37-A909-5A367C0CED9D}"/>
-    <hyperlink ref="H35" r:id="rId5" display="https://www.allocine.fr/personne/fichepersonne_gen_cpersonne=26775.html" xr:uid="{E99DA839-9EAE-46C8-9966-8157BE556500}"/>
-    <hyperlink ref="H39" r:id="rId6" display="https://www.allocine.fr/personne/fichepersonne_gen_cpersonne=104291.html" xr:uid="{22AE17EF-CD25-4EC9-B854-8039426D8BDB}"/>
-    <hyperlink ref="H40" r:id="rId7" display="https://www.allocine.fr/personne/fichepersonne_gen_cpersonne=250774.html" xr:uid="{F6B24DBD-649F-4907-81AD-ED0573F0AD82}"/>
-    <hyperlink ref="H41" r:id="rId8" display="https://www.allocine.fr/personne/fichepersonne_gen_cpersonne=253074.html" xr:uid="{A9A5BD63-BA19-4C1D-803A-3F70DA0B7D2D}"/>
-    <hyperlink ref="H43" r:id="rId9" display="https://www.allocine.fr/personne/fichepersonne_gen_cpersonne=1000027639.html" xr:uid="{06A588E2-B740-4E9A-AE88-7E7B14EEB3A7}"/>
-    <hyperlink ref="H45" r:id="rId10" display="https://www.allocine.fr/personne/fichepersonne_gen_cpersonne=990126.html" xr:uid="{5D1340E0-BC03-4805-BCF3-AC059BC4A7E5}"/>
-    <hyperlink ref="H49" r:id="rId11" display="https://www.allocine.fr/personne/fichepersonne_gen_cpersonne=433596.html" xr:uid="{DBDA1A8A-0174-45DA-B890-3E8A2083A289}"/>
-    <hyperlink ref="H57" r:id="rId12" display="https://www.allocine.fr/personne/fichepersonne_gen_cpersonne=11282.html" xr:uid="{19095CDA-1362-4C52-B0EB-F25D1C4DA6EC}"/>
-    <hyperlink ref="H66" r:id="rId13" display="https://www.allocine.fr/personne/fichepersonne_gen_cpersonne=24248.html" xr:uid="{D435704D-57FD-4D64-A80C-3FB5769690EA}"/>
-    <hyperlink ref="H68" r:id="rId14" display="https://www.allocine.fr/personne/fichepersonne_gen_cpersonne=600795.html" xr:uid="{79FC6525-DE11-4E21-893F-2FD308A3249A}"/>
-    <hyperlink ref="H70" r:id="rId15" display="https://www.allocine.fr/personne/fichepersonne_gen_cpersonne=588933.html" xr:uid="{F79AC834-FA50-4FA3-BB34-CF0340424B5B}"/>
-    <hyperlink ref="H76" r:id="rId16" display="https://www.allocine.fr/personne/fichepersonne_gen_cpersonne=692388.html" xr:uid="{0865C441-72E3-4C69-89BB-BECCE1FCEE47}"/>
-    <hyperlink ref="H77" r:id="rId17" display="https://www.allocine.fr/personne/fichepersonne_gen_cpersonne=8400.html" xr:uid="{E4F31BF2-49D4-49B1-80B9-F2756FF0D2A4}"/>
-    <hyperlink ref="H78" r:id="rId18" display="https://www.allocine.fr/personne/fichepersonne_gen_cpersonne=146639.html" xr:uid="{0D3ACA65-D1C8-449A-9B0A-EDA503AA0CCD}"/>
-    <hyperlink ref="H84" r:id="rId19" display="https://www.allocine.fr/personne/fichepersonne_gen_cpersonne=11732.html" xr:uid="{178B91DA-3501-4B85-A8A1-FA531BFCF581}"/>
-    <hyperlink ref="H89" r:id="rId20" display="https://www.allocine.fr/personne/fichepersonne_gen_cpersonne=579873.html" xr:uid="{E2395DDC-9F0A-43A0-834C-3A30AAB6EAEC}"/>
-    <hyperlink ref="H99" r:id="rId21" display="https://www.allocine.fr/personne/fichepersonne_gen_cpersonne=579873.html" xr:uid="{66DC094A-D44A-42AE-9294-5E96086C33FA}"/>
-    <hyperlink ref="H101" r:id="rId22" display="https://www.allocine.fr/personne/fichepersonne_gen_cpersonne=658205.html" xr:uid="{FADFA2EE-7C7E-4BC1-AECA-BDED4215825C}"/>
-    <hyperlink ref="H105" r:id="rId23" display="https://www.allocine.fr/personne/fichepersonne_gen_cpersonne=14352.html" xr:uid="{5B50020C-4F64-408A-84D4-6D4D2092B7B1}"/>
-    <hyperlink ref="H109" r:id="rId24" display="https://www.allocine.fr/personne/fichepersonne_gen_cpersonne=55361.html" xr:uid="{A1F69754-CD4B-47AC-A844-21F4E227CD58}"/>
-    <hyperlink ref="H111" r:id="rId25" display="https://www.allocine.fr/personne/fichepersonne_gen_cpersonne=20968.html" xr:uid="{0D6889D5-2497-4E96-8590-8D1DAF79BDF0}"/>
-  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" scale="37" orientation="portrait" horizontalDpi="4294967293" verticalDpi="4294967293" r:id="rId26"/>
+  <pageSetup paperSize="9" scale="37" orientation="portrait" horizontalDpi="4294967293" verticalDpi="4294967293" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{19D8F6E0-B935-4442-A9F9-93EFDE55CF19}">
   <dimension ref="A1"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
